--- a/data.xlsx
+++ b/data.xlsx
@@ -5,18 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\personal\last-war-tools\streamlit-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186EDECB-D57A-422C-BDB3-63D73DA29521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52463D89-653A-49A9-8C25-10914957C08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="3504" windowWidth="31608" windowHeight="19884" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
+    <workbookView xWindow="8412" yWindow="4560" windowWidth="31620" windowHeight="19884" activeTab="2" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
   </bookViews>
   <sheets>
-    <sheet name="raw_20260609_185140" sheetId="1" r:id="rId1"/>
-    <sheet name="raw_20260609_185943" sheetId="2" r:id="rId2"/>
+    <sheet name="vs (thru Wed 740pm)" sheetId="1" r:id="rId1"/>
+    <sheet name="power" sheetId="2" r:id="rId2"/>
     <sheet name="analysis" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,59 +36,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="102">
-  <si>
-    <t>Heneral UNO</t>
-  </si>
-  <si>
-    <t>ClementineWoolysocks</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
   <si>
     <t>GhostSumit</t>
   </si>
   <si>
-    <t>Chota Rajan</t>
-  </si>
-  <si>
     <t>Acsoxg</t>
   </si>
   <si>
-    <t>spitttfire</t>
-  </si>
-  <si>
-    <t>Stache003</t>
-  </si>
-  <si>
     <t>Thailand5139</t>
   </si>
   <si>
-    <t>WASEEM KING 2</t>
-  </si>
-  <si>
     <t>Mager100hari</t>
   </si>
   <si>
-    <t>Kurosufy</t>
-  </si>
-  <si>
     <t>AlleyBoss129453</t>
   </si>
   <si>
-    <t>ϛϚMEOWW</t>
-  </si>
-  <si>
-    <t>SoldierRaja</t>
-  </si>
-  <si>
-    <t>DUMB011</t>
-  </si>
-  <si>
-    <t>TOY MISCHIEF</t>
-  </si>
-  <si>
-    <t>linxers</t>
-  </si>
-  <si>
     <t>Magykiall</t>
   </si>
   <si>
@@ -105,45 +68,21 @@
     <t>GlokkBoy</t>
   </si>
   <si>
-    <t>H4ZZ</t>
-  </si>
-  <si>
     <t>Baby shark67</t>
   </si>
   <si>
-    <t>ふぁみ Phamy</t>
-  </si>
-  <si>
     <t>Raven2222</t>
   </si>
   <si>
-    <t>tach2312</t>
-  </si>
-  <si>
-    <t>Beslaiq</t>
-  </si>
-  <si>
-    <t>Vestapubg77</t>
-  </si>
-  <si>
     <t>Pokachu</t>
   </si>
   <si>
-    <t>The Enlighten</t>
-  </si>
-  <si>
-    <t>Knox Vegas Hammy</t>
-  </si>
-  <si>
     <t>Jcox787</t>
   </si>
   <si>
     <t>MrSingh2026</t>
   </si>
   <si>
-    <t>Lucixdswyz</t>
-  </si>
-  <si>
     <t>fly in a blue dream</t>
   </si>
   <si>
@@ -153,15 +92,9 @@
     <t>The big Bopper</t>
   </si>
   <si>
-    <t>Tomaessa</t>
-  </si>
-  <si>
     <t>Skylsaa</t>
   </si>
   <si>
-    <t>Omega Priime</t>
-  </si>
-  <si>
     <t>Whethackk</t>
   </si>
   <si>
@@ -186,27 +119,12 @@
     <t>라떼아이스2</t>
   </si>
   <si>
-    <t>Foxxiegirl</t>
-  </si>
-  <si>
     <t>Fwaankmom</t>
   </si>
   <si>
-    <t>Oquz61</t>
-  </si>
-  <si>
-    <t>3rootstilk3</t>
-  </si>
-  <si>
     <t>Kavaz25</t>
   </si>
   <si>
-    <t>vodkababara7</t>
-  </si>
-  <si>
-    <t>Tibas2</t>
-  </si>
-  <si>
     <t>Punsilly</t>
   </si>
   <si>
@@ -222,15 +140,6 @@
     <t>Visgimir</t>
   </si>
   <si>
-    <t>SuperZzZz</t>
-  </si>
-  <si>
-    <t>Sassy Chicken</t>
-  </si>
-  <si>
-    <t>Goody777</t>
-  </si>
-  <si>
     <t>Hokage IX</t>
   </si>
   <si>
@@ -249,45 +158,27 @@
     <t>Daryl Dixon1984</t>
   </si>
   <si>
-    <t>Violence99</t>
-  </si>
-  <si>
     <t>GatorsALegend</t>
   </si>
   <si>
-    <t>DaNoNinA</t>
-  </si>
-  <si>
     <t>CalonPolwan</t>
   </si>
   <si>
     <t>NiEvelka</t>
   </si>
   <si>
-    <t>GiosMegalo</t>
-  </si>
-  <si>
     <t>RaYYY</t>
   </si>
   <si>
     <t>Padre007cf</t>
   </si>
   <si>
-    <t>HunBro</t>
-  </si>
-  <si>
     <t>Crazy BuLL</t>
   </si>
   <si>
     <t>SkyInvalid</t>
   </si>
   <si>
-    <t>♡ Elena ♡</t>
-  </si>
-  <si>
-    <t>JennyBelle</t>
-  </si>
-  <si>
     <t>Bonifacy lub Filemon</t>
   </si>
   <si>
@@ -306,24 +197,12 @@
     <t>Firekeeper01</t>
   </si>
   <si>
-    <t>marcoporco</t>
-  </si>
-  <si>
     <t>player_name</t>
   </si>
   <si>
     <t>rank</t>
   </si>
   <si>
-    <t>Essam Abu Mughasib</t>
-  </si>
-  <si>
-    <t>WOLF 2274</t>
-  </si>
-  <si>
-    <t>Ờ  hớ</t>
-  </si>
-  <si>
     <t>Space   Ghost</t>
   </si>
   <si>
@@ -339,10 +218,151 @@
     <t>Composite</t>
   </si>
   <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Queenery♡</t>
+    <t>score</t>
+  </si>
+  <si>
+    <t>Ghostnova</t>
+  </si>
+  <si>
+    <t>BEEEF</t>
+  </si>
+  <si>
+    <t>Loganc77</t>
+  </si>
+  <si>
+    <t>Eagle741</t>
+  </si>
+  <si>
+    <t>crabasourus</t>
+  </si>
+  <si>
+    <t>Tenente Calango</t>
+  </si>
+  <si>
+    <t>Billtoppe</t>
+  </si>
+  <si>
+    <t>anh minh 1991</t>
+  </si>
+  <si>
+    <t>RhiannonVII</t>
+  </si>
+  <si>
+    <t>Absolute Obam</t>
+  </si>
+  <si>
+    <t>fortknox101</t>
+  </si>
+  <si>
+    <t>KittyLea</t>
+  </si>
+  <si>
+    <t>madsje</t>
+  </si>
+  <si>
+    <t>BummbleB33</t>
+  </si>
+  <si>
+    <t>Rembrandt00</t>
+  </si>
+  <si>
+    <t>Indiemeows</t>
+  </si>
+  <si>
+    <t>JojoBest</t>
+  </si>
+  <si>
+    <t>BadApples</t>
+  </si>
+  <si>
+    <t>nangst</t>
+  </si>
+  <si>
+    <t>elite4titude2</t>
+  </si>
+  <si>
+    <t>Star2933</t>
+  </si>
+  <si>
+    <t>StraightFacts</t>
+  </si>
+  <si>
+    <t>tinyocean</t>
+  </si>
+  <si>
+    <t>Voodooo ranger</t>
+  </si>
+  <si>
+    <t>NEP1ST0</t>
+  </si>
+  <si>
+    <t>دهماني</t>
+  </si>
+  <si>
+    <t>Z I M</t>
+  </si>
+  <si>
+    <t>Sa D Boi</t>
+  </si>
+  <si>
+    <t>GrimmKitty</t>
+  </si>
+  <si>
+    <t>راغنار ر</t>
+  </si>
+  <si>
+    <t>MinhTruong9x</t>
+  </si>
+  <si>
+    <t>emmy118</t>
+  </si>
+  <si>
+    <t>Berluscone95</t>
+  </si>
+  <si>
+    <t>scotch mist</t>
+  </si>
+  <si>
+    <t>Twinkletoes999</t>
+  </si>
+  <si>
+    <t>Qarizma04</t>
+  </si>
+  <si>
+    <t>Blackqq</t>
+  </si>
+  <si>
+    <t>Arthur   Morgan</t>
+  </si>
+  <si>
+    <t>Cursed Sick 2274</t>
+  </si>
+  <si>
+    <t>Thundrct</t>
+  </si>
+  <si>
+    <t>Shike Ryu</t>
+  </si>
+  <si>
+    <t>ℌ Vee ℌ</t>
+  </si>
+  <si>
+    <t>Ờ hố</t>
+  </si>
+  <si>
+    <t>BulletBill2026</t>
+  </si>
+  <si>
+    <t>M15k</t>
+  </si>
+  <si>
+    <t>Jatin ind</t>
+  </si>
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>Score</t>
   </si>
 </sst>
 </file>
@@ -351,9 +371,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +392,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3333FF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -399,13 +426,13 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -414,6 +441,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -515,289 +543,289 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="95"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.80800000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.77600000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.627</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.41399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.60599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.45700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.92500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.48899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.76500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.98899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.53100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.29699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.38200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.74399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.86099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.94599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.39300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.308</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.78700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.372</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.191</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.61699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.70199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.79700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.56299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.21199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.24399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.65900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.42499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.26500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>0.44600000000000001</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="44">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>0.91400000000000003</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="47">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.72299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.46800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.52100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.436</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.89300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.872</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>0.59499999999999997</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.2000000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.127</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="56">
+                  <c:v>0.58499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.81899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>0.23400000000000001</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.26500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.48899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.308</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="59">
                   <c:v>0.93600000000000005</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.82899999999999996</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.65900000000000003</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.1E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.89300000000000002</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.64800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.81899999999999995</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.78700000000000003</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.106</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.98899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.39300000000000002</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.56299999999999994</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.57399999999999995</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.80800000000000005</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>2.1000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.85099999999999998</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.51</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.71199999999999997</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.47799999999999998</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.255</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.73399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.88200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.97799999999999998</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="60">
+                  <c:v>0.35099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.31900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.27600000000000002</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>0.36099999999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.92500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.95699999999999996</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.60599999999999998</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.35099999999999998</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.11700000000000001</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.67</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.191</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.38200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>9.5000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.20200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.223</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.96799999999999997</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.372</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.76500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.72299999999999998</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.45700000000000002</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.58499999999999996</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.872</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.40400000000000003</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.32900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.63800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.28699999999999998</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.86099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
                   <c:v>0.755</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.94599999999999995</c:v>
+                  <c:v>0.40400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.70199999999999996</c:v>
+                  <c:v>0.20200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.90400000000000003</c:v>
+                  <c:v>0.63800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.436</c:v>
+                  <c:v>0.159</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.14799999999999999</c:v>
+                  <c:v>0.106</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.53100000000000003</c:v>
+                  <c:v>7.3999999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
+                  <c:v>0.73399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.223</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.54200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.28699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.55300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.82899999999999996</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>5.2999999999999999E-2</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="81">
+                  <c:v>0.255</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.64800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.69099999999999995</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.47799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.85099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.32900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
                   <c:v>6.3E-2</c:v>
                 </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.74399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.69099999999999995</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.29699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>7.3999999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.41399999999999998</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.627</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.42499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.77600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.31900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.79700000000000004</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>0.61699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>8.5000000000000006E-2</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.46800000000000003</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.52100000000000002</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.13800000000000001</c:v>
-                </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.27600000000000002</c:v>
+                  <c:v>0.71199999999999997</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.55300000000000005</c:v>
+                  <c:v>0.127</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.54200000000000004</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -809,289 +837,289 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="95"/>
                 <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.96799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.95699999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.94599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.93600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.92500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.91400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.90400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.89300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.88200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.872</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.85099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.82899999999999996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.81899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.80800000000000005</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="19">
+                  <c:v>0.79700000000000004</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.78700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.77600000000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.76500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.755</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.74399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.73399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.72299999999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.71199999999999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.70199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.69099999999999995</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.65900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.64800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.63800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.627</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.61699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.60599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.59499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.58499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.56299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.55300000000000005</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.54200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.53100000000000003</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.52100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>0.51</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="47">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.48899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.47799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.46800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.45700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.44600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.436</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.42499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.41399999999999998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.40400000000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.39300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.38200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.372</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.36099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.35099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.32900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.31900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.308</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.29699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.28699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.27600000000000002</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.26500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.255</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.24399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.23400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.223</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.21199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.20200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.191</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.159</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.14799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.127</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.11700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
                   <c:v>0.106</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.48899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.69099999999999995</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.191</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.372</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.85099999999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="85">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>4.2000000000000003E-2</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.72299999999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.29699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.35099999999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="91">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.98899999999999999</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.59499999999999997</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.73399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.13800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7.3999999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.71199999999999997</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8.5000000000000006E-2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.31900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.81899999999999995</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.23400000000000001</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>5.2999999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.94599999999999995</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.47799999999999998</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.20200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.56299999999999994</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.67</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>0.86099999999999999</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>0.64800000000000002</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>0.255</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>0.53100000000000003</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>0.89300000000000002</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>0.63800000000000001</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>0.95699999999999996</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>0.93600000000000005</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.436</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.57399999999999995</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.627</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.46800000000000003</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.42499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.1000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.39300000000000002</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.01</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.78700000000000003</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.55300000000000005</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.41399999999999998</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.88200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.74399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.54200000000000004</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.90400000000000003</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.60599999999999998</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.11700000000000001</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.68</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.70199999999999996</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.26500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>9.5000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>0.308</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>0.77600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>0.92500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>0.79700000000000004</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>0.872</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>0.755</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>0.45700000000000002</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>0.24399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>0.65900000000000003</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>0.21199999999999999</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>0.223</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>0.27600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>0.76500000000000001</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>0.52100000000000002</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.61699999999999999</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.32900000000000001</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>3.1E-2</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>0.84</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>0.40400000000000003</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>0.96799999999999997</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>0.91400000000000003</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>6.3E-2</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>0.127</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>0.58499999999999996</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>0.38200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>0.36099999999999999</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>0.44600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>0.28699999999999998</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>0.82899999999999996</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>0.97799999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2296,7 +2324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88A03F2-8926-4C01-BA57-6D8896DC3284}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
@@ -2305,13 +2333,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2319,10 +2347,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>12415346</v>
+        <v>15702055</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2330,10 +2358,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C3">
-        <v>12245364</v>
+        <v>12214971</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2341,10 +2369,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="C4">
-        <v>11634735</v>
+        <v>9119649</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2352,10 +2380,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>10569143</v>
+        <v>8611927</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2363,10 +2391,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>9314206</v>
+        <v>8401268</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2374,10 +2402,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>9247571</v>
+        <v>6311179</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2385,10 +2413,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>8931884</v>
+        <v>6194536</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2396,10 +2424,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C9">
-        <v>8603326</v>
+        <v>6070432</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2407,10 +2435,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C10">
-        <v>6966055</v>
+        <v>5827820</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2418,10 +2446,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C11">
-        <v>6863684</v>
+        <v>5794630</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2429,10 +2457,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="C12">
-        <v>6797175</v>
+        <v>5693755</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2440,10 +2468,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>6733809</v>
+        <v>5499645</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2451,10 +2479,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>6645174</v>
+        <v>5314806</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2462,10 +2490,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>6451253</v>
+        <v>4992116</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2473,10 +2501,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>6387590</v>
+        <v>4862491</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2484,10 +2512,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C17">
-        <v>6330561</v>
+        <v>4792980</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2495,10 +2523,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C18">
-        <v>6146150</v>
+        <v>4791169</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2506,10 +2534,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C19">
-        <v>6143355</v>
+        <v>4789200</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2517,10 +2545,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20">
-        <v>6115380</v>
+        <v>4737953</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2528,10 +2556,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21">
-        <v>6040919</v>
+        <v>4714228</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2542,7 +2570,7 @@
         <v>69</v>
       </c>
       <c r="C22">
-        <v>6013376</v>
+        <v>4647868</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2550,10 +2578,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C23">
-        <v>6008329</v>
+        <v>4627335</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2561,10 +2589,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>5969930</v>
+        <v>4546105</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2572,10 +2600,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>5904086</v>
+        <v>4365881</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2583,10 +2611,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C26">
-        <v>5730280</v>
+        <v>4150745</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2594,10 +2622,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C27">
-        <v>5638493</v>
+        <v>4150228</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2605,10 +2633,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C28">
-        <v>5636919</v>
+        <v>4121213</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2616,10 +2644,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C29">
-        <v>5553839</v>
+        <v>4109114</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2627,10 +2655,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C30">
-        <v>5225717</v>
+        <v>4088818</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2638,10 +2666,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C31">
-        <v>5225346</v>
+        <v>4011219</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2649,10 +2677,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C32">
-        <v>5128448</v>
+        <v>3884630</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2660,10 +2688,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C33">
-        <v>4995656</v>
+        <v>3826667</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2671,10 +2699,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C34">
-        <v>4935573</v>
+        <v>3810506</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2682,10 +2710,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="C35">
-        <v>4869154</v>
+        <v>3804815</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2693,10 +2721,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>4837386</v>
+        <v>3676403</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2704,10 +2732,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C37">
-        <v>4641189</v>
+        <v>3643650</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -2715,10 +2743,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C38">
-        <v>4576300</v>
+        <v>3641493</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2726,10 +2754,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>4523804</v>
+        <v>3509465</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -2737,10 +2765,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="C40">
-        <v>4448558</v>
+        <v>3491725</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -2748,10 +2776,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C41">
-        <v>4411775</v>
+        <v>3433393</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -2759,10 +2787,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C42">
-        <v>4404572</v>
+        <v>3370400</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -2770,10 +2798,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C43">
-        <v>4337158</v>
+        <v>3363330</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2781,10 +2809,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C44">
-        <v>4322394</v>
+        <v>3307184</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -2792,10 +2820,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C45">
-        <v>4206739</v>
+        <v>3198516</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -2803,10 +2831,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C46">
-        <v>4189911</v>
+        <v>3185355</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -2814,10 +2842,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C47">
-        <v>4149133</v>
+        <v>3176420</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2825,10 +2853,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C48">
-        <v>4094452</v>
+        <v>3160555</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2836,10 +2864,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C49">
-        <v>4017933</v>
+        <v>3135488</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2847,10 +2875,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>4007714</v>
+        <v>3089205</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -2858,10 +2886,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C51">
-        <v>4003559</v>
+        <v>3087825</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2869,10 +2897,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C52">
-        <v>3962431</v>
+        <v>3068419</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2880,10 +2908,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>3919064</v>
+        <v>2871198</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -2891,10 +2919,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="C54">
-        <v>3918479</v>
+        <v>2853030</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -2902,10 +2930,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C55">
-        <v>3863563</v>
+        <v>2851320</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -2913,10 +2941,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C56">
-        <v>3831240</v>
+        <v>2849850</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -2924,10 +2952,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C57">
-        <v>3799003</v>
+        <v>2766515</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2935,10 +2963,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C58">
-        <v>3747996</v>
+        <v>2722105</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -2946,10 +2974,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C59">
-        <v>3719900</v>
+        <v>2644035</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -2957,10 +2985,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>3296653</v>
+        <v>2640978</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2968,10 +2996,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="C61">
-        <v>3262380</v>
+        <v>2592515</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -2979,10 +3007,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C62">
-        <v>3075077</v>
+        <v>2356849</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -2990,10 +3018,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="C63">
-        <v>2890318</v>
+        <v>2342828</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3001,10 +3029,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C64">
-        <v>2775719</v>
+        <v>2321953</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3012,10 +3040,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>2775200</v>
+        <v>2315865</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3023,10 +3051,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C66">
-        <v>2766540</v>
+        <v>2315507</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -3034,10 +3062,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C67">
-        <v>2754992</v>
+        <v>2305405</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3045,10 +3073,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="C68">
-        <v>2736811</v>
+        <v>2217385</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3056,10 +3084,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C69">
-        <v>2735954</v>
+        <v>2192925</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3067,10 +3095,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C70">
-        <v>2349397</v>
+        <v>2158459</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -3078,10 +3106,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="C71">
-        <v>2264183</v>
+        <v>2075935</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -3089,10 +3117,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C72">
-        <v>2230810</v>
+        <v>2071567</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3100,10 +3128,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C73">
-        <v>2088029</v>
+        <v>2034260</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -3111,10 +3139,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="C74">
-        <v>2061656</v>
+        <v>2025230</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3122,10 +3150,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="C75">
-        <v>1946527</v>
+        <v>2024897</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3133,10 +3161,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="C76">
-        <v>1901010</v>
+        <v>1976858</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3144,10 +3172,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C77">
-        <v>1817914</v>
+        <v>1936160</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3155,10 +3183,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C78">
-        <v>1805208</v>
+        <v>1911772</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3166,10 +3194,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C79">
-        <v>1757457</v>
+        <v>1784180</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -3177,10 +3205,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C80">
-        <v>1672833</v>
+        <v>1768410</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -3188,10 +3216,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="C81">
-        <v>1554098</v>
+        <v>1649135</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -3199,10 +3227,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C82">
-        <v>1552907</v>
+        <v>1610065</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3210,10 +3238,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="C83">
-        <v>1472845</v>
+        <v>1544400</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3221,10 +3249,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="C84">
-        <v>1404180</v>
+        <v>1523733</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -3232,10 +3260,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>1269313</v>
+        <v>1437938</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3243,10 +3271,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>7</v>
       </c>
       <c r="C86">
-        <v>1120614</v>
+        <v>1152085</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3254,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C87">
-        <v>998281</v>
+        <v>1109645</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -3265,10 +3293,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="C88">
-        <v>938217</v>
+        <v>1014383</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3276,10 +3304,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C89">
-        <v>935911</v>
+        <v>959715</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3290,7 +3318,7 @@
         <v>6</v>
       </c>
       <c r="C90">
-        <v>774862</v>
+        <v>935625</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -3298,10 +3326,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="C91">
-        <v>620681</v>
+        <v>922725</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -3309,10 +3337,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="C92">
-        <v>455533</v>
+        <v>894740</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3320,10 +3348,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C93">
-        <v>285550</v>
+        <v>885310</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3331,10 +3359,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C94">
-        <v>254963</v>
+        <v>701850</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -3342,10 +3370,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C95">
-        <v>205800</v>
+        <v>692004</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -3353,10 +3381,21 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C96">
-        <v>196436</v>
+        <v>548600</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>100</v>
+      </c>
+      <c r="C97">
+        <v>531480</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24945C66-D800-432D-A518-3C3085EBA399}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
@@ -3376,13 +3415,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -3390,10 +3429,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C2">
-        <v>22543717</v>
+        <v>42986788</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3401,10 +3440,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>22201430</v>
+        <v>38451162</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3412,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>21048315</v>
+        <v>33500100</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3423,10 +3462,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>20030103</v>
+        <v>30396271</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -3434,10 +3473,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C6">
-        <v>20009077</v>
+        <v>28585390</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -3445,10 +3484,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C7">
-        <v>19995322</v>
+        <v>26684639</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -3456,10 +3495,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>19304683</v>
+        <v>26145694</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -3467,10 +3506,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9">
-        <v>18960154</v>
+        <v>25648467</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -3478,10 +3517,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>18607827</v>
+        <v>25323011</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -3489,10 +3528,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C11">
-        <v>18155735</v>
+        <v>25115705</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3500,10 +3539,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C12">
-        <v>17754429</v>
+        <v>24106900</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -3511,10 +3550,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="C13">
-        <v>16798323</v>
+        <v>23874606</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -3522,10 +3561,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C14">
-        <v>16522180</v>
+        <v>23418217</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -3533,10 +3572,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C15">
-        <v>16223844</v>
+        <v>22782331</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -3544,10 +3583,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C16">
-        <v>15906464</v>
+        <v>22700462</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -3555,10 +3594,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C17">
-        <v>15590506</v>
+        <v>22556083</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -3566,10 +3605,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>15413816</v>
+        <v>22343250</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -3577,10 +3616,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>15267872</v>
+        <v>21970466</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -3588,10 +3627,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C20">
-        <v>15138324</v>
+        <v>21965627</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -3599,10 +3638,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C21">
-        <v>14883117</v>
+        <v>21834920</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -3610,10 +3649,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C22">
-        <v>14255257</v>
+        <v>21719679</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -3621,10 +3660,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>14222534</v>
+        <v>21474747</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -3632,10 +3671,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="C24">
-        <v>14165047</v>
+        <v>21473942</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -3643,10 +3682,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="C25">
-        <v>14111194</v>
+        <v>20767769</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -3654,10 +3693,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C26">
-        <v>13986523</v>
+        <v>20276711</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -3665,10 +3704,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C27">
-        <v>13834039</v>
+        <v>20264949</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -3676,10 +3715,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C28">
-        <v>13526162</v>
+        <v>20205353</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -3687,10 +3726,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="C29">
-        <v>13471090</v>
+        <v>20175495</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -3698,10 +3737,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C30">
-        <v>13348723</v>
+        <v>20126375</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -3709,10 +3748,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="C31">
-        <v>13319643</v>
+        <v>19864472</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -3720,10 +3759,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C32">
-        <v>13225145</v>
+        <v>19357004</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -3731,10 +3770,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C33">
-        <v>13199144</v>
+        <v>19329210</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -3742,10 +3781,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="C34">
-        <v>12847984</v>
+        <v>19072642</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -3753,10 +3792,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="C35">
-        <v>12777474</v>
+        <v>19015237</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -3764,10 +3803,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C36">
-        <v>12753703</v>
+        <v>19012659</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -3775,10 +3814,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C37">
-        <v>12660260</v>
+        <v>18945602</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -3786,10 +3825,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="C38">
-        <v>12625044</v>
+        <v>18937484</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -3797,10 +3836,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="C39">
-        <v>12539577</v>
+        <v>18535206</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -3808,10 +3847,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C40">
-        <v>12529656</v>
+        <v>18234830</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -3819,10 +3858,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="C41">
-        <v>12461232</v>
+        <v>18183875</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -3830,10 +3869,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="C42">
-        <v>12424171</v>
+        <v>17966681</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -3841,10 +3880,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="C43">
-        <v>12379420</v>
+        <v>17785133</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -3852,10 +3891,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>12262715</v>
+        <v>17705696</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -3863,10 +3902,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>12211506</v>
+        <v>17590063</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -3874,10 +3913,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C46">
-        <v>12202433</v>
+        <v>17540105</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -3885,10 +3924,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="C47">
-        <v>12180355</v>
+        <v>17505236</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -3896,10 +3935,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C48">
-        <v>12083184</v>
+        <v>17439878</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -3907,10 +3946,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C49">
-        <v>12030539</v>
+        <v>17282972</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -3918,10 +3957,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>11814326</v>
+        <v>17113163</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -3929,10 +3968,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>11647735</v>
+        <v>17038910</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -3940,10 +3979,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C52">
-        <v>11588003</v>
+        <v>16866712</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -3951,10 +3990,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C53">
-        <v>11417454</v>
+        <v>16865076</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -3962,10 +4001,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C54">
-        <v>11377581</v>
+        <v>16837866</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -3973,10 +4012,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C55">
-        <v>11312667</v>
+        <v>16613357</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -3984,10 +4023,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="C56">
-        <v>11242399</v>
+        <v>16597381</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -3995,10 +4034,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57">
-        <v>11164215</v>
+        <v>16435246</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -4006,10 +4045,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C58">
-        <v>11018161</v>
+        <v>16286110</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -4017,10 +4056,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C59">
-        <v>10948170</v>
+        <v>16283751</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -4028,10 +4067,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C60">
-        <v>10940573</v>
+        <v>16268725</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -4039,10 +4078,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="C61">
-        <v>10919112</v>
+        <v>16213659</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -4050,10 +4089,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>10802273</v>
+        <v>16143559</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -4061,10 +4100,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C63">
-        <v>10533113</v>
+        <v>16116026</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -4072,10 +4111,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C64">
-        <v>10512329</v>
+        <v>16054780</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -4083,10 +4122,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C65">
-        <v>10356991</v>
+        <v>16019009</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -4094,10 +4133,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>10356025</v>
+        <v>15728355</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -4105,10 +4144,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>10334151</v>
+        <v>15257020</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -4116,10 +4155,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C68">
-        <v>10255914</v>
+        <v>15213690</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -4127,10 +4166,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C69">
-        <v>9737463</v>
+        <v>15208939</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -4138,10 +4177,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C70">
-        <v>9401283</v>
+        <v>15152164</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -4149,10 +4188,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>9314496</v>
+        <v>14981242</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -4160,10 +4199,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>9281024</v>
+        <v>14956578</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -4171,10 +4210,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C73">
-        <v>9083791</v>
+        <v>14562244</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -4182,10 +4221,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C74">
-        <v>9074995</v>
+        <v>14491010</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -4193,10 +4232,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C75">
-        <v>8857105</v>
+        <v>14295737</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -4204,10 +4243,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C76">
-        <v>8798022</v>
+        <v>14151745</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -4215,10 +4254,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C77">
-        <v>8767566</v>
+        <v>13936106</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -4226,10 +4265,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="C78">
-        <v>8699159</v>
+        <v>13586729</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -4237,10 +4276,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C79">
-        <v>8681257</v>
+        <v>13553595</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -4248,10 +4287,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C80">
-        <v>8652496</v>
+        <v>13281809</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -4259,10 +4298,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C81">
-        <v>8638981</v>
+        <v>12940061</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -4270,10 +4309,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C82">
-        <v>8593188</v>
+        <v>12712960</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -4281,10 +4320,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C83">
-        <v>8464203</v>
+        <v>12440467</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -4292,10 +4331,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C84">
-        <v>8392844</v>
+        <v>12371637</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -4303,10 +4342,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C85">
-        <v>8305300</v>
+        <v>12279732</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -4314,10 +4353,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C86">
-        <v>8201013</v>
+        <v>12183896</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -4325,10 +4364,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C87">
-        <v>8073053</v>
+        <v>12155206</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -4336,10 +4375,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="C88">
-        <v>7990739</v>
+        <v>11654822</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -4347,10 +4386,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C89">
-        <v>7876160</v>
+        <v>11569806</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -4358,10 +4397,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C90">
-        <v>7555440</v>
+        <v>11299986</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -4369,10 +4408,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>7522797</v>
+        <v>11280129</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -4380,10 +4419,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C92">
-        <v>6670513</v>
+        <v>11078297</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -4391,10 +4430,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="C93">
-        <v>6460817</v>
+        <v>10825922</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -4402,10 +4441,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C94">
-        <v>6254387</v>
+        <v>10738045</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -4413,10 +4452,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C95">
-        <v>6167119</v>
+        <v>10641846</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -4424,10 +4463,65 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="C96">
-        <v>6003695</v>
+        <v>10522529</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>80</v>
+      </c>
+      <c r="C97">
+        <v>9983003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>94</v>
+      </c>
+      <c r="C98">
+        <v>5997750</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>71</v>
+      </c>
+      <c r="C99">
+        <v>5821797</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100">
+        <v>2029812</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>92</v>
+      </c>
+      <c r="C101">
+        <v>1595038</v>
       </c>
     </row>
   </sheetData>
@@ -4437,7 +4531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91A2156-7B37-4F0F-A286-78AC594703A1}">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
@@ -4450,1635 +4544,1633 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>98</v>
+        <v>56</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="3">
-        <f>VLOOKUP(A2,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3918479</v>
-      </c>
-      <c r="C2" s="3">
-        <f>VLOOKUP(A2,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>15138324</v>
+        <v>61</v>
+      </c>
+      <c r="B2">
+        <f>VLOOKUP(A2,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>15702055</v>
+      </c>
+      <c r="C2">
+        <f>VLOOKUP(A2,power!$B$2:$C$101,2,FALSE)</f>
+        <v>42986788</v>
       </c>
       <c r="E2" s="5">
         <f>PERCENTRANK(B$2:B$96,B2)</f>
-        <v>0.44600000000000001</v>
+        <v>1</v>
       </c>
       <c r="F2" s="5">
         <f>PERCENTRANK(C$2:C$96,C2)</f>
-        <v>0.80800000000000005</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3">
         <f t="shared" ref="H2:H66" si="0">+E2*F2*10000</f>
-        <v>3603.6800000000003</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="3">
-        <f>VLOOKUP(A3,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6966055</v>
-      </c>
-      <c r="C3" s="3">
-        <f>VLOOKUP(A3,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12083184</v>
+        <v>64</v>
+      </c>
+      <c r="B3">
+        <f>VLOOKUP(A3,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5794630</v>
+      </c>
+      <c r="C3">
+        <f>VLOOKUP(A3,power!$B$2:$C$101,2,FALSE)</f>
+        <v>38451162</v>
       </c>
       <c r="E3" s="5">
         <f t="shared" ref="E3:E66" si="1">PERCENTRANK(B$2:B$96,B3)</f>
-        <v>0.91400000000000003</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" ref="F3:H66" si="2">PERCENTRANK(C$2:C$96,C3)</f>
-        <v>0.51</v>
+        <f t="shared" ref="F3:F66" si="2">PERCENTRANK(C$2:C$96,C3)</f>
+        <v>0.98899999999999999</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="0"/>
-        <v>4661.3999999999996</v>
+        <v>8940.56</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="3">
-        <f>VLOOKUP(A4,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4448558</v>
-      </c>
-      <c r="C4" s="3">
-        <f>VLOOKUP(A4,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8201013</v>
+        <v>67</v>
+      </c>
+      <c r="B4">
+        <f>VLOOKUP(A4,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4737953</v>
+      </c>
+      <c r="C4">
+        <f>VLOOKUP(A4,power!$B$2:$C$101,2,FALSE)</f>
+        <v>33500100</v>
       </c>
       <c r="E4" s="5">
         <f t="shared" si="1"/>
-        <v>0.59499999999999997</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" si="2"/>
-        <v>0.106</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>630.70000000000005</v>
+        <v>7902.2400000000007</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <f>VLOOKUP(A5,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>455533</v>
-      </c>
-      <c r="C5" s="3">
-        <f>VLOOKUP(A5,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11814326</v>
+        <v>50</v>
+      </c>
+      <c r="B5">
+        <f>VLOOKUP(A5,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8401268</v>
+      </c>
+      <c r="C5">
+        <f>VLOOKUP(A5,power!$B$2:$C$101,2,FALSE)</f>
+        <v>30396271</v>
       </c>
       <c r="E5" s="5">
         <f t="shared" si="1"/>
-        <v>4.2000000000000003E-2</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" si="2"/>
-        <v>0.48899999999999999</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>205.38</v>
+        <v>9263.76</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3">
-        <f>VLOOKUP(A6,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1404180</v>
-      </c>
-      <c r="C6" s="3">
-        <f>VLOOKUP(A6,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13319643</v>
+        <v>70</v>
+      </c>
+      <c r="B6">
+        <f>VLOOKUP(A6,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4627335</v>
+      </c>
+      <c r="C6">
+        <f>VLOOKUP(A6,power!$B$2:$C$101,2,FALSE)</f>
+        <v>28585390</v>
       </c>
       <c r="E6" s="5">
         <f t="shared" si="1"/>
-        <v>0.127</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" si="2"/>
-        <v>0.69099999999999995</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>877.56999999999982</v>
+        <v>7426.32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3">
-        <f>VLOOKUP(A7,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2061656</v>
-      </c>
-      <c r="C7" s="3">
-        <f>VLOOKUP(A7,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8699159</v>
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <f>VLOOKUP(A7,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3641493</v>
+      </c>
+      <c r="C7">
+        <f>VLOOKUP(A7,power!$B$2:$C$101,2,FALSE)</f>
+        <v>26684639</v>
       </c>
       <c r="E7" s="5">
         <f t="shared" si="1"/>
-        <v>0.23400000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="2"/>
-        <v>0.191</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>446.94000000000005</v>
+        <v>5931.4199999999992</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="3">
-        <f>VLOOKUP(A8,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2264183</v>
-      </c>
-      <c r="C8" s="3">
-        <f>VLOOKUP(A8,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10919112</v>
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <f>VLOOKUP(A8,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2644035</v>
+      </c>
+      <c r="C8">
+        <f>VLOOKUP(A8,power!$B$2:$C$101,2,FALSE)</f>
+        <v>26145694</v>
       </c>
       <c r="E8" s="5">
         <f t="shared" si="1"/>
-        <v>0.26500000000000001</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="2"/>
-        <v>0.372</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>985.8</v>
+        <v>3875.04</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="3">
-        <f>VLOOKUP(A9,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4007714</v>
-      </c>
-      <c r="C9" s="3">
-        <f>VLOOKUP(A9,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>15906464</v>
+        <v>75</v>
+      </c>
+      <c r="B9">
+        <f>VLOOKUP(A9,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3491725</v>
+      </c>
+      <c r="C9">
+        <f>VLOOKUP(A9,power!$B$2:$C$101,2,FALSE)</f>
+        <v>25648467</v>
       </c>
       <c r="E9" s="5">
         <f t="shared" si="1"/>
-        <v>0.48899999999999999</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="2"/>
-        <v>0.85099999999999998</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>4161.3899999999994</v>
+        <v>5605.5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3">
-        <f>VLOOKUP(A10,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2754992</v>
-      </c>
-      <c r="C10" s="3">
-        <f>VLOOKUP(A10,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>6670513</v>
+        <v>62</v>
+      </c>
+      <c r="B10">
+        <f>VLOOKUP(A10,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8611927</v>
+      </c>
+      <c r="C10">
+        <f>VLOOKUP(A10,power!$B$2:$C$101,2,FALSE)</f>
+        <v>25323011</v>
       </c>
       <c r="E10" s="5">
         <f t="shared" si="1"/>
-        <v>0.308</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="2"/>
-        <v>4.2000000000000003E-2</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="0"/>
-        <v>129.36000000000001</v>
+        <v>8847.52</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="3">
-        <f>VLOOKUP(A11,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>8931884</v>
-      </c>
-      <c r="C11" s="3">
-        <f>VLOOKUP(A11,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13526162</v>
+        <v>101</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>VLOOKUP(A11,power!$B$2:$C$101,2,FALSE)</f>
+        <v>25115705</v>
       </c>
       <c r="E11" s="5">
         <f t="shared" si="1"/>
-        <v>0.93600000000000005</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5">
         <f t="shared" si="2"/>
-        <v>0.72299999999999998</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="0"/>
-        <v>6767.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="3">
-        <f>VLOOKUP(A12,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6146150</v>
-      </c>
-      <c r="C12" s="3">
-        <f>VLOOKUP(A12,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10255914</v>
+        <v>40</v>
+      </c>
+      <c r="B12">
+        <f>VLOOKUP(A12,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2853030</v>
+      </c>
+      <c r="C12">
+        <f>VLOOKUP(A12,power!$B$2:$C$101,2,FALSE)</f>
+        <v>24106900</v>
       </c>
       <c r="E12" s="5">
         <f t="shared" si="1"/>
-        <v>0.82899999999999996</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="F12" s="5">
         <f t="shared" si="2"/>
-        <v>0.29699999999999999</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="0"/>
-        <v>2462.1299999999997</v>
+        <v>4081.0100000000007</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="3">
-        <f>VLOOKUP(A13,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4935573</v>
-      </c>
-      <c r="C13" s="3">
-        <f>VLOOKUP(A13,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10533113</v>
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <f>VLOOKUP(A13,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6070432</v>
+      </c>
+      <c r="C13">
+        <f>VLOOKUP(A13,power!$B$2:$C$101,2,FALSE)</f>
+        <v>23874606</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="1"/>
-        <v>0.65900000000000003</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="2"/>
-        <v>0.35099999999999998</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
-        <v>2313.0899999999997</v>
+        <v>8158.5000000000009</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="3">
-        <f>VLOOKUP(A14,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>285550</v>
-      </c>
-      <c r="C14" s="3">
-        <f>VLOOKUP(A14,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>6003695</v>
+        <v>78</v>
+      </c>
+      <c r="B14">
+        <f>VLOOKUP(A14,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3087825</v>
+      </c>
+      <c r="C14">
+        <f>VLOOKUP(A14,power!$B$2:$C$101,2,FALSE)</f>
+        <v>23418217</v>
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>3.1E-2</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.872</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4264.08</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="3">
-        <f>VLOOKUP(A15,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>205800</v>
-      </c>
-      <c r="C15" s="3">
-        <f>VLOOKUP(A15,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>22201430</v>
+        <v>33</v>
+      </c>
+      <c r="B15">
+        <f>VLOOKUP(A15,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3810506</v>
+      </c>
+      <c r="C15">
+        <f>VLOOKUP(A15,power!$B$2:$C$101,2,FALSE)</f>
+        <v>22782331</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>0.01</v>
+        <v>0.67</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="2"/>
-        <v>0.98899999999999999</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>98.899999999999991</v>
+        <v>5768.7</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" s="3">
-        <f>VLOOKUP(A16,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6797175</v>
-      </c>
-      <c r="C16" s="3">
-        <f>VLOOKUP(A16,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12529656</v>
+        <v>26</v>
+      </c>
+      <c r="B16">
+        <f>VLOOKUP(A16,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3826667</v>
+      </c>
+      <c r="C16">
+        <f>VLOOKUP(A16,power!$B$2:$C$101,2,FALSE)</f>
+        <v>22700462</v>
       </c>
       <c r="E16" s="5">
         <f t="shared" si="1"/>
-        <v>0.89300000000000002</v>
+        <v>0.68</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="2"/>
-        <v>0.59499999999999997</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="0"/>
-        <v>5313.35</v>
+        <v>5786.7999999999993</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="3">
-        <f>VLOOKUP(A17,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4869154</v>
-      </c>
-      <c r="C17" s="3">
-        <f>VLOOKUP(A17,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13834039</v>
+        <v>76</v>
+      </c>
+      <c r="B17">
+        <f>VLOOKUP(A17,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3363330</v>
+      </c>
+      <c r="C17">
+        <f>VLOOKUP(A17,power!$B$2:$C$101,2,FALSE)</f>
+        <v>22556083</v>
       </c>
       <c r="E17" s="5">
         <f t="shared" si="1"/>
-        <v>0.64800000000000002</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="F17" s="5">
         <f t="shared" si="2"/>
-        <v>0.73399999999999999</v>
+        <v>0.84</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
-        <v>4756.32</v>
+        <v>4821.5999999999995</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="3">
-        <f>VLOOKUP(A18,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6143355</v>
-      </c>
-      <c r="C18" s="3">
-        <f>VLOOKUP(A18,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8464203</v>
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <f>VLOOKUP(A18,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4546105</v>
+      </c>
+      <c r="C18">
+        <f>VLOOKUP(A18,power!$B$2:$C$101,2,FALSE)</f>
+        <v>22343250</v>
       </c>
       <c r="E18" s="5">
         <f t="shared" si="1"/>
-        <v>0.81899999999999995</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="F18" s="5">
         <f t="shared" si="2"/>
-        <v>0.13800000000000001</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
-        <v>1130.22</v>
+        <v>6341.85</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="3">
-        <f>VLOOKUP(A19,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4017933</v>
-      </c>
-      <c r="C19" s="3">
-        <f>VLOOKUP(A19,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>7876160</v>
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <f>VLOOKUP(A19,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5499645</v>
+      </c>
+      <c r="C19">
+        <f>VLOOKUP(A19,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21970466</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>7.3999999999999996E-2</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
-        <v>370</v>
+        <v>7223.579999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="3">
-        <f>VLOOKUP(A20,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6013376</v>
-      </c>
-      <c r="C20" s="3">
-        <f>VLOOKUP(A20,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13471090</v>
+        <v>65</v>
+      </c>
+      <c r="B20">
+        <f>VLOOKUP(A20,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4792980</v>
+      </c>
+      <c r="C20">
+        <f>VLOOKUP(A20,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21965627</v>
       </c>
       <c r="E20" s="5">
         <f t="shared" si="1"/>
-        <v>0.78700000000000003</v>
+        <v>0.84</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" si="2"/>
-        <v>0.71199999999999997</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="0"/>
-        <v>5603.44</v>
+        <v>6787.2</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3">
-        <f>VLOOKUP(A21,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1554098</v>
-      </c>
-      <c r="C21" s="3">
-        <f>VLOOKUP(A21,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>7990739</v>
+        <v>49</v>
+      </c>
+      <c r="B21">
+        <f>VLOOKUP(A21,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12214971</v>
+      </c>
+      <c r="C21">
+        <f>VLOOKUP(A21,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21834920</v>
       </c>
       <c r="E21" s="5">
         <f t="shared" si="1"/>
-        <v>0.159</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="F21" s="5">
         <f t="shared" si="2"/>
-        <v>8.5000000000000006E-2</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>135.15</v>
+        <v>7882.3300000000008</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="3">
-        <f>VLOOKUP(A22,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1120614</v>
-      </c>
-      <c r="C22" s="3">
-        <f>VLOOKUP(A22,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10356025</v>
+        <v>52</v>
+      </c>
+      <c r="B22">
+        <f>VLOOKUP(A22,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3176420</v>
+      </c>
+      <c r="C22">
+        <f>VLOOKUP(A22,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21719679</v>
       </c>
       <c r="E22" s="5">
         <f t="shared" si="1"/>
-        <v>0.106</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="F22" s="5">
         <f t="shared" si="2"/>
-        <v>0.31900000000000001</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="0"/>
-        <v>338.14</v>
+        <v>4178.97</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="3">
-        <f>VLOOKUP(A23,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>12245364</v>
-      </c>
-      <c r="C23" s="3">
-        <f>VLOOKUP(A23,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>15267872</v>
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <f>VLOOKUP(A23,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2158459</v>
+      </c>
+      <c r="C23">
+        <f>VLOOKUP(A23,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21474747</v>
       </c>
       <c r="E23" s="5">
         <f t="shared" si="1"/>
-        <v>0.98899999999999999</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="F23" s="5">
         <f t="shared" si="2"/>
-        <v>0.81899999999999995</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="0"/>
-        <v>8099.9099999999989</v>
+        <v>2304.7199999999998</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="3">
-        <f>VLOOKUP(A24,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3719900</v>
-      </c>
-      <c r="C24" s="3">
-        <f>VLOOKUP(A24,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9074995</v>
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <f>VLOOKUP(A24,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2356849</v>
+      </c>
+      <c r="C24">
+        <f>VLOOKUP(A24,power!$B$2:$C$101,2,FALSE)</f>
+        <v>21473942</v>
       </c>
       <c r="E24" s="5">
         <f t="shared" si="1"/>
-        <v>0.39300000000000002</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="F24" s="5">
         <f t="shared" si="2"/>
-        <v>0.23400000000000001</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
-        <v>919.62000000000012</v>
+        <v>2922.2999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="3">
-        <f>VLOOKUP(A25,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4337158</v>
-      </c>
-      <c r="C25" s="3">
-        <f>VLOOKUP(A25,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10512329</v>
+        <v>39</v>
+      </c>
+      <c r="B25">
+        <f>VLOOKUP(A25,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4150745</v>
+      </c>
+      <c r="C25">
+        <f>VLOOKUP(A25,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20767769</v>
       </c>
       <c r="E25" s="5">
         <f t="shared" si="1"/>
-        <v>0.56299999999999994</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="F25" s="5">
         <f t="shared" si="2"/>
-        <v>0.34</v>
+        <v>0.755</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
-        <v>1914.2</v>
+        <v>5617.2</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3">
-        <f>VLOOKUP(A26,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4404572</v>
-      </c>
-      <c r="C26" s="3">
-        <f>VLOOKUP(A26,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>7522797</v>
+        <v>19</v>
+      </c>
+      <c r="B26">
+        <f>VLOOKUP(A26,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4992116</v>
+      </c>
+      <c r="C26">
+        <f>VLOOKUP(A26,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20276711</v>
       </c>
       <c r="E26" s="5">
         <f t="shared" si="1"/>
-        <v>0.57399999999999995</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="F26" s="5">
         <f t="shared" si="2"/>
-        <v>5.2999999999999999E-2</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
-        <v>304.21999999999997</v>
+        <v>6405.8399999999992</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="3">
-        <f>VLOOKUP(A27,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6115380</v>
-      </c>
-      <c r="C27" s="3">
-        <f>VLOOKUP(A27,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>19995322</v>
+        <v>34</v>
+      </c>
+      <c r="B27">
+        <f>VLOOKUP(A27,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6311179</v>
+      </c>
+      <c r="C27">
+        <f>VLOOKUP(A27,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20264949</v>
       </c>
       <c r="E27" s="5">
         <f t="shared" si="1"/>
-        <v>0.80800000000000005</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="F27" s="5">
         <f t="shared" si="2"/>
-        <v>0.94599999999999995</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>7643.68</v>
+        <v>6943.6399999999994</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="3">
-        <f>VLOOKUP(A28,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>254963</v>
-      </c>
-      <c r="C28" s="3">
-        <f>VLOOKUP(A28,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11647735</v>
+        <v>43</v>
+      </c>
+      <c r="B28">
+        <f>VLOOKUP(A28,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9119649</v>
+      </c>
+      <c r="C28">
+        <f>VLOOKUP(A28,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20205353</v>
       </c>
       <c r="E28" s="5">
         <f t="shared" si="1"/>
-        <v>2.1000000000000001E-2</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="F28" s="5">
         <f t="shared" si="2"/>
-        <v>0.47799999999999998</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
-        <v>100.38</v>
+        <v>7070.94</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>75</v>
-      </c>
-      <c r="B29" s="3">
-        <f>VLOOKUP(A29,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6387590</v>
-      </c>
-      <c r="C29" s="3">
-        <f>VLOOKUP(A29,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8767566</v>
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <f>VLOOKUP(A29,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2592515</v>
+      </c>
+      <c r="C29">
+        <f>VLOOKUP(A29,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20175495</v>
       </c>
       <c r="E29" s="5">
         <f t="shared" si="1"/>
-        <v>0.85099999999999998</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="F29" s="5">
         <f t="shared" si="2"/>
-        <v>0.20200000000000001</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
-        <v>1719.02</v>
+        <v>2798.1600000000003</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="3">
-        <f>VLOOKUP(A30,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2088029</v>
-      </c>
-      <c r="C30" s="3">
-        <f>VLOOKUP(A30,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12379420</v>
+        <v>84</v>
+      </c>
+      <c r="B30">
+        <f>VLOOKUP(A30,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2192925</v>
+      </c>
+      <c r="C30">
+        <f>VLOOKUP(A30,power!$B$2:$C$101,2,FALSE)</f>
+        <v>20126375</v>
       </c>
       <c r="E30" s="5">
         <f t="shared" si="1"/>
-        <v>0.24399999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="F30" s="5">
         <f t="shared" si="2"/>
-        <v>0.56299999999999994</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
-        <v>1373.72</v>
+        <v>2162.16</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="3">
-        <f>VLOOKUP(A31,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4094452</v>
-      </c>
-      <c r="C31" s="3">
-        <f>VLOOKUP(A31,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12030539</v>
+        <v>69</v>
+      </c>
+      <c r="B31">
+        <f>VLOOKUP(A31,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4647868</v>
+      </c>
+      <c r="C31">
+        <f>VLOOKUP(A31,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19864472</v>
       </c>
       <c r="E31" s="5">
         <f t="shared" si="1"/>
-        <v>0.51</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="F31" s="5">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="0"/>
-        <v>2550</v>
+        <v>5438.17</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="3">
-        <f>VLOOKUP(A32,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5553839</v>
-      </c>
-      <c r="C32" s="3">
-        <f>VLOOKUP(A32,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13199144</v>
+        <v>102</v>
+      </c>
+      <c r="B32">
+        <f>VLOOKUP(A32,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2342828</v>
+      </c>
+      <c r="C32">
+        <f>VLOOKUP(A32,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19357004</v>
       </c>
       <c r="E32" s="5">
         <f t="shared" si="1"/>
-        <v>0.71199999999999997</v>
+        <v>0.372</v>
       </c>
       <c r="F32" s="5">
         <f t="shared" si="2"/>
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="0"/>
-        <v>4770.4000000000005</v>
+        <v>2529.6000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3">
-        <f>VLOOKUP(A33,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4003559</v>
-      </c>
-      <c r="C33" s="3">
-        <f>VLOOKUP(A33,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>16223844</v>
+        <v>30</v>
+      </c>
+      <c r="B33">
+        <f>VLOOKUP(A33,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1768410</v>
+      </c>
+      <c r="C33">
+        <f>VLOOKUP(A33,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19329210</v>
       </c>
       <c r="E33" s="5">
         <f t="shared" si="1"/>
-        <v>0.47799999999999998</v>
+        <v>0.191</v>
       </c>
       <c r="F33" s="5">
         <f t="shared" si="2"/>
-        <v>0.86099999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="0"/>
-        <v>4115.58</v>
+        <v>1279.7</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="3">
-        <f>VLOOKUP(A34,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2230810</v>
-      </c>
-      <c r="C34" s="3">
-        <f>VLOOKUP(A34,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12777474</v>
+        <v>42</v>
+      </c>
+      <c r="B34">
+        <f>VLOOKUP(A34,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3509465</v>
+      </c>
+      <c r="C34">
+        <f>VLOOKUP(A34,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19072642</v>
       </c>
       <c r="E34" s="5">
         <f t="shared" si="1"/>
-        <v>0.255</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="F34" s="5">
         <f t="shared" si="2"/>
-        <v>0.64800000000000002</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" si="0"/>
-        <v>1652.4</v>
+        <v>4066.0299999999997</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="3">
-        <f>VLOOKUP(A35,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>196436</v>
-      </c>
-      <c r="C35" s="3">
-        <f>VLOOKUP(A35,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9281024</v>
+        <v>73</v>
+      </c>
+      <c r="B35">
+        <f>VLOOKUP(A35,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4011219</v>
+      </c>
+      <c r="C35">
+        <f>VLOOKUP(A35,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19015237</v>
       </c>
       <c r="E35" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="2"/>
-        <v>0.255</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4548.96</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="3">
-        <f>VLOOKUP(A36,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5638493</v>
-      </c>
-      <c r="C36" s="3">
-        <f>VLOOKUP(A36,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12202433</v>
+        <v>68</v>
+      </c>
+      <c r="B36">
+        <f>VLOOKUP(A36,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4714228</v>
+      </c>
+      <c r="C36">
+        <f>VLOOKUP(A36,power!$B$2:$C$101,2,FALSE)</f>
+        <v>19012659</v>
       </c>
       <c r="E36" s="5">
         <f t="shared" si="1"/>
-        <v>0.73399999999999999</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="F36" s="5">
         <f t="shared" si="2"/>
-        <v>0.53100000000000003</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="0"/>
-        <v>3897.54</v>
+        <v>5084.8599999999997</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="3">
-        <f>VLOOKUP(A37,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6733809</v>
-      </c>
-      <c r="C37" s="3">
-        <f>VLOOKUP(A37,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>17754429</v>
+        <v>46</v>
+      </c>
+      <c r="B37">
+        <f>VLOOKUP(A37,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3307184</v>
+      </c>
+      <c r="C37">
+        <f>VLOOKUP(A37,power!$B$2:$C$101,2,FALSE)</f>
+        <v>18945602</v>
       </c>
       <c r="E37" s="5">
         <f t="shared" si="1"/>
-        <v>0.88200000000000001</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="F37" s="5">
         <f t="shared" si="2"/>
-        <v>0.89300000000000002</v>
+        <v>0.627</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="0"/>
-        <v>7876.26</v>
+        <v>3530.0099999999998</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="3">
-        <f>VLOOKUP(A38,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>11634735</v>
-      </c>
-      <c r="C38" s="3">
-        <f>VLOOKUP(A38,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12753703</v>
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <f>VLOOKUP(A38,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1437938</v>
+      </c>
+      <c r="C38">
+        <f>VLOOKUP(A38,power!$B$2:$C$101,2,FALSE)</f>
+        <v>18937484</v>
       </c>
       <c r="E38" s="5">
         <f t="shared" si="1"/>
-        <v>0.97799999999999998</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="F38" s="5">
         <f t="shared" si="2"/>
-        <v>0.63800000000000001</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="0"/>
-        <v>6239.6399999999994</v>
+        <v>913.16</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="3">
-        <f>VLOOKUP(A39,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3075077</v>
-      </c>
-      <c r="C39" s="3">
-        <f>VLOOKUP(A39,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8652496</v>
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <f>VLOOKUP(A39,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1911772</v>
+      </c>
+      <c r="C39">
+        <f>VLOOKUP(A39,power!$B$2:$C$101,2,FALSE)</f>
+        <v>18535206</v>
       </c>
       <c r="E39" s="5">
         <f t="shared" si="1"/>
-        <v>0.36099999999999999</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="F39" s="5">
         <f t="shared" si="2"/>
-        <v>0.17</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="0"/>
-        <v>613.70000000000005</v>
+        <v>1284.72</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="3">
-        <f>VLOOKUP(A40,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>8603326</v>
-      </c>
-      <c r="C40" s="3">
-        <f>VLOOKUP(A40,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>20009077</v>
+        <v>87</v>
+      </c>
+      <c r="B40">
+        <f>VLOOKUP(A40,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2024897</v>
+      </c>
+      <c r="C40">
+        <f>VLOOKUP(A40,power!$B$2:$C$101,2,FALSE)</f>
+        <v>18234830</v>
       </c>
       <c r="E40" s="5">
         <f t="shared" si="1"/>
-        <v>0.92500000000000004</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="F40" s="5">
         <f t="shared" si="2"/>
-        <v>0.95699999999999996</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="0"/>
-        <v>8852.25</v>
+        <v>1451.8</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="3">
-        <f>VLOOKUP(A41,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>9314206</v>
-      </c>
-      <c r="C41" s="3">
-        <f>VLOOKUP(A41,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>19304683</v>
+        <v>103</v>
+      </c>
+      <c r="B41">
+        <f>VLOOKUP(A41,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3804815</v>
+      </c>
+      <c r="C41">
+        <f>VLOOKUP(A41,power!$B$2:$C$101,2,FALSE)</f>
+        <v>18183875</v>
       </c>
       <c r="E41" s="5">
         <f t="shared" si="1"/>
-        <v>0.95699999999999996</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="F41" s="5">
         <f t="shared" si="2"/>
-        <v>0.93600000000000005</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="0"/>
-        <v>8957.52</v>
+        <v>3855.15</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="3">
-        <f>VLOOKUP(A42,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4523804</v>
-      </c>
-      <c r="C42" s="3">
-        <f>VLOOKUP(A42,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11312667</v>
+        <v>81</v>
+      </c>
+      <c r="B42">
+        <f>VLOOKUP(A42,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2722105</v>
+      </c>
+      <c r="C42">
+        <f>VLOOKUP(A42,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17966681</v>
       </c>
       <c r="E42" s="5">
         <f t="shared" si="1"/>
-        <v>0.60599999999999998</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="F42" s="5">
         <f t="shared" si="2"/>
-        <v>0.436</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="0"/>
-        <v>2642.16</v>
+        <v>2439.4999999999995</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="3">
-        <f>VLOOKUP(A43,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1901010</v>
-      </c>
-      <c r="C43" s="3">
-        <f>VLOOKUP(A43,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12424171</v>
+        <v>104</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <f>VLOOKUP(A43,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17785133</v>
       </c>
       <c r="E43" s="5">
         <f t="shared" si="1"/>
-        <v>0.21199999999999999</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5">
         <f t="shared" si="2"/>
-        <v>0.57399999999999995</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="0"/>
-        <v>1216.8799999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="3">
-        <f>VLOOKUP(A44,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2890318</v>
-      </c>
-      <c r="C44" s="3">
-        <f>VLOOKUP(A44,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12660260</v>
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <f>VLOOKUP(A44,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2034260</v>
+      </c>
+      <c r="C44">
+        <f>VLOOKUP(A44,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17705696</v>
       </c>
       <c r="E44" s="5">
         <f t="shared" si="1"/>
-        <v>0.35099999999999998</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="F44" s="5">
         <f t="shared" si="2"/>
-        <v>0.627</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="0"/>
-        <v>2200.77</v>
+        <v>1465.45</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="3">
-        <f>VLOOKUP(A45,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1269313</v>
-      </c>
-      <c r="C45" s="3">
-        <f>VLOOKUP(A45,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11588003</v>
+        <v>17</v>
+      </c>
+      <c r="B45">
+        <f>VLOOKUP(A45,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2851320</v>
+      </c>
+      <c r="C45">
+        <f>VLOOKUP(A45,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17590063</v>
       </c>
       <c r="E45" s="5">
         <f t="shared" si="1"/>
-        <v>0.11700000000000001</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="F45" s="5">
         <f t="shared" si="2"/>
-        <v>0.46800000000000003</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="0"/>
-        <v>547.56000000000006</v>
+        <v>2417.3200000000002</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="3">
-        <f>VLOOKUP(A46,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4995656</v>
-      </c>
-      <c r="C46" s="3">
-        <f>VLOOKUP(A46,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11242399</v>
+        <v>100</v>
+      </c>
+      <c r="B46">
+        <f>VLOOKUP(A46,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>531480</v>
+      </c>
+      <c r="C46">
+        <f>VLOOKUP(A46,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17540105</v>
       </c>
       <c r="E46" s="5">
         <f t="shared" si="1"/>
-        <v>0.67</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="F46" s="5">
         <f t="shared" si="2"/>
-        <v>0.42499999999999999</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="0"/>
-        <v>2847.5</v>
+        <v>223.02</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="3">
-        <f>VLOOKUP(A47,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1805208</v>
-      </c>
-      <c r="C47" s="3">
-        <f>VLOOKUP(A47,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>6254387</v>
+        <v>96</v>
+      </c>
+      <c r="B47">
+        <f>VLOOKUP(A47,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>894740</v>
+      </c>
+      <c r="C47">
+        <f>VLOOKUP(A47,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17505236</v>
       </c>
       <c r="E47" s="5">
         <f t="shared" si="1"/>
-        <v>0.191</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="F47" s="5">
         <f t="shared" si="2"/>
-        <v>2.1000000000000001E-2</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="0"/>
-        <v>40.110000000000007</v>
+        <v>442.85</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" s="3">
-        <f>VLOOKUP(A48,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3296653</v>
-      </c>
-      <c r="C48" s="3">
-        <f>VLOOKUP(A48,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10948170</v>
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <f>VLOOKUP(A48,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5827820</v>
+      </c>
+      <c r="C48">
+        <f>VLOOKUP(A48,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17439878</v>
       </c>
       <c r="E48" s="5">
         <f t="shared" si="1"/>
-        <v>0.38200000000000001</v>
+        <v>0.91400000000000003</v>
       </c>
       <c r="F48" s="5">
         <f t="shared" si="2"/>
-        <v>0.39300000000000002</v>
+        <v>0.51</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="0"/>
-        <v>1501.26</v>
+        <v>4661.3999999999996</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="3">
-        <f>VLOOKUP(A49,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>998281</v>
-      </c>
-      <c r="C49" s="3">
-        <f>VLOOKUP(A49,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>6167119</v>
+        <v>31</v>
+      </c>
+      <c r="B49">
+        <f>VLOOKUP(A49,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3135488</v>
+      </c>
+      <c r="C49">
+        <f>VLOOKUP(A49,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17282972</v>
       </c>
       <c r="E49" s="5">
         <f t="shared" si="1"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.51</v>
       </c>
       <c r="F49" s="5">
         <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="3">
-        <f>VLOOKUP(A50,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1817914</v>
-      </c>
-      <c r="C50" s="3">
-        <f>VLOOKUP(A50,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>14255257</v>
+        <v>28</v>
+      </c>
+      <c r="B50">
+        <f>VLOOKUP(A50,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4109114</v>
+      </c>
+      <c r="C50">
+        <f>VLOOKUP(A50,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17113163</v>
       </c>
       <c r="E50" s="5">
         <f t="shared" si="1"/>
-        <v>0.20200000000000001</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="F50" s="5">
         <f t="shared" si="2"/>
-        <v>0.78700000000000003</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="0"/>
-        <v>1589.74</v>
+        <v>3535.47</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>89</v>
-      </c>
-      <c r="B51" s="3">
-        <f>VLOOKUP(A51,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>12415346</v>
-      </c>
-      <c r="C51" s="3">
-        <f>VLOOKUP(A51,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12262715</v>
+        <v>4</v>
+      </c>
+      <c r="B51">
+        <f>VLOOKUP(A51,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2871198</v>
+      </c>
+      <c r="C51">
+        <f>VLOOKUP(A51,power!$B$2:$C$101,2,FALSE)</f>
+        <v>17038910</v>
       </c>
       <c r="E51" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="F51" s="5">
         <f t="shared" si="2"/>
-        <v>0.55300000000000005</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="H51" s="3">
         <f t="shared" si="0"/>
-        <v>5530.0000000000009</v>
+        <v>2237.04</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" s="3">
-        <f>VLOOKUP(A52,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1946527</v>
-      </c>
-      <c r="C52" s="3">
-        <f>VLOOKUP(A52,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11164215</v>
+        <v>77</v>
+      </c>
+      <c r="B52">
+        <f>VLOOKUP(A52,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3160555</v>
+      </c>
+      <c r="C52">
+        <f>VLOOKUP(A52,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16866712</v>
       </c>
       <c r="E52" s="5">
         <f t="shared" si="1"/>
-        <v>0.223</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F52" s="5">
         <f t="shared" si="2"/>
-        <v>0.41399999999999998</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="0"/>
-        <v>923.22</v>
+        <v>2438.2800000000002</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" s="3">
-        <f>VLOOKUP(A53,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>10569143</v>
-      </c>
-      <c r="C53" s="3">
-        <f>VLOOKUP(A53,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>16798323</v>
+        <v>22</v>
+      </c>
+      <c r="B53">
+        <f>VLOOKUP(A53,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2766515</v>
+      </c>
+      <c r="C53">
+        <f>VLOOKUP(A53,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16865076</v>
       </c>
       <c r="E53" s="5">
         <f t="shared" si="1"/>
-        <v>0.96799999999999997</v>
+        <v>0.436</v>
       </c>
       <c r="F53" s="5">
         <f t="shared" si="2"/>
-        <v>0.88200000000000001</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" si="0"/>
-        <v>8537.76</v>
+        <v>1992.5200000000002</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>33</v>
-      </c>
-      <c r="B54" s="3">
-        <f>VLOOKUP(A54,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3262380</v>
-      </c>
-      <c r="C54" s="3">
-        <f>VLOOKUP(A54,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13986523</v>
+        <v>51</v>
+      </c>
+      <c r="B54">
+        <f>VLOOKUP(A54,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5693755</v>
+      </c>
+      <c r="C54">
+        <f>VLOOKUP(A54,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16837866</v>
       </c>
       <c r="E54" s="5">
         <f t="shared" si="1"/>
-        <v>0.372</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="F54" s="5">
         <f t="shared" si="2"/>
-        <v>0.74399999999999999</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="0"/>
-        <v>2767.6800000000003</v>
+        <v>3982.78</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>67</v>
-      </c>
-      <c r="B55" s="3">
-        <f>VLOOKUP(A55,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5969930</v>
-      </c>
-      <c r="C55" s="3">
-        <f>VLOOKUP(A55,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12211506</v>
+        <v>24</v>
+      </c>
+      <c r="B55">
+        <f>VLOOKUP(A55,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5314806</v>
+      </c>
+      <c r="C55">
+        <f>VLOOKUP(A55,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16613357</v>
       </c>
       <c r="E55" s="5">
         <f t="shared" si="1"/>
-        <v>0.76500000000000001</v>
+        <v>0.872</v>
       </c>
       <c r="F55" s="5">
         <f t="shared" si="2"/>
-        <v>0.54200000000000004</v>
+        <v>0.436</v>
       </c>
       <c r="H55" s="3">
         <f t="shared" si="0"/>
-        <v>4146.3</v>
+        <v>3801.9199999999996</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" s="3">
-        <f>VLOOKUP(A56,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6330561</v>
-      </c>
-      <c r="C56" s="3">
-        <f>VLOOKUP(A56,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>18155735</v>
+        <v>9</v>
+      </c>
+      <c r="B56">
+        <f>VLOOKUP(A56,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>959715</v>
+      </c>
+      <c r="C56">
+        <f>VLOOKUP(A56,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16597381</v>
       </c>
       <c r="E56" s="5">
         <f t="shared" si="1"/>
-        <v>0.84</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="F56" s="5">
         <f t="shared" si="2"/>
-        <v>0.90400000000000003</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="0"/>
-        <v>7593.6</v>
+        <v>497.25</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="3">
-        <f>VLOOKUP(A57,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5636919</v>
-      </c>
-      <c r="C57" s="3">
-        <f>VLOOKUP(A57,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12539577</v>
+        <v>18</v>
+      </c>
+      <c r="B57">
+        <f>VLOOKUP(A57,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3433393</v>
+      </c>
+      <c r="C57">
+        <f>VLOOKUP(A57,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16435246</v>
       </c>
       <c r="E57" s="5">
         <f t="shared" si="1"/>
-        <v>0.72299999999999998</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="F57" s="5">
         <f t="shared" si="2"/>
-        <v>0.60599999999999998</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="H57" s="3">
         <f t="shared" si="0"/>
-        <v>4381.38</v>
+        <v>2463.2999999999997</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3">
-        <f>VLOOKUP(A58,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3919064</v>
-      </c>
-      <c r="C58" s="3">
-        <f>VLOOKUP(A58,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8305300</v>
+        <v>37</v>
+      </c>
+      <c r="B58">
+        <f>VLOOKUP(A58,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3370400</v>
+      </c>
+      <c r="C58">
+        <f>VLOOKUP(A58,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16286110</v>
       </c>
       <c r="E58" s="5">
         <f t="shared" si="1"/>
-        <v>0.45700000000000002</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="F58" s="5">
         <f t="shared" si="2"/>
-        <v>0.11700000000000001</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="H58" s="3">
         <f t="shared" si="0"/>
-        <v>534.69000000000005</v>
+        <v>2363.4</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="3">
-        <f>VLOOKUP(A59,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4411775</v>
-      </c>
-      <c r="C59" s="3">
-        <f>VLOOKUP(A59,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13225145</v>
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <f>VLOOKUP(A59,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4789200</v>
+      </c>
+      <c r="C59">
+        <f>VLOOKUP(A59,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16283751</v>
       </c>
       <c r="E59" s="5">
         <f t="shared" si="1"/>
-        <v>0.58499999999999996</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="F59" s="5">
         <f t="shared" si="2"/>
-        <v>0.68</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="0"/>
-        <v>3978</v>
+        <v>3218.67</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>77</v>
-      </c>
-      <c r="B60" s="3">
-        <f>VLOOKUP(A60,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6645174</v>
-      </c>
-      <c r="C60" s="3">
-        <f>VLOOKUP(A60,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>13348723</v>
+        <v>88</v>
+      </c>
+      <c r="B60">
+        <f>VLOOKUP(A60,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1976858</v>
+      </c>
+      <c r="C60">
+        <f>VLOOKUP(A60,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16268725</v>
       </c>
       <c r="E60" s="5">
         <f t="shared" si="1"/>
-        <v>0.872</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F60" s="5">
         <f t="shared" si="2"/>
-        <v>0.70199999999999996</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="H60" s="3">
         <f t="shared" si="0"/>
-        <v>6121.4399999999987</v>
+        <v>893.88000000000011</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="3">
-        <f>VLOOKUP(A61,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3747996</v>
-      </c>
-      <c r="C61" s="3">
-        <f>VLOOKUP(A61,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9314496</v>
+        <v>63</v>
+      </c>
+      <c r="B61">
+        <f>VLOOKUP(A61,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6194536</v>
+      </c>
+      <c r="C61">
+        <f>VLOOKUP(A61,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16213659</v>
       </c>
       <c r="E61" s="5">
         <f t="shared" si="1"/>
-        <v>0.40400000000000003</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="F61" s="5">
         <f t="shared" si="2"/>
-        <v>0.26500000000000001</v>
+        <v>0.372</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="0"/>
-        <v>1070.6000000000001</v>
+        <v>3481.92</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" s="3">
-        <f>VLOOKUP(A62,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2775200</v>
-      </c>
-      <c r="C62" s="3">
-        <f>VLOOKUP(A62,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8073053</v>
+        <v>10</v>
+      </c>
+      <c r="B62">
+        <f>VLOOKUP(A62,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2315865</v>
+      </c>
+      <c r="C62">
+        <f>VLOOKUP(A62,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16143559</v>
       </c>
       <c r="E62" s="5">
         <f t="shared" si="1"/>
-        <v>0.32900000000000001</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="F62" s="5">
         <f t="shared" si="2"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="0"/>
-        <v>312.55000000000007</v>
+        <v>1267.1099999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="3">
-        <f>VLOOKUP(A63,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4837386</v>
-      </c>
-      <c r="C63" s="3">
-        <f>VLOOKUP(A63,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10334151</v>
+        <v>83</v>
+      </c>
+      <c r="B63">
+        <f>VLOOKUP(A63,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2217385</v>
+      </c>
+      <c r="C63">
+        <f>VLOOKUP(A63,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16116026</v>
       </c>
       <c r="E63" s="5">
         <f t="shared" si="1"/>
-        <v>0.63800000000000001</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="F63" s="5">
         <f t="shared" si="2"/>
-        <v>0.308</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="0"/>
-        <v>1965.0400000000002</v>
+        <v>1119.69</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>25</v>
-      </c>
-      <c r="B64" s="3">
-        <f>VLOOKUP(A64,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2735954</v>
-      </c>
-      <c r="C64" s="3">
-        <f>VLOOKUP(A64,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>14222534</v>
+        <v>32</v>
+      </c>
+      <c r="B64">
+        <f>VLOOKUP(A64,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2071567</v>
+      </c>
+      <c r="C64">
+        <f>VLOOKUP(A64,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16054780</v>
       </c>
       <c r="E64" s="5">
         <f t="shared" si="1"/>
-        <v>0.28699999999999998</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="F64" s="5">
         <f t="shared" si="2"/>
-        <v>0.77600000000000002</v>
+        <v>0.34</v>
       </c>
       <c r="H64" s="3">
         <f t="shared" si="0"/>
-        <v>2227.12</v>
+        <v>938.4000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" s="3">
-        <f>VLOOKUP(A65,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6451253</v>
-      </c>
-      <c r="C65" s="3">
-        <f>VLOOKUP(A65,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>18960154</v>
+        <v>14</v>
+      </c>
+      <c r="B65">
+        <f>VLOOKUP(A65,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2321953</v>
+      </c>
+      <c r="C65">
+        <f>VLOOKUP(A65,power!$B$2:$C$101,2,FALSE)</f>
+        <v>16019009</v>
       </c>
       <c r="E65" s="5">
         <f t="shared" si="1"/>
-        <v>0.86099999999999999</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="F65" s="5">
         <f t="shared" si="2"/>
-        <v>0.92500000000000004</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" si="0"/>
-        <v>7964.2500000000009</v>
+        <v>1187.69</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="3">
-        <f>VLOOKUP(A66,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5904086</v>
-      </c>
-      <c r="C66" s="3">
-        <f>VLOOKUP(A66,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>22543717</v>
+        <v>0</v>
+      </c>
+      <c r="B66">
+        <f>VLOOKUP(A66,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4365881</v>
+      </c>
+      <c r="C66">
+        <f>VLOOKUP(A66,power!$B$2:$C$101,2,FALSE)</f>
+        <v>15728355</v>
       </c>
       <c r="E66" s="5">
         <f t="shared" si="1"/>
@@ -6086,761 +6178,824 @@
       </c>
       <c r="F66" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="0"/>
-        <v>7550</v>
+        <v>2408.4499999999998</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>84</v>
-      </c>
-      <c r="B67" s="3">
-        <f>VLOOKUP(A67,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>9247571</v>
-      </c>
-      <c r="C67" s="3">
-        <f>VLOOKUP(A67,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>14883117</v>
+        <v>15</v>
+      </c>
+      <c r="B67">
+        <f>VLOOKUP(A67,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2640978</v>
+      </c>
+      <c r="C67">
+        <f>VLOOKUP(A67,power!$B$2:$C$101,2,FALSE)</f>
+        <v>15257020</v>
       </c>
       <c r="E67" s="5">
         <f t="shared" ref="E67:E96" si="3">PERCENTRANK(B$2:B$96,B67)</f>
-        <v>0.94599999999999995</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="F67" s="5">
-        <f t="shared" ref="F67:H96" si="4">PERCENTRANK(C$2:C$96,C67)</f>
-        <v>0.79700000000000004</v>
+        <f t="shared" ref="F67:F96" si="4">PERCENTRANK(C$2:C$96,C67)</f>
+        <v>0.308</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" ref="H67:H96" si="5">+E67*F67*10000</f>
-        <v>7539.62</v>
+        <v>1244.32</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="3">
-        <f>VLOOKUP(A68,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5225717</v>
-      </c>
-      <c r="C68" s="3">
-        <f>VLOOKUP(A68,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>16522180</v>
+        <v>89</v>
+      </c>
+      <c r="B68">
+        <f>VLOOKUP(A68,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1784180</v>
+      </c>
+      <c r="C68">
+        <f>VLOOKUP(A68,power!$B$2:$C$101,2,FALSE)</f>
+        <v>15213690</v>
       </c>
       <c r="E68" s="5">
         <f t="shared" si="3"/>
-        <v>0.70199999999999996</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="F68" s="5">
         <f t="shared" si="4"/>
-        <v>0.872</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="5"/>
-        <v>6121.4399999999987</v>
+        <v>599.93999999999994</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="3">
-        <f>VLOOKUP(A69,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6863684</v>
-      </c>
-      <c r="C69" s="3">
-        <f>VLOOKUP(A69,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>14111194</v>
+        <v>45</v>
+      </c>
+      <c r="B69">
+        <f>VLOOKUP(A69,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3643650</v>
+      </c>
+      <c r="C69">
+        <f>VLOOKUP(A69,power!$B$2:$C$101,2,FALSE)</f>
+        <v>15208939</v>
       </c>
       <c r="E69" s="5">
         <f t="shared" si="3"/>
-        <v>0.90400000000000003</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="F69" s="5">
         <f t="shared" si="4"/>
-        <v>0.755</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="5"/>
-        <v>6825.2</v>
+        <v>1831.06</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="3">
-        <f>VLOOKUP(A70,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3863563</v>
-      </c>
-      <c r="C70" s="3">
-        <f>VLOOKUP(A70,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11417454</v>
+        <v>93</v>
+      </c>
+      <c r="B70">
+        <f>VLOOKUP(A70,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1523733</v>
+      </c>
+      <c r="C70">
+        <f>VLOOKUP(A70,power!$B$2:$C$101,2,FALSE)</f>
+        <v>15152164</v>
       </c>
       <c r="E70" s="5">
         <f t="shared" si="3"/>
-        <v>0.436</v>
+        <v>0.159</v>
       </c>
       <c r="F70" s="5">
         <f t="shared" si="4"/>
-        <v>0.45700000000000002</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="5"/>
-        <v>1992.5200000000002</v>
+        <v>438.84000000000009</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>13</v>
-      </c>
-      <c r="B71" s="3">
-        <f>VLOOKUP(A71,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1552907</v>
-      </c>
-      <c r="C71" s="3">
-        <f>VLOOKUP(A71,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9083791</v>
+        <v>6</v>
+      </c>
+      <c r="B71">
+        <f>VLOOKUP(A71,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>935625</v>
+      </c>
+      <c r="C71">
+        <f>VLOOKUP(A71,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14981242</v>
       </c>
       <c r="E71" s="5">
         <f t="shared" si="3"/>
-        <v>0.14799999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="F71" s="5">
         <f t="shared" si="4"/>
-        <v>0.24399999999999999</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="5"/>
-        <v>361.12</v>
+        <v>280.89999999999998</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="3">
-        <f>VLOOKUP(A72,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4189911</v>
-      </c>
-      <c r="C72" s="3">
-        <f>VLOOKUP(A72,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12847984</v>
+        <v>8</v>
+      </c>
+      <c r="B72">
+        <f>VLOOKUP(A72,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>885310</v>
+      </c>
+      <c r="C72">
+        <f>VLOOKUP(A72,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14956578</v>
       </c>
       <c r="E72" s="5">
         <f t="shared" si="3"/>
-        <v>0.53100000000000003</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="F72" s="5">
         <f t="shared" si="4"/>
-        <v>0.65900000000000003</v>
+        <v>0.255</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="5"/>
-        <v>3499.2900000000004</v>
+        <v>188.7</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73" s="3">
-        <f>VLOOKUP(A73,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>620681</v>
-      </c>
-      <c r="C73" s="3">
-        <f>VLOOKUP(A73,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8798022</v>
+        <v>29</v>
+      </c>
+      <c r="B73">
+        <f>VLOOKUP(A73,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4150228</v>
+      </c>
+      <c r="C73">
+        <f>VLOOKUP(A73,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14562244</v>
       </c>
       <c r="E73" s="5">
         <f t="shared" si="3"/>
-        <v>5.2999999999999999E-2</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="F73" s="5">
         <f t="shared" si="4"/>
-        <v>0.21199999999999999</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="5"/>
-        <v>112.36</v>
+        <v>1790.96</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="3">
-        <f>VLOOKUP(A74,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>774862</v>
-      </c>
-      <c r="C74" s="3">
-        <f>VLOOKUP(A74,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8857105</v>
+        <v>41</v>
+      </c>
+      <c r="B74">
+        <f>VLOOKUP(A74,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1936160</v>
+      </c>
+      <c r="C74">
+        <f>VLOOKUP(A74,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14491010</v>
       </c>
       <c r="E74" s="5">
         <f t="shared" si="3"/>
-        <v>6.3E-2</v>
+        <v>0.223</v>
       </c>
       <c r="F74" s="5">
         <f t="shared" si="4"/>
-        <v>0.223</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="5"/>
-        <v>140.49</v>
+        <v>521.82000000000005</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="3">
-        <f>VLOOKUP(A75,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5730280</v>
-      </c>
-      <c r="C75" s="3">
-        <f>VLOOKUP(A75,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9401283</v>
+        <v>35</v>
+      </c>
+      <c r="B75">
+        <f>VLOOKUP(A75,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3185355</v>
+      </c>
+      <c r="C75">
+        <f>VLOOKUP(A75,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14295737</v>
       </c>
       <c r="E75" s="5">
         <f t="shared" si="3"/>
-        <v>0.74399999999999999</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="F75" s="5">
         <f t="shared" si="4"/>
-        <v>0.27600000000000002</v>
+        <v>0.223</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="5"/>
-        <v>2053.44</v>
+        <v>1208.6600000000001</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>61</v>
-      </c>
-      <c r="B76" s="3">
-        <f>VLOOKUP(A76,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5225346</v>
-      </c>
-      <c r="C76" s="3">
-        <f>VLOOKUP(A76,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>14165047</v>
+        <v>7</v>
+      </c>
+      <c r="B76">
+        <f>VLOOKUP(A76,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1152085</v>
+      </c>
+      <c r="C76">
+        <f>VLOOKUP(A76,power!$B$2:$C$101,2,FALSE)</f>
+        <v>14151745</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="3"/>
-        <v>0.69099999999999995</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="4"/>
-        <v>0.76500000000000001</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="5"/>
-        <v>5286.15</v>
+        <v>292.56</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>26</v>
-      </c>
-      <c r="B77" s="3">
-        <f>VLOOKUP(A77,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2736811</v>
-      </c>
-      <c r="C77" s="3">
-        <f>VLOOKUP(A77,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8638981</v>
+        <v>95</v>
+      </c>
+      <c r="B77">
+        <f>VLOOKUP(A77,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>922725</v>
+      </c>
+      <c r="C77">
+        <f>VLOOKUP(A77,power!$B$2:$C$101,2,FALSE)</f>
+        <v>13936106</v>
       </c>
       <c r="E77" s="5">
         <f t="shared" si="3"/>
-        <v>0.29699999999999999</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="F77" s="5">
         <f t="shared" si="4"/>
-        <v>0.159</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="5"/>
-        <v>472.23</v>
+        <v>191.90000000000003</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="3">
-        <f>VLOOKUP(A78,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>935911</v>
-      </c>
-      <c r="C78" s="3">
-        <f>VLOOKUP(A78,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12180355</v>
+        <v>105</v>
+      </c>
+      <c r="B78" s="6">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <f>VLOOKUP(A78,power!$B$2:$C$101,2,FALSE)</f>
+        <v>13586729</v>
       </c>
       <c r="E78" s="5">
         <f t="shared" si="3"/>
-        <v>7.3999999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="F78" s="5">
         <f t="shared" si="4"/>
-        <v>0.52100000000000002</v>
+        <v>0.191</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="5"/>
-        <v>385.53999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="3">
-        <f>VLOOKUP(A79,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3799003</v>
-      </c>
-      <c r="C79" s="3">
-        <f>VLOOKUP(A79,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12625044</v>
+        <v>85</v>
+      </c>
+      <c r="B79">
+        <f>VLOOKUP(A79,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2075935</v>
+      </c>
+      <c r="C79">
+        <f>VLOOKUP(A79,power!$B$2:$C$101,2,FALSE)</f>
+        <v>13553595</v>
       </c>
       <c r="E79" s="5">
         <f t="shared" si="3"/>
-        <v>0.41399999999999998</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="F79" s="5">
         <f t="shared" si="4"/>
-        <v>0.61699999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="5"/>
-        <v>2554.38</v>
+        <v>516.59999999999991</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" s="3">
-        <f>VLOOKUP(A80,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2775719</v>
-      </c>
-      <c r="C80" s="3">
-        <f>VLOOKUP(A80,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10356991</v>
+        <v>55</v>
+      </c>
+      <c r="B80">
+        <f>VLOOKUP(A80,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3198516</v>
+      </c>
+      <c r="C80">
+        <f>VLOOKUP(A80,power!$B$2:$C$101,2,FALSE)</f>
+        <v>13281809</v>
       </c>
       <c r="E80" s="5">
         <f t="shared" si="3"/>
-        <v>0.34</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="F80" s="5">
         <f t="shared" si="4"/>
-        <v>0.32900000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="5"/>
-        <v>1118.6000000000001</v>
+        <v>940.10000000000014</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>55</v>
-      </c>
-      <c r="B81" s="3">
-        <f>VLOOKUP(A81,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4641189</v>
-      </c>
-      <c r="C81" s="3">
-        <f>VLOOKUP(A81,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8593188</v>
+        <v>66</v>
+      </c>
+      <c r="B81">
+        <f>VLOOKUP(A81,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4791169</v>
+      </c>
+      <c r="C81">
+        <f>VLOOKUP(A81,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12940061</v>
       </c>
       <c r="E81" s="5">
         <f t="shared" si="3"/>
-        <v>0.627</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="F81" s="5">
         <f t="shared" si="4"/>
-        <v>0.14799999999999999</v>
+        <v>0.159</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="5"/>
-        <v>927.95999999999992</v>
+        <v>1318.11</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>38</v>
-      </c>
-      <c r="B82" s="3">
-        <f>VLOOKUP(A82,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3831240</v>
-      </c>
-      <c r="C82" s="3">
-        <f>VLOOKUP(A82,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8681257</v>
+        <v>98</v>
+      </c>
+      <c r="B82">
+        <f>VLOOKUP(A82,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>692004</v>
+      </c>
+      <c r="C82">
+        <f>VLOOKUP(A82,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12712960</v>
       </c>
       <c r="E82" s="5">
         <f t="shared" si="3"/>
-        <v>0.42499999999999999</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="F82" s="5">
         <f t="shared" si="4"/>
-        <v>0.18</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="5"/>
-        <v>765</v>
+        <v>78.439999999999984</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="3">
-        <f>VLOOKUP(A83,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1672833</v>
-      </c>
-      <c r="C83" s="3">
-        <f>VLOOKUP(A83,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>6460817</v>
+        <v>86</v>
+      </c>
+      <c r="B83">
+        <f>VLOOKUP(A83,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2025230</v>
+      </c>
+      <c r="C83">
+        <f>VLOOKUP(A83,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12440467</v>
       </c>
       <c r="E83" s="5">
         <f t="shared" si="3"/>
-        <v>0.17</v>
+        <v>0.255</v>
       </c>
       <c r="F83" s="5">
         <f t="shared" si="4"/>
-        <v>3.1E-2</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="H83" s="3">
         <f t="shared" si="5"/>
-        <v>52.7</v>
+        <v>351.90000000000003</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>68</v>
-      </c>
-      <c r="B84" s="3">
-        <f>VLOOKUP(A84,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6008329</v>
-      </c>
-      <c r="C84" s="3">
-        <f>VLOOKUP(A84,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>15590506</v>
+        <v>91</v>
+      </c>
+      <c r="B84">
+        <f>VLOOKUP(A84,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1610065</v>
+      </c>
+      <c r="C84">
+        <f>VLOOKUP(A84,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12371637</v>
       </c>
       <c r="E84" s="5">
         <f t="shared" si="3"/>
-        <v>0.77600000000000002</v>
+        <v>0.17</v>
       </c>
       <c r="F84" s="5">
         <f t="shared" si="4"/>
-        <v>0.84</v>
+        <v>0.127</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="5"/>
-        <v>6518.4</v>
+        <v>215.9</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>28</v>
-      </c>
-      <c r="B85" s="3">
-        <f>VLOOKUP(A85,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2766540</v>
-      </c>
-      <c r="C85" s="3">
-        <f>VLOOKUP(A85,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11018161</v>
+        <v>90</v>
+      </c>
+      <c r="B85">
+        <f>VLOOKUP(A85,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1649135</v>
+      </c>
+      <c r="C85">
+        <f>VLOOKUP(A85,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12279732</v>
       </c>
       <c r="E85" s="5">
         <f t="shared" si="3"/>
-        <v>0.31900000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F85" s="5">
         <f t="shared" si="4"/>
-        <v>0.40400000000000003</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="5"/>
-        <v>1288.7600000000002</v>
+        <v>210.6</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>70</v>
-      </c>
-      <c r="B86" s="3">
-        <f>VLOOKUP(A86,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>6040919</v>
-      </c>
-      <c r="C86" s="3">
-        <f>VLOOKUP(A86,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>20030103</v>
+        <v>13</v>
+      </c>
+      <c r="B86">
+        <f>VLOOKUP(A86,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3089205</v>
+      </c>
+      <c r="C86">
+        <f>VLOOKUP(A86,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12183896</v>
       </c>
       <c r="E86" s="5">
         <f t="shared" si="3"/>
-        <v>0.79700000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="F86" s="5">
         <f t="shared" si="4"/>
-        <v>0.96799999999999997</v>
+        <v>0.106</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="5"/>
-        <v>7714.9600000000009</v>
+        <v>530</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>60</v>
-      </c>
-      <c r="B87" s="3">
-        <f>VLOOKUP(A87,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>5128448</v>
-      </c>
-      <c r="C87" s="3">
-        <f>VLOOKUP(A87,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>18607827</v>
+        <v>16</v>
+      </c>
+      <c r="B87">
+        <f>VLOOKUP(A87,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3676403</v>
+      </c>
+      <c r="C87">
+        <f>VLOOKUP(A87,power!$B$2:$C$101,2,FALSE)</f>
+        <v>12155206</v>
       </c>
       <c r="E87" s="5">
         <f t="shared" si="3"/>
-        <v>0.68</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="F87" s="5">
         <f t="shared" si="4"/>
-        <v>0.91400000000000003</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="5"/>
-        <v>6215.2000000000007</v>
+        <v>615.6</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>54</v>
-      </c>
-      <c r="B88" s="3">
-        <f>VLOOKUP(A88,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4576300</v>
-      </c>
-      <c r="C88" s="3">
-        <f>VLOOKUP(A88,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>7555440</v>
+        <v>82</v>
+      </c>
+      <c r="B88">
+        <f>VLOOKUP(A88,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2315507</v>
+      </c>
+      <c r="C88">
+        <f>VLOOKUP(A88,power!$B$2:$C$101,2,FALSE)</f>
+        <v>11654822</v>
       </c>
       <c r="E88" s="5">
         <f t="shared" si="3"/>
-        <v>0.61699999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="F88" s="5">
         <f t="shared" si="4"/>
-        <v>6.3E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="5"/>
-        <v>388.71000000000004</v>
+        <v>289.00000000000006</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>8</v>
-      </c>
-      <c r="B89" s="3">
-        <f>VLOOKUP(A89,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>938217</v>
-      </c>
-      <c r="C89" s="3">
-        <f>VLOOKUP(A89,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>8392844</v>
+        <v>74</v>
+      </c>
+      <c r="B89">
+        <f>VLOOKUP(A89,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3884630</v>
+      </c>
+      <c r="C89">
+        <f>VLOOKUP(A89,power!$B$2:$C$101,2,FALSE)</f>
+        <v>11569806</v>
       </c>
       <c r="E89" s="5">
         <f t="shared" si="3"/>
-        <v>8.5000000000000006E-2</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="F89" s="5">
         <f t="shared" si="4"/>
-        <v>0.127</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="5"/>
-        <v>107.95</v>
+        <v>511.33999999999992</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>41</v>
-      </c>
-      <c r="B90" s="3">
-        <f>VLOOKUP(A90,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>3962431</v>
-      </c>
-      <c r="C90" s="3">
-        <f>VLOOKUP(A90,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>12461232</v>
+        <v>79</v>
+      </c>
+      <c r="B90">
+        <f>VLOOKUP(A90,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3068419</v>
+      </c>
+      <c r="C90">
+        <f>VLOOKUP(A90,power!$B$2:$C$101,2,FALSE)</f>
+        <v>11299986</v>
       </c>
       <c r="E90" s="5">
         <f t="shared" si="3"/>
-        <v>0.46800000000000003</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="F90" s="5">
         <f t="shared" si="4"/>
-        <v>0.58499999999999996</v>
+        <v>6.3E-2</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="5"/>
-        <v>2737.8</v>
+        <v>301.14</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>93</v>
-      </c>
-      <c r="B91" s="3">
-        <f>VLOOKUP(A91,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1757457</v>
-      </c>
-      <c r="C91" s="3">
-        <f>VLOOKUP(A91,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10940573</v>
+        <v>3</v>
+      </c>
+      <c r="B91">
+        <f>VLOOKUP(A91,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4862491</v>
+      </c>
+      <c r="C91">
+        <f>VLOOKUP(A91,power!$B$2:$C$101,2,FALSE)</f>
+        <v>11280129</v>
       </c>
       <c r="E91" s="5">
         <f t="shared" si="3"/>
-        <v>0.18</v>
+        <v>0.85099999999999998</v>
       </c>
       <c r="F91" s="5">
         <f t="shared" si="4"/>
-        <v>0.38200000000000001</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="5"/>
-        <v>687.6</v>
+        <v>451.03</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>46</v>
-      </c>
-      <c r="B92" s="3">
-        <f>VLOOKUP(A92,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4149133</v>
-      </c>
-      <c r="C92" s="3">
-        <f>VLOOKUP(A92,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>10802273</v>
+        <v>12</v>
+      </c>
+      <c r="B92">
+        <f>VLOOKUP(A92,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2305405</v>
+      </c>
+      <c r="C92">
+        <f>VLOOKUP(A92,power!$B$2:$C$101,2,FALSE)</f>
+        <v>11078297</v>
       </c>
       <c r="E92" s="5">
         <f t="shared" si="3"/>
-        <v>0.52100000000000002</v>
+        <v>0.32900000000000001</v>
       </c>
       <c r="F92" s="5">
         <f t="shared" si="4"/>
-        <v>0.36099999999999999</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="5"/>
-        <v>1880.81</v>
+        <v>138.18000000000004</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="3">
-        <f>VLOOKUP(A93,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>1472845</v>
-      </c>
-      <c r="C93" s="3">
-        <f>VLOOKUP(A93,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>11377581</v>
+        <v>97</v>
+      </c>
+      <c r="B93">
+        <f>VLOOKUP(A93,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>701850</v>
+      </c>
+      <c r="C93">
+        <f>VLOOKUP(A93,power!$B$2:$C$101,2,FALSE)</f>
+        <v>10825922</v>
       </c>
       <c r="E93" s="5">
         <f t="shared" si="3"/>
-        <v>0.13800000000000001</v>
+        <v>6.3E-2</v>
       </c>
       <c r="F93" s="5">
         <f t="shared" si="4"/>
-        <v>0.44600000000000001</v>
+        <v>3.1E-2</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="5"/>
-        <v>615.48</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>24</v>
-      </c>
-      <c r="B94" s="3">
-        <f>VLOOKUP(A94,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>2349397</v>
-      </c>
-      <c r="C94" s="3">
-        <f>VLOOKUP(A94,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>9737463</v>
+        <v>72</v>
+      </c>
+      <c r="B94">
+        <f>VLOOKUP(A94,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4088818</v>
+      </c>
+      <c r="C94">
+        <f>VLOOKUP(A94,power!$B$2:$C$101,2,FALSE)</f>
+        <v>10738045</v>
       </c>
       <c r="E94" s="5">
         <f t="shared" si="3"/>
-        <v>0.27600000000000002</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="F94" s="5">
         <f t="shared" si="4"/>
-        <v>0.28699999999999998</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="5"/>
-        <v>792.12</v>
+        <v>149.52000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>48</v>
-      </c>
-      <c r="B95" s="3">
-        <f>VLOOKUP(A95,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4322394</v>
-      </c>
-      <c r="C95" s="3">
-        <f>VLOOKUP(A95,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>15413816</v>
+        <v>27</v>
+      </c>
+      <c r="B95">
+        <f>VLOOKUP(A95,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1109645</v>
+      </c>
+      <c r="C95">
+        <f>VLOOKUP(A95,power!$B$2:$C$101,2,FALSE)</f>
+        <v>10641846</v>
       </c>
       <c r="E95" s="5">
         <f t="shared" si="3"/>
-        <v>0.55300000000000005</v>
+        <v>0.127</v>
       </c>
       <c r="F95" s="5">
         <f t="shared" si="4"/>
-        <v>0.82899999999999996</v>
+        <v>0.01</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="5"/>
-        <v>4584.3700000000008</v>
+        <v>12.700000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>47</v>
-      </c>
-      <c r="B96" s="3">
-        <f>VLOOKUP(A96,raw_20260609_185140!$B$2:$C$96,2,FALSE)</f>
-        <v>4206739</v>
-      </c>
-      <c r="C96" s="3">
-        <f>VLOOKUP(A96,raw_20260609_185943!$B$2:$C$96,2,FALSE)</f>
-        <v>21048315</v>
+        <v>106</v>
+      </c>
+      <c r="B96" s="6">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <f>VLOOKUP(A96,power!$B$2:$C$101,2,FALSE)</f>
+        <v>10522529</v>
       </c>
       <c r="E96" s="5">
         <f t="shared" si="3"/>
-        <v>0.54200000000000004</v>
+        <v>0</v>
       </c>
       <c r="F96" s="5">
         <f t="shared" si="4"/>
-        <v>0.97799999999999998</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="5"/>
-        <v>5300.76</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>80</v>
+      </c>
+      <c r="B97">
+        <f>VLOOKUP(A97,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2849850</v>
+      </c>
+      <c r="C97">
+        <f>VLOOKUP(A97,power!$B$2:$C$101,2,FALSE)</f>
+        <v>9983003</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>94</v>
+      </c>
+      <c r="B98">
+        <f>VLOOKUP(A98,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1014383</v>
+      </c>
+      <c r="C98">
+        <f>VLOOKUP(A98,power!$B$2:$C$101,2,FALSE)</f>
+        <v>5997750</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>71</v>
+      </c>
+      <c r="B99">
+        <f>VLOOKUP(A99,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4121213</v>
+      </c>
+      <c r="C99">
+        <f>VLOOKUP(A99,power!$B$2:$C$101,2,FALSE)</f>
+        <v>5821797</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <f>VLOOKUP(A100,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>548600</v>
+      </c>
+      <c r="C100">
+        <f>VLOOKUP(A100,power!$B$2:$C$101,2,FALSE)</f>
+        <v>2029812</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>92</v>
+      </c>
+      <c r="B101">
+        <f>VLOOKUP(A101,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1544400</v>
+      </c>
+      <c r="C101">
+        <f>VLOOKUP(A101,power!$B$2:$C$101,2,FALSE)</f>
+        <v>1595038</v>
       </c>
     </row>
   </sheetData>
@@ -6850,2036 +7005,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14CD2CC-D2E0-4DAF-8D16-31DCF73231C6}">
-  <dimension ref="A1:F96"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24.109375" customWidth="1"/>
-    <col min="2" max="3" width="13.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="2.88671875" customWidth="1"/>
-    <col min="5" max="6" width="13.21875" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="3">
-        <f>VLOOKUP(A2,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>8957.52</v>
-      </c>
-      <c r="C2" s="3">
-        <f>RANK(B2,$B$2:$B$96)</f>
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <f>VLOOKUP(A2,analysis!$A$1:$C$96,2)</f>
-        <v>9314206</v>
-      </c>
-      <c r="F2" s="3">
-        <f>VLOOKUP(A2,analysis!$A$1:$C$96,3)</f>
-        <v>19304683</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="3">
-        <f>VLOOKUP(A3,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>8852.25</v>
-      </c>
-      <c r="C3" s="3">
-        <f>RANK(B3,$B$2:$B$96)</f>
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
-        <f>VLOOKUP(A3,analysis!$A$1:$C$96,2)</f>
-        <v>8603326</v>
-      </c>
-      <c r="F3" s="3">
-        <f>VLOOKUP(A3,analysis!$A$1:$C$96,3)</f>
-        <v>20009077</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3">
-        <f>VLOOKUP(A4,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>8537.76</v>
-      </c>
-      <c r="C4" s="3">
-        <f>RANK(B4,$B$2:$B$96)</f>
-        <v>3</v>
-      </c>
-      <c r="E4" s="3">
-        <f>VLOOKUP(A4,analysis!$A$1:$C$96,2)</f>
-        <v>10569143</v>
-      </c>
-      <c r="F4" s="3">
-        <f>VLOOKUP(A4,analysis!$A$1:$C$96,3)</f>
-        <v>16798323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5" s="3">
-        <f>VLOOKUP(A5,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>8099.9099999999989</v>
-      </c>
-      <c r="C5" s="3">
-        <f>RANK(B5,$B$2:$B$96)</f>
-        <v>4</v>
-      </c>
-      <c r="E5" s="3">
-        <f>VLOOKUP(A5,analysis!$A$1:$C$96,2)</f>
-        <v>12245364</v>
-      </c>
-      <c r="F5" s="3">
-        <f>VLOOKUP(A5,analysis!$A$1:$C$96,3)</f>
-        <v>15267872</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="3">
-        <f>VLOOKUP(A6,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7964.2500000000009</v>
-      </c>
-      <c r="C6" s="3">
-        <f>RANK(B6,$B$2:$B$96)</f>
-        <v>5</v>
-      </c>
-      <c r="E6" s="3">
-        <f>VLOOKUP(A6,analysis!$A$1:$C$96,2)</f>
-        <v>6451253</v>
-      </c>
-      <c r="F6" s="3">
-        <f>VLOOKUP(A6,analysis!$A$1:$C$96,3)</f>
-        <v>18960154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="3">
-        <f>VLOOKUP(A7,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7876.26</v>
-      </c>
-      <c r="C7" s="3">
-        <f>RANK(B7,$B$2:$B$96)</f>
-        <v>6</v>
-      </c>
-      <c r="E7" s="3">
-        <f>VLOOKUP(A7,analysis!$A$1:$C$96,2)</f>
-        <v>6733809</v>
-      </c>
-      <c r="F7" s="3">
-        <f>VLOOKUP(A7,analysis!$A$1:$C$96,3)</f>
-        <v>17754429</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="3">
-        <f>VLOOKUP(A8,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7714.9600000000009</v>
-      </c>
-      <c r="C8" s="3">
-        <f>RANK(B8,$B$2:$B$96)</f>
-        <v>7</v>
-      </c>
-      <c r="E8" s="3">
-        <f>VLOOKUP(A8,analysis!$A$1:$C$96,2)</f>
-        <v>6040919</v>
-      </c>
-      <c r="F8" s="3">
-        <f>VLOOKUP(A8,analysis!$A$1:$C$96,3)</f>
-        <v>20030103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="3">
-        <f>VLOOKUP(A9,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7643.68</v>
-      </c>
-      <c r="C9" s="3">
-        <f>RANK(B9,$B$2:$B$96)</f>
-        <v>8</v>
-      </c>
-      <c r="E9" s="3">
-        <f>VLOOKUP(A9,analysis!$A$1:$C$96,2)</f>
-        <v>6115380</v>
-      </c>
-      <c r="F9" s="3">
-        <f>VLOOKUP(A9,analysis!$A$1:$C$96,3)</f>
-        <v>19995322</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="3">
-        <f>VLOOKUP(A10,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7593.6</v>
-      </c>
-      <c r="C10" s="3">
-        <f>RANK(B10,$B$2:$B$96)</f>
-        <v>9</v>
-      </c>
-      <c r="E10" s="3">
-        <f>VLOOKUP(A10,analysis!$A$1:$C$96,2)</f>
-        <v>6330561</v>
-      </c>
-      <c r="F10" s="3">
-        <f>VLOOKUP(A10,analysis!$A$1:$C$96,3)</f>
-        <v>18155735</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="3">
-        <f>VLOOKUP(A11,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7550</v>
-      </c>
-      <c r="C11" s="3">
-        <f>RANK(B11,$B$2:$B$96)</f>
-        <v>10</v>
-      </c>
-      <c r="E11" s="3">
-        <f>VLOOKUP(A11,analysis!$A$1:$C$96,2)</f>
-        <v>5904086</v>
-      </c>
-      <c r="F11" s="3">
-        <f>VLOOKUP(A11,analysis!$A$1:$C$96,3)</f>
-        <v>22543717</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="3">
-        <f>VLOOKUP(A12,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>7539.62</v>
-      </c>
-      <c r="C12" s="3">
-        <f>RANK(B12,$B$2:$B$96)</f>
-        <v>11</v>
-      </c>
-      <c r="E12" s="3">
-        <f>VLOOKUP(A12,analysis!$A$1:$C$96,2)</f>
-        <v>9247571</v>
-      </c>
-      <c r="F12" s="3">
-        <f>VLOOKUP(A12,analysis!$A$1:$C$96,3)</f>
-        <v>14883117</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="3">
-        <f>VLOOKUP(A13,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6825.2</v>
-      </c>
-      <c r="C13" s="3">
-        <f>RANK(B13,$B$2:$B$96)</f>
-        <v>12</v>
-      </c>
-      <c r="E13" s="3">
-        <f>VLOOKUP(A13,analysis!$A$1:$C$96,2)</f>
-        <v>6863684</v>
-      </c>
-      <c r="F13" s="3">
-        <f>VLOOKUP(A13,analysis!$A$1:$C$96,3)</f>
-        <v>14111194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="3">
-        <f>VLOOKUP(A14,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6767.28</v>
-      </c>
-      <c r="C14" s="3">
-        <f>RANK(B14,$B$2:$B$96)</f>
-        <v>13</v>
-      </c>
-      <c r="E14" s="3">
-        <f>VLOOKUP(A14,analysis!$A$1:$C$96,2)</f>
-        <v>8931884</v>
-      </c>
-      <c r="F14" s="3">
-        <f>VLOOKUP(A14,analysis!$A$1:$C$96,3)</f>
-        <v>13526162</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="3">
-        <f>VLOOKUP(A15,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6518.4</v>
-      </c>
-      <c r="C15" s="3">
-        <f>RANK(B15,$B$2:$B$96)</f>
-        <v>14</v>
-      </c>
-      <c r="E15" s="3">
-        <f>VLOOKUP(A15,analysis!$A$1:$C$96,2)</f>
-        <v>6008329</v>
-      </c>
-      <c r="F15" s="3">
-        <f>VLOOKUP(A15,analysis!$A$1:$C$96,3)</f>
-        <v>15590506</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="3">
-        <f>VLOOKUP(A16,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6239.6399999999994</v>
-      </c>
-      <c r="C16" s="3">
-        <f>RANK(B16,$B$2:$B$96)</f>
-        <v>15</v>
-      </c>
-      <c r="E16" s="3">
-        <f>VLOOKUP(A16,analysis!$A$1:$C$96,2)</f>
-        <v>11634735</v>
-      </c>
-      <c r="F16" s="3">
-        <f>VLOOKUP(A16,analysis!$A$1:$C$96,3)</f>
-        <v>12753703</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="3">
-        <f>VLOOKUP(A17,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6215.2000000000007</v>
-      </c>
-      <c r="C17" s="3">
-        <f>RANK(B17,$B$2:$B$96)</f>
-        <v>16</v>
-      </c>
-      <c r="E17" s="3">
-        <f>VLOOKUP(A17,analysis!$A$1:$C$96,2)</f>
-        <v>5128448</v>
-      </c>
-      <c r="F17" s="3">
-        <f>VLOOKUP(A17,analysis!$A$1:$C$96,3)</f>
-        <v>18607827</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="3">
-        <f>VLOOKUP(A18,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6121.4399999999987</v>
-      </c>
-      <c r="C18" s="3">
-        <f>RANK(B18,$B$2:$B$96)</f>
-        <v>17</v>
-      </c>
-      <c r="E18" s="3">
-        <f>VLOOKUP(A18,analysis!$A$1:$C$96,2)</f>
-        <v>6645174</v>
-      </c>
-      <c r="F18" s="3">
-        <f>VLOOKUP(A18,analysis!$A$1:$C$96,3)</f>
-        <v>13348723</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="3">
-        <f>VLOOKUP(A19,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>6121.4399999999987</v>
-      </c>
-      <c r="C19" s="3">
-        <f>RANK(B19,$B$2:$B$96)</f>
-        <v>17</v>
-      </c>
-      <c r="E19" s="3">
-        <f>VLOOKUP(A19,analysis!$A$1:$C$96,2)</f>
-        <v>5225717</v>
-      </c>
-      <c r="F19" s="3">
-        <f>VLOOKUP(A19,analysis!$A$1:$C$96,3)</f>
-        <v>16522180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="3">
-        <f>VLOOKUP(A20,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>5603.44</v>
-      </c>
-      <c r="C20" s="3">
-        <f>RANK(B20,$B$2:$B$96)</f>
-        <v>19</v>
-      </c>
-      <c r="E20" s="3">
-        <f>VLOOKUP(A20,analysis!$A$1:$C$96,2)</f>
-        <v>6013376</v>
-      </c>
-      <c r="F20" s="3">
-        <f>VLOOKUP(A20,analysis!$A$1:$C$96,3)</f>
-        <v>13471090</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="3">
-        <f>VLOOKUP(A21,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>5530.0000000000009</v>
-      </c>
-      <c r="C21" s="3">
-        <f>RANK(B21,$B$2:$B$96)</f>
-        <v>20</v>
-      </c>
-      <c r="E21" s="3">
-        <f>VLOOKUP(A21,analysis!$A$1:$C$96,2)</f>
-        <v>12415346</v>
-      </c>
-      <c r="F21" s="3">
-        <f>VLOOKUP(A21,analysis!$A$1:$C$96,3)</f>
-        <v>12262715</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="3">
-        <f>VLOOKUP(A22,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>5313.35</v>
-      </c>
-      <c r="C22" s="3">
-        <f>RANK(B22,$B$2:$B$96)</f>
-        <v>21</v>
-      </c>
-      <c r="E22" s="3">
-        <f>VLOOKUP(A22,analysis!$A$1:$C$96,2)</f>
-        <v>6797175</v>
-      </c>
-      <c r="F22" s="3">
-        <f>VLOOKUP(A22,analysis!$A$1:$C$96,3)</f>
-        <v>12529656</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="3">
-        <f>VLOOKUP(A23,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>5300.76</v>
-      </c>
-      <c r="C23" s="3">
-        <f>RANK(B23,$B$2:$B$96)</f>
-        <v>22</v>
-      </c>
-      <c r="E23" s="3">
-        <f>VLOOKUP(A23,analysis!$A$1:$C$96,2)</f>
-        <v>4206739</v>
-      </c>
-      <c r="F23" s="3">
-        <f>VLOOKUP(A23,analysis!$A$1:$C$96,3)</f>
-        <v>21048315</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="3">
-        <f>VLOOKUP(A24,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>5286.15</v>
-      </c>
-      <c r="C24" s="3">
-        <f>RANK(B24,$B$2:$B$96)</f>
-        <v>23</v>
-      </c>
-      <c r="E24" s="3">
-        <f>VLOOKUP(A24,analysis!$A$1:$C$96,2)</f>
-        <v>5225346</v>
-      </c>
-      <c r="F24" s="3">
-        <f>VLOOKUP(A24,analysis!$A$1:$C$96,3)</f>
-        <v>14165047</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="3">
-        <f>VLOOKUP(A25,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4770.4000000000005</v>
-      </c>
-      <c r="C25" s="3">
-        <f>RANK(B25,$B$2:$B$96)</f>
-        <v>24</v>
-      </c>
-      <c r="E25" s="3">
-        <f>VLOOKUP(A25,analysis!$A$1:$C$96,2)</f>
-        <v>5553839</v>
-      </c>
-      <c r="F25" s="3">
-        <f>VLOOKUP(A25,analysis!$A$1:$C$96,3)</f>
-        <v>13199144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="3">
-        <f>VLOOKUP(A26,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4756.32</v>
-      </c>
-      <c r="C26" s="3">
-        <f>RANK(B26,$B$2:$B$96)</f>
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <f>VLOOKUP(A26,analysis!$A$1:$C$96,2)</f>
-        <v>4869154</v>
-      </c>
-      <c r="F26" s="3">
-        <f>VLOOKUP(A26,analysis!$A$1:$C$96,3)</f>
-        <v>13834039</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="3">
-        <f>VLOOKUP(A27,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4661.3999999999996</v>
-      </c>
-      <c r="C27" s="3">
-        <f>RANK(B27,$B$2:$B$96)</f>
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <f>VLOOKUP(A27,analysis!$A$1:$C$96,2)</f>
-        <v>6966055</v>
-      </c>
-      <c r="F27" s="3">
-        <f>VLOOKUP(A27,analysis!$A$1:$C$96,3)</f>
-        <v>12083184</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="3">
-        <f>VLOOKUP(A28,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4584.3700000000008</v>
-      </c>
-      <c r="C28" s="3">
-        <f>RANK(B28,$B$2:$B$96)</f>
-        <v>27</v>
-      </c>
-      <c r="E28" s="3">
-        <f>VLOOKUP(A28,analysis!$A$1:$C$96,2)</f>
-        <v>4322394</v>
-      </c>
-      <c r="F28" s="3">
-        <f>VLOOKUP(A28,analysis!$A$1:$C$96,3)</f>
-        <v>15413816</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="3">
-        <f>VLOOKUP(A29,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4381.38</v>
-      </c>
-      <c r="C29" s="3">
-        <f>RANK(B29,$B$2:$B$96)</f>
-        <v>28</v>
-      </c>
-      <c r="E29" s="3">
-        <f>VLOOKUP(A29,analysis!$A$1:$C$96,2)</f>
-        <v>5636919</v>
-      </c>
-      <c r="F29" s="3">
-        <f>VLOOKUP(A29,analysis!$A$1:$C$96,3)</f>
-        <v>12539577</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="3">
-        <f>VLOOKUP(A30,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4161.3899999999994</v>
-      </c>
-      <c r="C30" s="3">
-        <f>RANK(B30,$B$2:$B$96)</f>
-        <v>29</v>
-      </c>
-      <c r="E30" s="3">
-        <f>VLOOKUP(A30,analysis!$A$1:$C$96,2)</f>
-        <v>4007714</v>
-      </c>
-      <c r="F30" s="3">
-        <f>VLOOKUP(A30,analysis!$A$1:$C$96,3)</f>
-        <v>15906464</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="3">
-        <f>VLOOKUP(A31,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4146.3</v>
-      </c>
-      <c r="C31" s="3">
-        <f>RANK(B31,$B$2:$B$96)</f>
-        <v>30</v>
-      </c>
-      <c r="E31" s="3">
-        <f>VLOOKUP(A31,analysis!$A$1:$C$96,2)</f>
-        <v>5969930</v>
-      </c>
-      <c r="F31" s="3">
-        <f>VLOOKUP(A31,analysis!$A$1:$C$96,3)</f>
-        <v>12211506</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="3">
-        <f>VLOOKUP(A32,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>4115.58</v>
-      </c>
-      <c r="C32" s="3">
-        <f>RANK(B32,$B$2:$B$96)</f>
-        <v>31</v>
-      </c>
-      <c r="E32" s="3">
-        <f>VLOOKUP(A32,analysis!$A$1:$C$96,2)</f>
-        <v>4003559</v>
-      </c>
-      <c r="F32" s="3">
-        <f>VLOOKUP(A32,analysis!$A$1:$C$96,3)</f>
-        <v>16223844</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="3">
-        <f>VLOOKUP(A33,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>3978</v>
-      </c>
-      <c r="C33" s="3">
-        <f>RANK(B33,$B$2:$B$96)</f>
-        <v>32</v>
-      </c>
-      <c r="E33" s="3">
-        <f>VLOOKUP(A33,analysis!$A$1:$C$96,2)</f>
-        <v>4411775</v>
-      </c>
-      <c r="F33" s="3">
-        <f>VLOOKUP(A33,analysis!$A$1:$C$96,3)</f>
-        <v>13225145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="3">
-        <f>VLOOKUP(A34,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>3897.54</v>
-      </c>
-      <c r="C34" s="3">
-        <f>RANK(B34,$B$2:$B$96)</f>
-        <v>33</v>
-      </c>
-      <c r="E34" s="3">
-        <f>VLOOKUP(A34,analysis!$A$1:$C$96,2)</f>
-        <v>5638493</v>
-      </c>
-      <c r="F34" s="3">
-        <f>VLOOKUP(A34,analysis!$A$1:$C$96,3)</f>
-        <v>12202433</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>101</v>
-      </c>
-      <c r="B35" s="3">
-        <f>VLOOKUP(A35,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>3603.6800000000003</v>
-      </c>
-      <c r="C35" s="3">
-        <f>RANK(B35,$B$2:$B$96)</f>
-        <v>34</v>
-      </c>
-      <c r="E35" s="3">
-        <f>VLOOKUP(A35,analysis!$A$1:$C$96,2)</f>
-        <v>4837386</v>
-      </c>
-      <c r="F35" s="3">
-        <f>VLOOKUP(A35,analysis!$A$1:$C$96,3)</f>
-        <v>10334151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" s="3">
-        <f>VLOOKUP(A36,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>3499.2900000000004</v>
-      </c>
-      <c r="C36" s="3">
-        <f>RANK(B36,$B$2:$B$96)</f>
-        <v>35</v>
-      </c>
-      <c r="E36" s="3">
-        <f>VLOOKUP(A36,analysis!$A$1:$C$96,2)</f>
-        <v>4189911</v>
-      </c>
-      <c r="F36" s="3">
-        <f>VLOOKUP(A36,analysis!$A$1:$C$96,3)</f>
-        <v>12847984</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="3">
-        <f>VLOOKUP(A37,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2847.5</v>
-      </c>
-      <c r="C37" s="3">
-        <f>RANK(B37,$B$2:$B$96)</f>
-        <v>36</v>
-      </c>
-      <c r="E37" s="3">
-        <f>VLOOKUP(A37,analysis!$A$1:$C$96,2)</f>
-        <v>4995656</v>
-      </c>
-      <c r="F37" s="3">
-        <f>VLOOKUP(A37,analysis!$A$1:$C$96,3)</f>
-        <v>11242399</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>33</v>
-      </c>
-      <c r="B38" s="3">
-        <f>VLOOKUP(A38,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2767.6800000000003</v>
-      </c>
-      <c r="C38" s="3">
-        <f>RANK(B38,$B$2:$B$96)</f>
-        <v>37</v>
-      </c>
-      <c r="E38" s="3">
-        <f>VLOOKUP(A38,analysis!$A$1:$C$96,2)</f>
-        <v>3262380</v>
-      </c>
-      <c r="F38" s="3">
-        <f>VLOOKUP(A38,analysis!$A$1:$C$96,3)</f>
-        <v>13986523</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3">
-        <f>VLOOKUP(A39,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2737.8</v>
-      </c>
-      <c r="C39" s="3">
-        <f>RANK(B39,$B$2:$B$96)</f>
-        <v>38</v>
-      </c>
-      <c r="E39" s="3">
-        <f>VLOOKUP(A39,analysis!$A$1:$C$96,2)</f>
-        <v>3962431</v>
-      </c>
-      <c r="F39" s="3">
-        <f>VLOOKUP(A39,analysis!$A$1:$C$96,3)</f>
-        <v>12461232</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="3">
-        <f>VLOOKUP(A40,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2642.16</v>
-      </c>
-      <c r="C40" s="3">
-        <f>RANK(B40,$B$2:$B$96)</f>
-        <v>39</v>
-      </c>
-      <c r="E40" s="3">
-        <f>VLOOKUP(A40,analysis!$A$1:$C$96,2)</f>
-        <v>4523804</v>
-      </c>
-      <c r="F40" s="3">
-        <f>VLOOKUP(A40,analysis!$A$1:$C$96,3)</f>
-        <v>11312667</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="3">
-        <f>VLOOKUP(A41,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2554.38</v>
-      </c>
-      <c r="C41" s="3">
-        <f>RANK(B41,$B$2:$B$96)</f>
-        <v>40</v>
-      </c>
-      <c r="E41" s="3">
-        <f>VLOOKUP(A41,analysis!$A$1:$C$96,2)</f>
-        <v>3799003</v>
-      </c>
-      <c r="F41" s="3">
-        <f>VLOOKUP(A41,analysis!$A$1:$C$96,3)</f>
-        <v>12625044</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3">
-        <f>VLOOKUP(A42,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2550</v>
-      </c>
-      <c r="C42" s="3">
-        <f>RANK(B42,$B$2:$B$96)</f>
-        <v>41</v>
-      </c>
-      <c r="E42" s="3">
-        <f>VLOOKUP(A42,analysis!$A$1:$C$96,2)</f>
-        <v>4094452</v>
-      </c>
-      <c r="F42" s="3">
-        <f>VLOOKUP(A42,analysis!$A$1:$C$96,3)</f>
-        <v>12030539</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="3">
-        <f>VLOOKUP(A43,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2462.1299999999997</v>
-      </c>
-      <c r="C43" s="3">
-        <f>RANK(B43,$B$2:$B$96)</f>
-        <v>42</v>
-      </c>
-      <c r="E43" s="3">
-        <f>VLOOKUP(A43,analysis!$A$1:$C$96,2)</f>
-        <v>6146150</v>
-      </c>
-      <c r="F43" s="3">
-        <f>VLOOKUP(A43,analysis!$A$1:$C$96,3)</f>
-        <v>10255914</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44" s="3">
-        <f>VLOOKUP(A44,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2313.0899999999997</v>
-      </c>
-      <c r="C44" s="3">
-        <f>RANK(B44,$B$2:$B$96)</f>
-        <v>43</v>
-      </c>
-      <c r="E44" s="3">
-        <f>VLOOKUP(A44,analysis!$A$1:$C$96,2)</f>
-        <v>4935573</v>
-      </c>
-      <c r="F44" s="3">
-        <f>VLOOKUP(A44,analysis!$A$1:$C$96,3)</f>
-        <v>10533113</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="3">
-        <f>VLOOKUP(A45,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2227.12</v>
-      </c>
-      <c r="C45" s="3">
-        <f>RANK(B45,$B$2:$B$96)</f>
-        <v>44</v>
-      </c>
-      <c r="E45" s="3">
-        <f>VLOOKUP(A45,analysis!$A$1:$C$96,2)</f>
-        <v>2735954</v>
-      </c>
-      <c r="F45" s="3">
-        <f>VLOOKUP(A45,analysis!$A$1:$C$96,3)</f>
-        <v>14222534</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>31</v>
-      </c>
-      <c r="B46" s="3">
-        <f>VLOOKUP(A46,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2200.77</v>
-      </c>
-      <c r="C46" s="3">
-        <f>RANK(B46,$B$2:$B$96)</f>
-        <v>45</v>
-      </c>
-      <c r="E46" s="3">
-        <f>VLOOKUP(A46,analysis!$A$1:$C$96,2)</f>
-        <v>2890318</v>
-      </c>
-      <c r="F46" s="3">
-        <f>VLOOKUP(A46,analysis!$A$1:$C$96,3)</f>
-        <v>12660260</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="3">
-        <f>VLOOKUP(A47,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>2053.44</v>
-      </c>
-      <c r="C47" s="3">
-        <f>RANK(B47,$B$2:$B$96)</f>
-        <v>46</v>
-      </c>
-      <c r="E47" s="3">
-        <f>VLOOKUP(A47,analysis!$A$1:$C$96,2)</f>
-        <v>5730280</v>
-      </c>
-      <c r="F47" s="3">
-        <f>VLOOKUP(A47,analysis!$A$1:$C$96,3)</f>
-        <v>9401283</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="3">
-        <f>VLOOKUP(A48,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1992.5200000000002</v>
-      </c>
-      <c r="C48" s="3">
-        <f>RANK(B48,$B$2:$B$96)</f>
-        <v>47</v>
-      </c>
-      <c r="E48" s="3">
-        <f>VLOOKUP(A48,analysis!$A$1:$C$96,2)</f>
-        <v>3863563</v>
-      </c>
-      <c r="F48" s="3">
-        <f>VLOOKUP(A48,analysis!$A$1:$C$96,3)</f>
-        <v>11417454</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="3">
-        <f>VLOOKUP(A49,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1965.0400000000002</v>
-      </c>
-      <c r="C49" s="3">
-        <f>RANK(B49,$B$2:$B$96)</f>
-        <v>48</v>
-      </c>
-      <c r="E49" s="3">
-        <f>VLOOKUP(A49,analysis!$A$1:$C$96,2)</f>
-        <v>4837386</v>
-      </c>
-      <c r="F49" s="3">
-        <f>VLOOKUP(A49,analysis!$A$1:$C$96,3)</f>
-        <v>10334151</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3">
-        <f>VLOOKUP(A50,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1914.2</v>
-      </c>
-      <c r="C50" s="3">
-        <f>RANK(B50,$B$2:$B$96)</f>
-        <v>49</v>
-      </c>
-      <c r="E50" s="3">
-        <f>VLOOKUP(A50,analysis!$A$1:$C$96,2)</f>
-        <v>4337158</v>
-      </c>
-      <c r="F50" s="3">
-        <f>VLOOKUP(A50,analysis!$A$1:$C$96,3)</f>
-        <v>10512329</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="3">
-        <f>VLOOKUP(A51,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1880.81</v>
-      </c>
-      <c r="C51" s="3">
-        <f>RANK(B51,$B$2:$B$96)</f>
-        <v>50</v>
-      </c>
-      <c r="E51" s="3">
-        <f>VLOOKUP(A51,analysis!$A$1:$C$96,2)</f>
-        <v>4149133</v>
-      </c>
-      <c r="F51" s="3">
-        <f>VLOOKUP(A51,analysis!$A$1:$C$96,3)</f>
-        <v>10802273</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="3">
-        <f>VLOOKUP(A52,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1719.02</v>
-      </c>
-      <c r="C52" s="3">
-        <f>RANK(B52,$B$2:$B$96)</f>
-        <v>51</v>
-      </c>
-      <c r="E52" s="3">
-        <f>VLOOKUP(A52,analysis!$A$1:$C$96,2)</f>
-        <v>6387590</v>
-      </c>
-      <c r="F52" s="3">
-        <f>VLOOKUP(A52,analysis!$A$1:$C$96,3)</f>
-        <v>8767566</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="3">
-        <f>VLOOKUP(A53,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1652.4</v>
-      </c>
-      <c r="C53" s="3">
-        <f>RANK(B53,$B$2:$B$96)</f>
-        <v>52</v>
-      </c>
-      <c r="E53" s="3">
-        <f>VLOOKUP(A53,analysis!$A$1:$C$96,2)</f>
-        <v>2230810</v>
-      </c>
-      <c r="F53" s="3">
-        <f>VLOOKUP(A53,analysis!$A$1:$C$96,3)</f>
-        <v>12777474</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="3">
-        <f>VLOOKUP(A54,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1589.74</v>
-      </c>
-      <c r="C54" s="3">
-        <f>RANK(B54,$B$2:$B$96)</f>
-        <v>53</v>
-      </c>
-      <c r="E54" s="3">
-        <f>VLOOKUP(A54,analysis!$A$1:$C$96,2)</f>
-        <v>1817914</v>
-      </c>
-      <c r="F54" s="3">
-        <f>VLOOKUP(A54,analysis!$A$1:$C$96,3)</f>
-        <v>14255257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="3">
-        <f>VLOOKUP(A55,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1501.26</v>
-      </c>
-      <c r="C55" s="3">
-        <f>RANK(B55,$B$2:$B$96)</f>
-        <v>54</v>
-      </c>
-      <c r="E55" s="3">
-        <f>VLOOKUP(A55,analysis!$A$1:$C$96,2)</f>
-        <v>3296653</v>
-      </c>
-      <c r="F55" s="3">
-        <f>VLOOKUP(A55,analysis!$A$1:$C$96,3)</f>
-        <v>10948170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="3">
-        <f>VLOOKUP(A56,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1373.72</v>
-      </c>
-      <c r="C56" s="3">
-        <f>RANK(B56,$B$2:$B$96)</f>
-        <v>55</v>
-      </c>
-      <c r="E56" s="3">
-        <f>VLOOKUP(A56,analysis!$A$1:$C$96,2)</f>
-        <v>2088029</v>
-      </c>
-      <c r="F56" s="3">
-        <f>VLOOKUP(A56,analysis!$A$1:$C$96,3)</f>
-        <v>12379420</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>28</v>
-      </c>
-      <c r="B57" s="3">
-        <f>VLOOKUP(A57,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1288.7600000000002</v>
-      </c>
-      <c r="C57" s="3">
-        <f>RANK(B57,$B$2:$B$96)</f>
-        <v>56</v>
-      </c>
-      <c r="E57" s="3">
-        <f>VLOOKUP(A57,analysis!$A$1:$C$96,2)</f>
-        <v>2766540</v>
-      </c>
-      <c r="F57" s="3">
-        <f>VLOOKUP(A57,analysis!$A$1:$C$96,3)</f>
-        <v>11018161</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>18</v>
-      </c>
-      <c r="B58" s="3">
-        <f>VLOOKUP(A58,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1216.8799999999999</v>
-      </c>
-      <c r="C58" s="3">
-        <f>RANK(B58,$B$2:$B$96)</f>
-        <v>57</v>
-      </c>
-      <c r="E58" s="3">
-        <f>VLOOKUP(A58,analysis!$A$1:$C$96,2)</f>
-        <v>1901010</v>
-      </c>
-      <c r="F58" s="3">
-        <f>VLOOKUP(A58,analysis!$A$1:$C$96,3)</f>
-        <v>12424171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="3">
-        <f>VLOOKUP(A59,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1130.22</v>
-      </c>
-      <c r="C59" s="3">
-        <f>RANK(B59,$B$2:$B$96)</f>
-        <v>58</v>
-      </c>
-      <c r="E59" s="3">
-        <f>VLOOKUP(A59,analysis!$A$1:$C$96,2)</f>
-        <v>6143355</v>
-      </c>
-      <c r="F59" s="3">
-        <f>VLOOKUP(A59,analysis!$A$1:$C$96,3)</f>
-        <v>8464203</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>30</v>
-      </c>
-      <c r="B60" s="3">
-        <f>VLOOKUP(A60,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1118.6000000000001</v>
-      </c>
-      <c r="C60" s="3">
-        <f>RANK(B60,$B$2:$B$96)</f>
-        <v>59</v>
-      </c>
-      <c r="E60" s="3">
-        <f>VLOOKUP(A60,analysis!$A$1:$C$96,2)</f>
-        <v>2775719</v>
-      </c>
-      <c r="F60" s="3">
-        <f>VLOOKUP(A60,analysis!$A$1:$C$96,3)</f>
-        <v>10356991</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>36</v>
-      </c>
-      <c r="B61" s="3">
-        <f>VLOOKUP(A61,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>1070.6000000000001</v>
-      </c>
-      <c r="C61" s="3">
-        <f>RANK(B61,$B$2:$B$96)</f>
-        <v>60</v>
-      </c>
-      <c r="E61" s="3">
-        <f>VLOOKUP(A61,analysis!$A$1:$C$96,2)</f>
-        <v>3747996</v>
-      </c>
-      <c r="F61" s="3">
-        <f>VLOOKUP(A61,analysis!$A$1:$C$96,3)</f>
-        <v>9314496</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" s="3">
-        <f>VLOOKUP(A62,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>985.8</v>
-      </c>
-      <c r="C62" s="3">
-        <f>RANK(B62,$B$2:$B$96)</f>
-        <v>61</v>
-      </c>
-      <c r="E62" s="3">
-        <f>VLOOKUP(A62,analysis!$A$1:$C$96,2)</f>
-        <v>2264183</v>
-      </c>
-      <c r="F62" s="3">
-        <f>VLOOKUP(A62,analysis!$A$1:$C$96,3)</f>
-        <v>10919112</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="3">
-        <f>VLOOKUP(A63,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>927.95999999999992</v>
-      </c>
-      <c r="C63" s="3">
-        <f>RANK(B63,$B$2:$B$96)</f>
-        <v>62</v>
-      </c>
-      <c r="E63" s="3">
-        <f>VLOOKUP(A63,analysis!$A$1:$C$96,2)</f>
-        <v>4641189</v>
-      </c>
-      <c r="F63" s="3">
-        <f>VLOOKUP(A63,analysis!$A$1:$C$96,3)</f>
-        <v>8593188</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>19</v>
-      </c>
-      <c r="B64" s="3">
-        <f>VLOOKUP(A64,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>923.22</v>
-      </c>
-      <c r="C64" s="3">
-        <f>RANK(B64,$B$2:$B$96)</f>
-        <v>63</v>
-      </c>
-      <c r="E64" s="3">
-        <f>VLOOKUP(A64,analysis!$A$1:$C$96,2)</f>
-        <v>1946527</v>
-      </c>
-      <c r="F64" s="3">
-        <f>VLOOKUP(A64,analysis!$A$1:$C$96,3)</f>
-        <v>11164215</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" s="3">
-        <f>VLOOKUP(A65,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>919.62000000000012</v>
-      </c>
-      <c r="C65" s="3">
-        <f>RANK(B65,$B$2:$B$96)</f>
-        <v>64</v>
-      </c>
-      <c r="E65" s="3">
-        <f>VLOOKUP(A65,analysis!$A$1:$C$96,2)</f>
-        <v>3719900</v>
-      </c>
-      <c r="F65" s="3">
-        <f>VLOOKUP(A65,analysis!$A$1:$C$96,3)</f>
-        <v>9074995</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="3">
-        <f>VLOOKUP(A66,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>877.56999999999982</v>
-      </c>
-      <c r="C66" s="3">
-        <f>RANK(B66,$B$2:$B$96)</f>
-        <v>65</v>
-      </c>
-      <c r="E66" s="3">
-        <f>VLOOKUP(A66,analysis!$A$1:$C$96,2)</f>
-        <v>1404180</v>
-      </c>
-      <c r="F66" s="3">
-        <f>VLOOKUP(A66,analysis!$A$1:$C$96,3)</f>
-        <v>13319643</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>24</v>
-      </c>
-      <c r="B67" s="3">
-        <f>VLOOKUP(A67,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>792.12</v>
-      </c>
-      <c r="C67" s="3">
-        <f>RANK(B67,$B$2:$B$96)</f>
-        <v>66</v>
-      </c>
-      <c r="E67" s="3">
-        <f>VLOOKUP(A67,analysis!$A$1:$C$96,2)</f>
-        <v>2349397</v>
-      </c>
-      <c r="F67" s="3">
-        <f>VLOOKUP(A67,analysis!$A$1:$C$96,3)</f>
-        <v>9737463</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="3">
-        <f>VLOOKUP(A68,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>765</v>
-      </c>
-      <c r="C68" s="3">
-        <f>RANK(B68,$B$2:$B$96)</f>
-        <v>67</v>
-      </c>
-      <c r="E68" s="3">
-        <f>VLOOKUP(A68,analysis!$A$1:$C$96,2)</f>
-        <v>3831240</v>
-      </c>
-      <c r="F68" s="3">
-        <f>VLOOKUP(A68,analysis!$A$1:$C$96,3)</f>
-        <v>8681257</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="3">
-        <f>VLOOKUP(A69,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>687.6</v>
-      </c>
-      <c r="C69" s="3">
-        <f>RANK(B69,$B$2:$B$96)</f>
-        <v>68</v>
-      </c>
-      <c r="E69" s="3">
-        <f>VLOOKUP(A69,analysis!$A$1:$C$96,2)</f>
-        <v>1757457</v>
-      </c>
-      <c r="F69" s="3">
-        <f>VLOOKUP(A69,analysis!$A$1:$C$96,3)</f>
-        <v>10940573</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>52</v>
-      </c>
-      <c r="B70" s="3">
-        <f>VLOOKUP(A70,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>630.70000000000005</v>
-      </c>
-      <c r="C70" s="3">
-        <f>RANK(B70,$B$2:$B$96)</f>
-        <v>69</v>
-      </c>
-      <c r="E70" s="3">
-        <f>VLOOKUP(A70,analysis!$A$1:$C$96,2)</f>
-        <v>4448558</v>
-      </c>
-      <c r="F70" s="3">
-        <f>VLOOKUP(A70,analysis!$A$1:$C$96,3)</f>
-        <v>8201013</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="3">
-        <f>VLOOKUP(A71,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>615.48</v>
-      </c>
-      <c r="C71" s="3">
-        <f>RANK(B71,$B$2:$B$96)</f>
-        <v>70</v>
-      </c>
-      <c r="E71" s="3">
-        <f>VLOOKUP(A71,analysis!$A$1:$C$96,2)</f>
-        <v>1472845</v>
-      </c>
-      <c r="F71" s="3">
-        <f>VLOOKUP(A71,analysis!$A$1:$C$96,3)</f>
-        <v>11377581</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>32</v>
-      </c>
-      <c r="B72" s="3">
-        <f>VLOOKUP(A72,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>613.70000000000005</v>
-      </c>
-      <c r="C72" s="3">
-        <f>RANK(B72,$B$2:$B$96)</f>
-        <v>71</v>
-      </c>
-      <c r="E72" s="3">
-        <f>VLOOKUP(A72,analysis!$A$1:$C$96,2)</f>
-        <v>3075077</v>
-      </c>
-      <c r="F72" s="3">
-        <f>VLOOKUP(A72,analysis!$A$1:$C$96,3)</f>
-        <v>8652496</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73" s="3">
-        <f>VLOOKUP(A73,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>547.56000000000006</v>
-      </c>
-      <c r="C73" s="3">
-        <f>RANK(B73,$B$2:$B$96)</f>
-        <v>72</v>
-      </c>
-      <c r="E73" s="3">
-        <f>VLOOKUP(A73,analysis!$A$1:$C$96,2)</f>
-        <v>1269313</v>
-      </c>
-      <c r="F73" s="3">
-        <f>VLOOKUP(A73,analysis!$A$1:$C$96,3)</f>
-        <v>11588003</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="3">
-        <f>VLOOKUP(A74,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>534.69000000000005</v>
-      </c>
-      <c r="C74" s="3">
-        <f>RANK(B74,$B$2:$B$96)</f>
-        <v>73</v>
-      </c>
-      <c r="E74" s="3">
-        <f>VLOOKUP(A74,analysis!$A$1:$C$96,2)</f>
-        <v>3919064</v>
-      </c>
-      <c r="F74" s="3">
-        <f>VLOOKUP(A74,analysis!$A$1:$C$96,3)</f>
-        <v>8305300</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>26</v>
-      </c>
-      <c r="B75" s="3">
-        <f>VLOOKUP(A75,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>472.23</v>
-      </c>
-      <c r="C75" s="3">
-        <f>RANK(B75,$B$2:$B$96)</f>
-        <v>74</v>
-      </c>
-      <c r="E75" s="3">
-        <f>VLOOKUP(A75,analysis!$A$1:$C$96,2)</f>
-        <v>2736811</v>
-      </c>
-      <c r="F75" s="3">
-        <f>VLOOKUP(A75,analysis!$A$1:$C$96,3)</f>
-        <v>8638981</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>20</v>
-      </c>
-      <c r="B76" s="3">
-        <f>VLOOKUP(A76,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>446.94000000000005</v>
-      </c>
-      <c r="C76" s="3">
-        <f>RANK(B76,$B$2:$B$96)</f>
-        <v>75</v>
-      </c>
-      <c r="E76" s="3">
-        <f>VLOOKUP(A76,analysis!$A$1:$C$96,2)</f>
-        <v>2061656</v>
-      </c>
-      <c r="F76" s="3">
-        <f>VLOOKUP(A76,analysis!$A$1:$C$96,3)</f>
-        <v>8699159</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>54</v>
-      </c>
-      <c r="B77" s="3">
-        <f>VLOOKUP(A77,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>388.71000000000004</v>
-      </c>
-      <c r="C77" s="3">
-        <f>RANK(B77,$B$2:$B$96)</f>
-        <v>76</v>
-      </c>
-      <c r="E77" s="3">
-        <f>VLOOKUP(A77,analysis!$A$1:$C$96,2)</f>
-        <v>4576300</v>
-      </c>
-      <c r="F77" s="3">
-        <f>VLOOKUP(A77,analysis!$A$1:$C$96,3)</f>
-        <v>7555440</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="3">
-        <f>VLOOKUP(A78,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>385.53999999999996</v>
-      </c>
-      <c r="C78" s="3">
-        <f>RANK(B78,$B$2:$B$96)</f>
-        <v>77</v>
-      </c>
-      <c r="E78" s="3">
-        <f>VLOOKUP(A78,analysis!$A$1:$C$96,2)</f>
-        <v>935911</v>
-      </c>
-      <c r="F78" s="3">
-        <f>VLOOKUP(A78,analysis!$A$1:$C$96,3)</f>
-        <v>12180355</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3">
-        <f>VLOOKUP(A79,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>370</v>
-      </c>
-      <c r="C79" s="3">
-        <f>RANK(B79,$B$2:$B$96)</f>
-        <v>78</v>
-      </c>
-      <c r="E79" s="3">
-        <f>VLOOKUP(A79,analysis!$A$1:$C$96,2)</f>
-        <v>4017933</v>
-      </c>
-      <c r="F79" s="3">
-        <f>VLOOKUP(A79,analysis!$A$1:$C$96,3)</f>
-        <v>7876160</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="3">
-        <f>VLOOKUP(A80,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>361.12</v>
-      </c>
-      <c r="C80" s="3">
-        <f>RANK(B80,$B$2:$B$96)</f>
-        <v>79</v>
-      </c>
-      <c r="E80" s="3">
-        <f>VLOOKUP(A80,analysis!$A$1:$C$96,2)</f>
-        <v>1552907</v>
-      </c>
-      <c r="F80" s="3">
-        <f>VLOOKUP(A80,analysis!$A$1:$C$96,3)</f>
-        <v>9083791</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>92</v>
-      </c>
-      <c r="B81" s="3">
-        <f>VLOOKUP(A81,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>338.14</v>
-      </c>
-      <c r="C81" s="3">
-        <f>RANK(B81,$B$2:$B$96)</f>
-        <v>80</v>
-      </c>
-      <c r="E81" s="3">
-        <f>VLOOKUP(A81,analysis!$A$1:$C$96,2)</f>
-        <v>1120614</v>
-      </c>
-      <c r="F81" s="3">
-        <f>VLOOKUP(A81,analysis!$A$1:$C$96,3)</f>
-        <v>10356025</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>29</v>
-      </c>
-      <c r="B82" s="3">
-        <f>VLOOKUP(A82,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>312.55000000000007</v>
-      </c>
-      <c r="C82" s="3">
-        <f>RANK(B82,$B$2:$B$96)</f>
-        <v>81</v>
-      </c>
-      <c r="E82" s="3">
-        <f>VLOOKUP(A82,analysis!$A$1:$C$96,2)</f>
-        <v>2775200</v>
-      </c>
-      <c r="F82" s="3">
-        <f>VLOOKUP(A82,analysis!$A$1:$C$96,3)</f>
-        <v>8073053</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>50</v>
-      </c>
-      <c r="B83" s="3">
-        <f>VLOOKUP(A83,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>304.21999999999997</v>
-      </c>
-      <c r="C83" s="3">
-        <f>RANK(B83,$B$2:$B$96)</f>
-        <v>82</v>
-      </c>
-      <c r="E83" s="3">
-        <f>VLOOKUP(A83,analysis!$A$1:$C$96,2)</f>
-        <v>4404572</v>
-      </c>
-      <c r="F83" s="3">
-        <f>VLOOKUP(A83,analysis!$A$1:$C$96,3)</f>
-        <v>7522797</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>4</v>
-      </c>
-      <c r="B84" s="3">
-        <f>VLOOKUP(A84,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>205.38</v>
-      </c>
-      <c r="C84" s="3">
-        <f>RANK(B84,$B$2:$B$96)</f>
-        <v>83</v>
-      </c>
-      <c r="E84" s="3">
-        <f>VLOOKUP(A84,analysis!$A$1:$C$96,2)</f>
-        <v>455533</v>
-      </c>
-      <c r="F84" s="3">
-        <f>VLOOKUP(A84,analysis!$A$1:$C$96,3)</f>
-        <v>11814326</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="3">
-        <f>VLOOKUP(A85,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>140.49</v>
-      </c>
-      <c r="C85" s="3">
-        <f>RANK(B85,$B$2:$B$96)</f>
-        <v>84</v>
-      </c>
-      <c r="E85" s="3">
-        <f>VLOOKUP(A85,analysis!$A$1:$C$96,2)</f>
-        <v>774862</v>
-      </c>
-      <c r="F85" s="3">
-        <f>VLOOKUP(A85,analysis!$A$1:$C$96,3)</f>
-        <v>8857105</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="3">
-        <f>VLOOKUP(A86,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>135.15</v>
-      </c>
-      <c r="C86" s="3">
-        <f>RANK(B86,$B$2:$B$96)</f>
-        <v>85</v>
-      </c>
-      <c r="E86" s="3">
-        <f>VLOOKUP(A86,analysis!$A$1:$C$96,2)</f>
-        <v>1554098</v>
-      </c>
-      <c r="F86" s="3">
-        <f>VLOOKUP(A86,analysis!$A$1:$C$96,3)</f>
-        <v>7990739</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>27</v>
-      </c>
-      <c r="B87" s="3">
-        <f>VLOOKUP(A87,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>129.36000000000001</v>
-      </c>
-      <c r="C87" s="3">
-        <f>RANK(B87,$B$2:$B$96)</f>
-        <v>86</v>
-      </c>
-      <c r="E87" s="3">
-        <f>VLOOKUP(A87,analysis!$A$1:$C$96,2)</f>
-        <v>2754992</v>
-      </c>
-      <c r="F87" s="3">
-        <f>VLOOKUP(A87,analysis!$A$1:$C$96,3)</f>
-        <v>6670513</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>5</v>
-      </c>
-      <c r="B88" s="3">
-        <f>VLOOKUP(A88,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>112.36</v>
-      </c>
-      <c r="C88" s="3">
-        <f>RANK(B88,$B$2:$B$96)</f>
-        <v>87</v>
-      </c>
-      <c r="E88" s="3">
-        <f>VLOOKUP(A88,analysis!$A$1:$C$96,2)</f>
-        <v>620681</v>
-      </c>
-      <c r="F88" s="3">
-        <f>VLOOKUP(A88,analysis!$A$1:$C$96,3)</f>
-        <v>8798022</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>8</v>
-      </c>
-      <c r="B89" s="3">
-        <f>VLOOKUP(A89,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>107.95</v>
-      </c>
-      <c r="C89" s="3">
-        <f>RANK(B89,$B$2:$B$96)</f>
-        <v>88</v>
-      </c>
-      <c r="E89" s="3">
-        <f>VLOOKUP(A89,analysis!$A$1:$C$96,2)</f>
-        <v>938217</v>
-      </c>
-      <c r="F89" s="3">
-        <f>VLOOKUP(A89,analysis!$A$1:$C$96,3)</f>
-        <v>8392844</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>2</v>
-      </c>
-      <c r="B90" s="3">
-        <f>VLOOKUP(A90,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>100.38</v>
-      </c>
-      <c r="C90" s="3">
-        <f>RANK(B90,$B$2:$B$96)</f>
-        <v>89</v>
-      </c>
-      <c r="E90" s="3">
-        <f>VLOOKUP(A90,analysis!$A$1:$C$96,2)</f>
-        <v>254963</v>
-      </c>
-      <c r="F90" s="3">
-        <f>VLOOKUP(A90,analysis!$A$1:$C$96,3)</f>
-        <v>11647735</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>1</v>
-      </c>
-      <c r="B91" s="3">
-        <f>VLOOKUP(A91,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>98.899999999999991</v>
-      </c>
-      <c r="C91" s="3">
-        <f>RANK(B91,$B$2:$B$96)</f>
-        <v>90</v>
-      </c>
-      <c r="E91" s="3">
-        <f>VLOOKUP(A91,analysis!$A$1:$C$96,2)</f>
-        <v>205800</v>
-      </c>
-      <c r="F91" s="3">
-        <f>VLOOKUP(A91,analysis!$A$1:$C$96,3)</f>
-        <v>22201430</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="3">
-        <f>VLOOKUP(A92,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>52.7</v>
-      </c>
-      <c r="C92" s="3">
-        <f>RANK(B92,$B$2:$B$96)</f>
-        <v>91</v>
-      </c>
-      <c r="E92" s="3">
-        <f>VLOOKUP(A92,analysis!$A$1:$C$96,2)</f>
-        <v>1672833</v>
-      </c>
-      <c r="F92" s="3">
-        <f>VLOOKUP(A92,analysis!$A$1:$C$96,3)</f>
-        <v>6460817</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>16</v>
-      </c>
-      <c r="B93" s="3">
-        <f>VLOOKUP(A93,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>40.110000000000007</v>
-      </c>
-      <c r="C93" s="3">
-        <f>RANK(B93,$B$2:$B$96)</f>
-        <v>92</v>
-      </c>
-      <c r="E93" s="3">
-        <f>VLOOKUP(A93,analysis!$A$1:$C$96,2)</f>
-        <v>1805208</v>
-      </c>
-      <c r="F93" s="3">
-        <f>VLOOKUP(A93,analysis!$A$1:$C$96,3)</f>
-        <v>6254387</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94" s="3">
-        <f>VLOOKUP(A94,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>9.5</v>
-      </c>
-      <c r="C94" s="3">
-        <f>RANK(B94,$B$2:$B$96)</f>
-        <v>93</v>
-      </c>
-      <c r="E94" s="3">
-        <f>VLOOKUP(A94,analysis!$A$1:$C$96,2)</f>
-        <v>998281</v>
-      </c>
-      <c r="F94" s="3">
-        <f>VLOOKUP(A94,analysis!$A$1:$C$96,3)</f>
-        <v>6167119</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="3">
-        <f>VLOOKUP(A95,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="3">
-        <f>RANK(B95,$B$2:$B$96)</f>
-        <v>94</v>
-      </c>
-      <c r="E95" s="3">
-        <f>VLOOKUP(A95,analysis!$A$1:$C$96,2)</f>
-        <v>285550</v>
-      </c>
-      <c r="F95" s="3">
-        <f>VLOOKUP(A95,analysis!$A$1:$C$96,3)</f>
-        <v>6003695</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>0</v>
-      </c>
-      <c r="B96" s="3">
-        <f>VLOOKUP(A96,analysis!$A$1:$H$96,8,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="C96" s="3">
-        <f>RANK(B96,$B$2:$B$96)</f>
-        <v>94</v>
-      </c>
-      <c r="E96" s="3">
-        <f>VLOOKUP(A96,analysis!$A$1:$C$96,2)</f>
-        <v>196436</v>
-      </c>
-      <c r="F96" s="3">
-        <f>VLOOKUP(A96,analysis!$A$1:$C$96,3)</f>
-        <v>9281024</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C191">
-    <sortCondition ref="C2:C191"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\personal\last-war-tools\streamlit-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52463D89-653A-49A9-8C25-10914957C08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6CF795-F1AF-47F3-9336-6F20BC293676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8412" yWindow="4560" windowWidth="31620" windowHeight="19884" activeTab="2" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
+    <workbookView xWindow="11208" yWindow="5988" windowWidth="31620" windowHeight="19884" activeTab="2" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
   </bookViews>
   <sheets>
     <sheet name="vs (thru Wed 740pm)" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="108">
   <si>
     <t>GhostSumit</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>Space   Ghost</t>
-  </si>
-  <si>
-    <t>Player</t>
   </si>
   <si>
     <t>VS</t>
@@ -2339,7 +2336,7 @@
         <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2347,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>15702055</v>
@@ -2380,7 +2377,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>8611927</v>
@@ -2413,7 +2410,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8">
         <v>6194536</v>
@@ -2446,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>5794630</v>
@@ -2512,7 +2509,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17">
         <v>4792980</v>
@@ -2523,7 +2520,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18">
         <v>4791169</v>
@@ -2545,7 +2542,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20">
         <v>4737953</v>
@@ -2556,7 +2553,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21">
         <v>4714228</v>
@@ -2567,7 +2564,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22">
         <v>4647868</v>
@@ -2578,7 +2575,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23">
         <v>4627335</v>
@@ -2633,7 +2630,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28">
         <v>4121213</v>
@@ -2655,7 +2652,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30">
         <v>4088818</v>
@@ -2666,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C31">
         <v>4011219</v>
@@ -2677,7 +2674,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C32">
         <v>3884630</v>
@@ -2710,7 +2707,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35">
         <v>3804815</v>
@@ -2765,7 +2762,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40">
         <v>3491725</v>
@@ -2798,7 +2795,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C43">
         <v>3363330</v>
@@ -2853,7 +2850,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C48">
         <v>3160555</v>
@@ -2886,7 +2883,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>3087825</v>
@@ -2897,7 +2894,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>3068419</v>
@@ -2941,7 +2938,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>2849850</v>
@@ -2963,7 +2960,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>2722105</v>
@@ -3018,7 +3015,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63">
         <v>2342828</v>
@@ -3051,7 +3048,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66">
         <v>2315507</v>
@@ -3073,7 +3070,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C68">
         <v>2217385</v>
@@ -3084,7 +3081,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C69">
         <v>2192925</v>
@@ -3106,7 +3103,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C71">
         <v>2075935</v>
@@ -3139,7 +3136,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C74">
         <v>2025230</v>
@@ -3150,7 +3147,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C75">
         <v>2024897</v>
@@ -3161,7 +3158,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C76">
         <v>1976858</v>
@@ -3194,7 +3191,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C79">
         <v>1784180</v>
@@ -3216,7 +3213,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C81">
         <v>1649135</v>
@@ -3227,7 +3224,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C82">
         <v>1610065</v>
@@ -3238,7 +3235,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83">
         <v>1544400</v>
@@ -3249,7 +3246,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C84">
         <v>1523733</v>
@@ -3293,7 +3290,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>1014383</v>
@@ -3326,7 +3323,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C91">
         <v>922725</v>
@@ -3337,7 +3334,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92">
         <v>894740</v>
@@ -3359,7 +3356,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C94">
         <v>701850</v>
@@ -3370,7 +3367,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C95">
         <v>692004</v>
@@ -3381,7 +3378,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C96">
         <v>548600</v>
@@ -3392,7 +3389,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C97">
         <v>531480</v>
@@ -3418,10 +3415,10 @@
         <v>54</v>
       </c>
       <c r="B1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" t="s">
         <v>107</v>
-      </c>
-      <c r="C1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -3429,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>42986788</v>
@@ -3440,7 +3437,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>38451162</v>
@@ -3451,7 +3448,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>33500100</v>
@@ -3473,7 +3470,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>28585390</v>
@@ -3506,7 +3503,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>25648467</v>
@@ -3517,7 +3514,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>25323011</v>
@@ -3528,7 +3525,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>25115705</v>
@@ -3561,7 +3558,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <v>23418217</v>
@@ -3594,7 +3591,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>22556083</v>
@@ -3627,7 +3624,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>21965627</v>
@@ -3737,7 +3734,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30">
         <v>20126375</v>
@@ -3748,7 +3745,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C31">
         <v>19864472</v>
@@ -3759,7 +3756,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32">
         <v>19357004</v>
@@ -3792,7 +3789,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C35">
         <v>19015237</v>
@@ -3803,7 +3800,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36">
         <v>19012659</v>
@@ -3847,7 +3844,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C40">
         <v>18234830</v>
@@ -3858,7 +3855,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41">
         <v>18183875</v>
@@ -3869,7 +3866,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42">
         <v>17966681</v>
@@ -3880,7 +3877,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43">
         <v>17785133</v>
@@ -3913,7 +3910,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C46">
         <v>17540105</v>
@@ -3924,7 +3921,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47">
         <v>17505236</v>
@@ -3979,7 +3976,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C52">
         <v>16866712</v>
@@ -4067,7 +4064,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>16268725</v>
@@ -4078,7 +4075,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61">
         <v>16213659</v>
@@ -4100,7 +4097,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <v>16116026</v>
@@ -4155,7 +4152,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>15213690</v>
@@ -4177,7 +4174,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>15152164</v>
@@ -4254,7 +4251,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C77">
         <v>13936106</v>
@@ -4265,7 +4262,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>13586729</v>
@@ -4276,7 +4273,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79">
         <v>13553595</v>
@@ -4298,7 +4295,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C81">
         <v>12940061</v>
@@ -4309,7 +4306,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C82">
         <v>12712960</v>
@@ -4320,7 +4317,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C83">
         <v>12440467</v>
@@ -4331,7 +4328,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C84">
         <v>12371637</v>
@@ -4342,7 +4339,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85">
         <v>12279732</v>
@@ -4375,7 +4372,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C88">
         <v>11654822</v>
@@ -4386,7 +4383,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C89">
         <v>11569806</v>
@@ -4397,7 +4394,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C90">
         <v>11299986</v>
@@ -4430,7 +4427,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C93">
         <v>10825922</v>
@@ -4441,7 +4438,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C94">
         <v>10738045</v>
@@ -4463,7 +4460,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C96">
         <v>10522529</v>
@@ -4474,7 +4471,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C97">
         <v>9983003</v>
@@ -4485,7 +4482,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C98">
         <v>5997750</v>
@@ -4496,7 +4493,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C99">
         <v>5821797</v>
@@ -4507,7 +4504,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100">
         <v>2029812</v>
@@ -4518,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C101">
         <v>1595038</v>
@@ -4544,27 +4541,27 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2">
         <f>VLOOKUP(A2,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4589,7 +4586,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <f>VLOOKUP(A3,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4">
         <f>VLOOKUP(A4,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4664,7 +4661,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6">
         <f>VLOOKUP(A6,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4739,7 +4736,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9">
         <f>VLOOKUP(A9,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4764,7 +4761,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B10">
         <f>VLOOKUP(A10,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4789,7 +4786,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
@@ -4863,7 +4860,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14">
         <f>VLOOKUP(A14,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -4938,7 +4935,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17">
         <f>VLOOKUP(A17,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5013,7 +5010,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20">
         <f>VLOOKUP(A20,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5263,7 +5260,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B30">
         <f>VLOOKUP(A30,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5288,7 +5285,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31">
         <f>VLOOKUP(A31,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5313,7 +5310,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32">
         <f>VLOOKUP(A32,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5388,7 +5385,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B35">
         <f>VLOOKUP(A35,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5413,7 +5410,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B36">
         <f>VLOOKUP(A36,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5513,7 +5510,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B40">
         <f>VLOOKUP(A40,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5538,7 +5535,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B41">
         <f>VLOOKUP(A41,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5563,7 +5560,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B42">
         <f>VLOOKUP(A42,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5588,7 +5585,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" s="6">
         <v>0</v>
@@ -5662,7 +5659,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B46">
         <f>VLOOKUP(A46,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5687,7 +5684,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47">
         <f>VLOOKUP(A47,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -5812,7 +5809,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B52">
         <f>VLOOKUP(A52,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6012,7 +6009,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60">
         <f>VLOOKUP(A60,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6037,7 +6034,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B61">
         <f>VLOOKUP(A61,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6087,7 +6084,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B63">
         <f>VLOOKUP(A63,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6212,7 +6209,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B68">
         <f>VLOOKUP(A68,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6262,7 +6259,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B70">
         <f>VLOOKUP(A70,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6437,7 +6434,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B77">
         <f>VLOOKUP(A77,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6462,7 +6459,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B78" s="6">
         <v>0</v>
@@ -6486,7 +6483,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B79">
         <f>VLOOKUP(A79,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6536,7 +6533,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B81">
         <f>VLOOKUP(A81,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6561,7 +6558,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B82">
         <f>VLOOKUP(A82,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6586,7 +6583,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <f>VLOOKUP(A83,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6611,7 +6608,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B84">
         <f>VLOOKUP(A84,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6636,7 +6633,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B85">
         <f>VLOOKUP(A85,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6711,7 +6708,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88">
         <f>VLOOKUP(A88,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6736,7 +6733,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B89">
         <f>VLOOKUP(A89,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6761,7 +6758,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B90">
         <f>VLOOKUP(A90,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6836,7 +6833,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93">
         <f>VLOOKUP(A93,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6861,7 +6858,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B94">
         <f>VLOOKUP(A94,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6911,7 +6908,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B96" s="6">
         <v>0</v>
@@ -6935,7 +6932,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B97">
         <f>VLOOKUP(A97,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6948,7 +6945,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B98">
         <f>VLOOKUP(A98,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6961,7 +6958,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B99">
         <f>VLOOKUP(A99,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6974,7 +6971,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100">
         <f>VLOOKUP(A100,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B101">
         <f>VLOOKUP(A101,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\personal\last-war-tools\streamlit-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6CF795-F1AF-47F3-9336-6F20BC293676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6B0161-9057-4066-822F-A91629E25A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11208" yWindow="5988" windowWidth="31620" windowHeight="19884" activeTab="2" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
+    <workbookView xWindow="19080" yWindow="2892" windowWidth="25572" windowHeight="19884" activeTab="2" xr2:uid="{8A76F465-58BB-49A3-B977-DD0827CA6734}"/>
   </bookViews>
   <sheets>
-    <sheet name="vs (thru Wed 740pm)" sheetId="1" r:id="rId1"/>
+    <sheet name="vs (thru Wed 815pm)" sheetId="1" r:id="rId1"/>
     <sheet name="power" sheetId="2" r:id="rId2"/>
     <sheet name="analysis" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -543,283 +543,283 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.90400000000000003</c:v>
+                  <c:v>0.94899999999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0.68600000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.97899999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.78700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.61599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0.80800000000000005</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.95699999999999996</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.77600000000000002</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.627</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.41399999999999998</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.60599999999999998</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.96799999999999997</c:v>
+                  <c:v>0.96899999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.45700000000000002</c:v>
+                  <c:v>0.747</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.92500000000000004</c:v>
+                  <c:v>0.79700000000000004</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.48899999999999999</c:v>
+                  <c:v>0.84799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.67</c:v>
+                  <c:v>0.55500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.68</c:v>
+                  <c:v>0.73699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.57399999999999995</c:v>
+                  <c:v>0.626</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.76500000000000001</c:v>
+                  <c:v>0.69599999999999995</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.88200000000000001</c:v>
+                  <c:v>0.878</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.84</c:v>
+                  <c:v>0.89800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>0.98899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.53100000000000003</c:v>
+                  <c:v>0.63600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.29699999999999999</c:v>
+                  <c:v>0.34300000000000003</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.38200000000000001</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.74399999999999999</c:v>
+                  <c:v>0.64600000000000002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.86099999999999999</c:v>
+                  <c:v>0.67600000000000005</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.94599999999999995</c:v>
+                  <c:v>0.85799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.97799999999999998</c:v>
+                  <c:v>0.92900000000000005</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.39300000000000002</c:v>
+                  <c:v>0.33300000000000002</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.308</c:v>
+                  <c:v>0.59499999999999997</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.78700000000000003</c:v>
+                  <c:v>0.88800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.372</c:v>
+                  <c:v>0.72699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.191</c:v>
+                  <c:v>0.35299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.61699999999999999</c:v>
+                  <c:v>0.70699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.70199999999999996</c:v>
+                  <c:v>0.26200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.79700000000000004</c:v>
+                  <c:v>0.95899999999999996</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.56299999999999994</c:v>
+                  <c:v>0.82799999999999996</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.14799999999999999</c:v>
+                  <c:v>0.20200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.21199999999999999</c:v>
+                  <c:v>0.51500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.24399999999999999</c:v>
+                  <c:v>0.313</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.65900000000000003</c:v>
+                  <c:v>0.18099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.42499999999999999</c:v>
+                  <c:v>0.66600000000000004</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.26500000000000001</c:v>
+                  <c:v>0.23200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.44600000000000001</c:v>
+                  <c:v>0.49399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>4.2000000000000003E-2</c:v>
+                  <c:v>0.151</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>8.5000000000000006E-2</c:v>
+                  <c:v>0.21199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.91400000000000003</c:v>
+                  <c:v>0.91900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.51</c:v>
+                  <c:v>0.75700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.72299999999999998</c:v>
+                  <c:v>0.56499999999999995</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.46800000000000003</c:v>
+                  <c:v>0.42399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.52100000000000002</c:v>
+                  <c:v>0.83799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.436</c:v>
+                  <c:v>0.505</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.89300000000000002</c:v>
+                  <c:v>0.77700000000000002</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.872</c:v>
+                  <c:v>0.65600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.11700000000000001</c:v>
+                  <c:v>0.161</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.59499999999999997</c:v>
+                  <c:v>0.44400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.58499999999999996</c:v>
+                  <c:v>0.81799999999999995</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.81899999999999995</c:v>
+                  <c:v>0.90900000000000003</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.23400000000000001</c:v>
+                  <c:v>0.32300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.93600000000000005</c:v>
+                  <c:v>0.93899999999999995</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.35099999999999998</c:v>
+                  <c:v>0.27200000000000002</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.31900000000000001</c:v>
+                  <c:v>0.10100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.27600000000000002</c:v>
+                  <c:v>0.252</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.36099999999999999</c:v>
+                  <c:v>0.39300000000000002</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.755</c:v>
+                  <c:v>0.48399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.40400000000000003</c:v>
+                  <c:v>0.434</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.20200000000000001</c:v>
+                  <c:v>0.29199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.63800000000000001</c:v>
+                  <c:v>0.86799999999999999</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.159</c:v>
+                  <c:v>0.17100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.106</c:v>
+                  <c:v>0.121</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>7.3999999999999996E-2</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.73399999999999999</c:v>
+                  <c:v>0.57499999999999996</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.223</c:v>
+                  <c:v>0.46400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.54200000000000004</c:v>
+                  <c:v>0.53500000000000003</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.13800000000000001</c:v>
+                  <c:v>0.191</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>9.5000000000000001E-2</c:v>
+                  <c:v>0.14099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="76">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.28699999999999998</c:v>
+                  <c:v>0.47399999999999998</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.55300000000000005</c:v>
+                  <c:v>0.54500000000000004</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.82899999999999996</c:v>
+                  <c:v>0.76700000000000002</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>5.2999999999999999E-2</c:v>
+                  <c:v>0.111</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.255</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.17</c:v>
+                  <c:v>0.222</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.18</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.5</c:v>
+                  <c:v>0.58499999999999996</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.64800000000000002</c:v>
+                  <c:v>0.71699999999999997</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.34</c:v>
+                  <c:v>0.373</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.69099999999999995</c:v>
+                  <c:v>0.45400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.47799999999999998</c:v>
+                  <c:v>0.40400000000000003</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.85099999999999998</c:v>
+                  <c:v>0.52500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.32900000000000001</c:v>
+                  <c:v>0.28199999999999997</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>6.3E-2</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.71199999999999997</c:v>
+                  <c:v>0.60599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.127</c:v>
+                  <c:v>0.36299999999999999</c:v>
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>0</c:v>
@@ -840,283 +840,283 @@
                   <c:v>0.98899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.97799999999999998</c:v>
+                  <c:v>0.97899999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.96799999999999997</c:v>
+                  <c:v>0.96899999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.95699999999999996</c:v>
+                  <c:v>0.95899999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.94599999999999995</c:v>
+                  <c:v>0.94899999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.93600000000000005</c:v>
+                  <c:v>0.93899999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.92500000000000004</c:v>
+                  <c:v>0.92900000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.91400000000000003</c:v>
+                  <c:v>0.91900000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90400000000000003</c:v>
+                  <c:v>0.90900000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.89300000000000002</c:v>
+                  <c:v>0.89800000000000002</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.88200000000000001</c:v>
+                  <c:v>0.88800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.872</c:v>
+                  <c:v>0.878</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.86099999999999999</c:v>
+                  <c:v>0.86799999999999999</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.85099999999999998</c:v>
+                  <c:v>0.85799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.84</c:v>
+                  <c:v>0.84799999999999998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.82899999999999996</c:v>
+                  <c:v>0.83799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.81899999999999995</c:v>
+                  <c:v>0.82799999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>0.81799999999999995</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>0.80800000000000005</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>0.79700000000000004</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>0.78700000000000003</c:v>
                 </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.77600000000000002</c:v>
-                </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.76500000000000001</c:v>
+                  <c:v>0.77700000000000002</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.755</c:v>
+                  <c:v>0.76700000000000002</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.74399999999999999</c:v>
+                  <c:v>0.75700000000000001</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.73399999999999999</c:v>
+                  <c:v>0.747</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.72299999999999998</c:v>
+                  <c:v>0.73699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.71199999999999997</c:v>
+                  <c:v>0.72699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.70199999999999996</c:v>
+                  <c:v>0.71699999999999997</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.69099999999999995</c:v>
+                  <c:v>0.70699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.68</c:v>
+                  <c:v>0.69599999999999995</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.67</c:v>
+                  <c:v>0.68600000000000005</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.65900000000000003</c:v>
+                  <c:v>0.67600000000000005</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.64800000000000002</c:v>
+                  <c:v>0.66600000000000004</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.63800000000000001</c:v>
+                  <c:v>0.65600000000000003</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.627</c:v>
+                  <c:v>0.64600000000000002</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.61699999999999999</c:v>
+                  <c:v>0.63600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>0.626</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.61599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>0.60599999999999998</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>0.59499999999999997</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>0.58499999999999996</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>0.57399999999999995</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.56299999999999994</c:v>
-                </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.55300000000000005</c:v>
+                  <c:v>0.57499999999999996</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.54200000000000004</c:v>
+                  <c:v>0.56499999999999995</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.53100000000000003</c:v>
+                  <c:v>0.55500000000000005</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.52100000000000002</c:v>
+                  <c:v>0.54500000000000004</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.51</c:v>
+                  <c:v>0.53500000000000003</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.5</c:v>
+                  <c:v>0.52500000000000002</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.48899999999999999</c:v>
+                  <c:v>0.51500000000000001</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.47799999999999998</c:v>
+                  <c:v>0.505</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.46800000000000003</c:v>
+                  <c:v>0.49399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.45700000000000002</c:v>
+                  <c:v>0.48399999999999999</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.44600000000000001</c:v>
+                  <c:v>0.47399999999999998</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.436</c:v>
+                  <c:v>0.46400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.42499999999999999</c:v>
+                  <c:v>0.45400000000000001</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>0.44400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.434</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.42399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>0.41399999999999998</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="59">
                   <c:v>0.40400000000000003</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="60">
                   <c:v>0.39300000000000002</c:v>
                 </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.38200000000000001</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.372</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.36099999999999999</c:v>
-                </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.35099999999999998</c:v>
+                  <c:v>0.38300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.34</c:v>
+                  <c:v>0.373</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.32900000000000001</c:v>
+                  <c:v>0.36299999999999999</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.31900000000000001</c:v>
+                  <c:v>0.35299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.308</c:v>
+                  <c:v>0.34300000000000003</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.29699999999999999</c:v>
+                  <c:v>0.33300000000000002</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.28699999999999998</c:v>
+                  <c:v>0.32300000000000001</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.27600000000000002</c:v>
+                  <c:v>0.313</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.26500000000000001</c:v>
+                  <c:v>0.30299999999999999</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.255</c:v>
+                  <c:v>0.29199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.24399999999999999</c:v>
+                  <c:v>0.28199999999999997</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.23400000000000001</c:v>
+                  <c:v>0.27200000000000002</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.223</c:v>
+                  <c:v>0.26200000000000001</c:v>
                 </c:pt>
                 <c:pt idx="74">
+                  <c:v>0.252</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.24199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.23200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.222</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>0.21199999999999999</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="79">
                   <c:v>0.20200000000000001</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="80">
                   <c:v>0.191</c:v>
                 </c:pt>
-                <c:pt idx="77">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>0.17</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>0.159</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>0.14799999999999999</c:v>
-                </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.13800000000000001</c:v>
+                  <c:v>0.18099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.127</c:v>
+                  <c:v>0.17100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.11700000000000001</c:v>
+                  <c:v>0.161</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.106</c:v>
+                  <c:v>0.151</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>9.5000000000000001E-2</c:v>
+                  <c:v>0.14099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>8.5000000000000006E-2</c:v>
+                  <c:v>0.13100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>7.3999999999999996E-2</c:v>
+                  <c:v>0.121</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>6.3E-2</c:v>
+                  <c:v>0.111</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>5.2999999999999999E-2</c:v>
+                  <c:v>0.10100000000000001</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>4.2000000000000003E-2</c:v>
+                  <c:v>0.09</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>3.1E-2</c:v>
+                  <c:v>0.08</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2.1000000000000001E-2</c:v>
+                  <c:v>7.0000000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.01</c:v>
+                  <c:v>0.06</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0</c:v>
+                  <c:v>0.05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2347,7 +2347,7 @@
         <v>60</v>
       </c>
       <c r="C2">
-        <v>15702055</v>
+        <v>46318941</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2358,7 +2358,7 @@
         <v>49</v>
       </c>
       <c r="C3">
-        <v>12214971</v>
+        <v>32812130</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2366,10 +2366,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>9119649</v>
+        <v>31296159</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2380,7 +2380,7 @@
         <v>61</v>
       </c>
       <c r="C5">
-        <v>8611927</v>
+        <v>24142013</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2388,10 +2388,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>8401268</v>
+        <v>22248635</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2399,10 +2399,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>6311179</v>
+        <v>22013526</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2413,7 +2413,7 @@
         <v>62</v>
       </c>
       <c r="C8">
-        <v>6194536</v>
+        <v>21169959</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2421,10 +2421,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C9">
-        <v>6070432</v>
+        <v>20424390</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2435,7 +2435,7 @@
         <v>47</v>
       </c>
       <c r="C10">
-        <v>5827820</v>
+        <v>19685975</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -2443,10 +2443,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C11">
-        <v>5794630</v>
+        <v>18355231</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2454,10 +2454,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C12">
-        <v>5693755</v>
+        <v>17529050</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -2465,10 +2465,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="C13">
-        <v>5499645</v>
+        <v>17190104</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2476,10 +2476,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>5314806</v>
+        <v>17111381</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -2487,10 +2487,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C15">
-        <v>4992116</v>
+        <v>16902407</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -2498,10 +2498,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C16">
-        <v>4862491</v>
+        <v>15563050</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -2509,10 +2509,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C17">
-        <v>4792980</v>
+        <v>15478743</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -2520,10 +2520,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C18">
-        <v>4791169</v>
+        <v>15294087</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -2531,10 +2531,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19">
-        <v>4789200</v>
+        <v>14839783</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -2542,10 +2542,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="C20">
-        <v>4737953</v>
+        <v>14291841</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -2553,10 +2553,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C21">
-        <v>4714228</v>
+        <v>14223751</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -2564,10 +2564,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C22">
-        <v>4647868</v>
+        <v>13920528</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -2575,10 +2575,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="C23">
-        <v>4627335</v>
+        <v>13442603</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -2586,10 +2586,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C24">
-        <v>4546105</v>
+        <v>13439148</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -2597,10 +2597,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="C25">
-        <v>4365881</v>
+        <v>13428284</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -2608,10 +2608,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>4150745</v>
+        <v>13093528</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -2619,10 +2619,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C27">
-        <v>4150228</v>
+        <v>12630533</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -2630,10 +2630,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>4121213</v>
+        <v>12564284</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -2641,10 +2641,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="C29">
-        <v>4109114</v>
+        <v>12499765</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -2652,10 +2652,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>4088818</v>
+        <v>12455209</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -2663,10 +2663,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C31">
-        <v>4011219</v>
+        <v>12272519</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -2674,10 +2674,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="C32">
-        <v>3884630</v>
+        <v>11689720</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -2685,10 +2685,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C33">
-        <v>3826667</v>
+        <v>11653937</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -2696,10 +2696,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C34">
-        <v>3810506</v>
+        <v>11620650</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -2707,10 +2707,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C35">
-        <v>3804815</v>
+        <v>11490947</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -2718,10 +2718,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C36">
-        <v>3676403</v>
+        <v>11078731</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -2729,10 +2729,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C37">
-        <v>3643650</v>
+        <v>11060238</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
@@ -2740,10 +2740,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C38">
-        <v>3641493</v>
+        <v>10830556</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -2751,10 +2751,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C39">
-        <v>3509465</v>
+        <v>10744985</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -2762,10 +2762,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C40">
-        <v>3491725</v>
+        <v>10724460</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -2773,10 +2773,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C41">
-        <v>3433393</v>
+        <v>10504976</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -2784,10 +2784,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="C42">
-        <v>3370400</v>
+        <v>10494315</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -2795,10 +2795,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="C43">
-        <v>3363330</v>
+        <v>10492307</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -2806,10 +2806,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C44">
-        <v>3307184</v>
+        <v>10327056</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
@@ -2817,10 +2817,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C45">
-        <v>3198516</v>
+        <v>10218996</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
@@ -2828,10 +2828,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46">
-        <v>3185355</v>
+        <v>9886132</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -2839,10 +2839,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C47">
-        <v>3176420</v>
+        <v>9846771</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -2850,10 +2850,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="C48">
-        <v>3160555</v>
+        <v>9789935</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -2861,10 +2861,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>3135488</v>
+        <v>9693854</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
@@ -2872,10 +2872,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C50">
-        <v>3089205</v>
+        <v>9567967</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -2883,10 +2883,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C51">
-        <v>3087825</v>
+        <v>9472278</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -2894,10 +2894,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C52">
-        <v>3068419</v>
+        <v>9428270</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
@@ -2905,10 +2905,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>2871198</v>
+        <v>9052808</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -2916,10 +2916,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C54">
-        <v>2853030</v>
+        <v>8767712</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -2927,10 +2927,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C55">
-        <v>2851320</v>
+        <v>8547509</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -2938,10 +2938,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C56">
-        <v>2849850</v>
+        <v>8301520</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
@@ -2949,10 +2949,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C57">
-        <v>2766515</v>
+        <v>8216150</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -2960,10 +2960,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>2722105</v>
+        <v>8108164</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
@@ -2971,10 +2971,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>2644035</v>
+        <v>7884924</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
@@ -2982,10 +2982,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C60">
-        <v>2640978</v>
+        <v>7827370</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -2993,10 +2993,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="C61">
-        <v>2592515</v>
+        <v>7813730</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -3004,10 +3004,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C62">
-        <v>2356849</v>
+        <v>7655584</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -3015,10 +3015,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>2342828</v>
+        <v>7534602</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
@@ -3026,10 +3026,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="C64">
-        <v>2321953</v>
+        <v>7434459</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -3037,10 +3037,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C65">
-        <v>2315865</v>
+        <v>7049198</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
@@ -3048,10 +3048,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C66">
-        <v>2315507</v>
+        <v>6760958</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -3059,10 +3059,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C67">
-        <v>2305405</v>
+        <v>6657628</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -3070,10 +3070,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>2217385</v>
+        <v>6495479</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -3081,10 +3081,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C69">
-        <v>2192925</v>
+        <v>6352421</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -3092,10 +3092,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C70">
-        <v>2158459</v>
+        <v>6347132</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
@@ -3103,10 +3103,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C71">
-        <v>2075935</v>
+        <v>6227502</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -3114,10 +3114,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="C72">
-        <v>2071567</v>
+        <v>6177225</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -3125,10 +3125,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>2034260</v>
+        <v>6060071</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
@@ -3136,10 +3136,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="C74">
-        <v>2025230</v>
+        <v>5928006</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -3147,10 +3147,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C75">
-        <v>2024897</v>
+        <v>5809095</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -3158,10 +3158,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C76">
-        <v>1976858</v>
+        <v>5204952</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -3169,10 +3169,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C77">
-        <v>1936160</v>
+        <v>4627335</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
@@ -3180,10 +3180,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C78">
-        <v>1911772</v>
+        <v>4579265</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -3191,10 +3191,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C79">
-        <v>1784180</v>
+        <v>4368383</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
@@ -3202,10 +3202,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="C80">
-        <v>1768410</v>
+        <v>4016198</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
@@ -3213,10 +3213,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>1649135</v>
+        <v>3968405</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -3224,10 +3224,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="C82">
-        <v>1610065</v>
+        <v>3938443</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -3235,10 +3235,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C83">
-        <v>1544400</v>
+        <v>3804815</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -3249,7 +3249,7 @@
         <v>92</v>
       </c>
       <c r="C84">
-        <v>1523733</v>
+        <v>3769888</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
@@ -3257,10 +3257,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C85">
-        <v>1437938</v>
+        <v>3548963</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -3268,10 +3268,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="C86">
-        <v>1152085</v>
+        <v>3317180</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
@@ -3279,10 +3279,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C87">
-        <v>1109645</v>
+        <v>3265579</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
@@ -3293,7 +3293,7 @@
         <v>93</v>
       </c>
       <c r="C88">
-        <v>1014383</v>
+        <v>3155370</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -3301,10 +3301,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C89">
-        <v>959715</v>
+        <v>3081809</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -3312,10 +3312,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C90">
-        <v>935625</v>
+        <v>2549147</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -3323,10 +3323,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C91">
-        <v>922725</v>
+        <v>2217385</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
@@ -3334,10 +3334,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C92">
-        <v>894740</v>
+        <v>2025230</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -3345,10 +3345,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C93">
-        <v>885310</v>
+        <v>1988150</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3356,10 +3356,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="C94">
-        <v>701850</v>
+        <v>1848861</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
@@ -3367,10 +3367,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C95">
-        <v>692004</v>
+        <v>1649135</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -3378,10 +3378,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C96">
-        <v>548600</v>
+        <v>1513550</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -3389,10 +3389,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C97">
-        <v>531480</v>
+        <v>629900</v>
       </c>
     </row>
   </sheetData>
@@ -4564,19 +4564,19 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <f>VLOOKUP(A2,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>15702055</v>
+        <f>VLOOKUP(A2,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>46318941</v>
       </c>
       <c r="C2">
         <f>VLOOKUP(A2,power!$B$2:$C$101,2,FALSE)</f>
         <v>42986788</v>
       </c>
       <c r="E2" s="5">
-        <f>PERCENTRANK(B$2:B$96,B2)</f>
+        <f>PERCENTRANK(B$2:B$101,B2)</f>
         <v>1</v>
       </c>
       <c r="F2" s="5">
-        <f>PERCENTRANK(C$2:C$96,C2)</f>
+        <f>PERCENTRANK(C$2:C$101,C2)</f>
         <v>1</v>
       </c>
       <c r="H2" s="3">
@@ -4589,24 +4589,24 @@
         <v>63</v>
       </c>
       <c r="B3">
-        <f>VLOOKUP(A3,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>5794630</v>
+        <f>VLOOKUP(A3,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>22013526</v>
       </c>
       <c r="C3">
         <f>VLOOKUP(A3,power!$B$2:$C$101,2,FALSE)</f>
         <v>38451162</v>
       </c>
       <c r="E3" s="5">
-        <f t="shared" ref="E3:E66" si="1">PERCENTRANK(B$2:B$96,B3)</f>
-        <v>0.90400000000000003</v>
+        <f t="shared" ref="E3:E66" si="1">PERCENTRANK(B$2:B$101,B3)</f>
+        <v>0.94899999999999995</v>
       </c>
       <c r="F3" s="5">
-        <f t="shared" ref="F3:F66" si="2">PERCENTRANK(C$2:C$96,C3)</f>
+        <f t="shared" ref="F3:F66" si="2">PERCENTRANK(C$2:C$101,C3)</f>
         <v>0.98899999999999999</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" si="0"/>
-        <v>8940.56</v>
+        <v>9385.61</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -4614,8 +4614,8 @@
         <v>66</v>
       </c>
       <c r="B4">
-        <f>VLOOKUP(A4,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4737953</v>
+        <f>VLOOKUP(A4,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11653937</v>
       </c>
       <c r="C4">
         <f>VLOOKUP(A4,power!$B$2:$C$101,2,FALSE)</f>
@@ -4623,15 +4623,15 @@
       </c>
       <c r="E4" s="5">
         <f t="shared" si="1"/>
-        <v>0.80800000000000005</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="F4" s="5">
         <f t="shared" si="2"/>
-        <v>0.97799999999999998</v>
+        <v>0.97899999999999998</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" si="0"/>
-        <v>7902.2400000000007</v>
+        <v>6715.9400000000005</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -4639,8 +4639,8 @@
         <v>50</v>
       </c>
       <c r="B5">
-        <f>VLOOKUP(A5,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>8401268</v>
+        <f>VLOOKUP(A5,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>31296159</v>
       </c>
       <c r="C5">
         <f>VLOOKUP(A5,power!$B$2:$C$101,2,FALSE)</f>
@@ -4648,15 +4648,15 @@
       </c>
       <c r="E5" s="5">
         <f t="shared" si="1"/>
-        <v>0.95699999999999996</v>
+        <v>0.97899999999999998</v>
       </c>
       <c r="F5" s="5">
         <f t="shared" si="2"/>
-        <v>0.96799999999999997</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>9263.76</v>
+        <v>9486.5099999999984</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -4664,7 +4664,7 @@
         <v>69</v>
       </c>
       <c r="B6">
-        <f>VLOOKUP(A6,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <f>VLOOKUP(A6,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
         <v>4627335</v>
       </c>
       <c r="C6">
@@ -4673,15 +4673,15 @@
       </c>
       <c r="E6" s="5">
         <f t="shared" si="1"/>
-        <v>0.77600000000000002</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="F6" s="5">
         <f t="shared" si="2"/>
-        <v>0.95699999999999996</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" si="0"/>
-        <v>7426.32</v>
+        <v>2320.7799999999997</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -4689,8 +4689,8 @@
         <v>36</v>
       </c>
       <c r="B7">
-        <f>VLOOKUP(A7,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3641493</v>
+        <f>VLOOKUP(A7,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>13442603</v>
       </c>
       <c r="C7">
         <f>VLOOKUP(A7,power!$B$2:$C$101,2,FALSE)</f>
@@ -4698,15 +4698,15 @@
       </c>
       <c r="E7" s="5">
         <f t="shared" si="1"/>
-        <v>0.627</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="F7" s="5">
         <f t="shared" si="2"/>
-        <v>0.94599999999999995</v>
+        <v>0.94899999999999995</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" si="0"/>
-        <v>5931.4199999999992</v>
+        <v>7468.6299999999992</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -4714,8 +4714,8 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <f>VLOOKUP(A8,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2644035</v>
+        <f>VLOOKUP(A8,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10724460</v>
       </c>
       <c r="C8">
         <f>VLOOKUP(A8,power!$B$2:$C$101,2,FALSE)</f>
@@ -4723,15 +4723,15 @@
       </c>
       <c r="E8" s="5">
         <f t="shared" si="1"/>
-        <v>0.41399999999999998</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="F8" s="5">
         <f t="shared" si="2"/>
-        <v>0.93600000000000005</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" si="0"/>
-        <v>3875.04</v>
+        <v>5784.24</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -4739,8 +4739,8 @@
         <v>74</v>
       </c>
       <c r="B9">
-        <f>VLOOKUP(A9,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3491725</v>
+        <f>VLOOKUP(A9,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>14223751</v>
       </c>
       <c r="C9">
         <f>VLOOKUP(A9,power!$B$2:$C$101,2,FALSE)</f>
@@ -4748,15 +4748,15 @@
       </c>
       <c r="E9" s="5">
         <f t="shared" si="1"/>
-        <v>0.60599999999999998</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F9" s="5">
         <f t="shared" si="2"/>
-        <v>0.92500000000000004</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>5605.5</v>
+        <v>7506.3200000000006</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -4764,8 +4764,8 @@
         <v>61</v>
       </c>
       <c r="B10">
-        <f>VLOOKUP(A10,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>8611927</v>
+        <f>VLOOKUP(A10,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>24142013</v>
       </c>
       <c r="C10">
         <f>VLOOKUP(A10,power!$B$2:$C$101,2,FALSE)</f>
@@ -4773,15 +4773,15 @@
       </c>
       <c r="E10" s="5">
         <f t="shared" si="1"/>
-        <v>0.96799999999999997</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="F10" s="5">
         <f t="shared" si="2"/>
-        <v>0.91400000000000003</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="0"/>
-        <v>8847.52</v>
+        <v>8905.11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="F11" s="5">
         <f t="shared" si="2"/>
-        <v>0.90400000000000003</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="0"/>
@@ -4813,8 +4813,8 @@
         <v>40</v>
       </c>
       <c r="B12">
-        <f>VLOOKUP(A12,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2853030</v>
+        <f>VLOOKUP(A12,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12630533</v>
       </c>
       <c r="C12">
         <f>VLOOKUP(A12,power!$B$2:$C$101,2,FALSE)</f>
@@ -4822,15 +4822,15 @@
       </c>
       <c r="E12" s="5">
         <f t="shared" si="1"/>
-        <v>0.45700000000000002</v>
+        <v>0.747</v>
       </c>
       <c r="F12" s="5">
         <f t="shared" si="2"/>
-        <v>0.89300000000000002</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="0"/>
-        <v>4081.0100000000007</v>
+        <v>6708.06</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -4838,8 +4838,8 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <f>VLOOKUP(A13,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>6070432</v>
+        <f>VLOOKUP(A13,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>13920528</v>
       </c>
       <c r="C13">
         <f>VLOOKUP(A13,power!$B$2:$C$101,2,FALSE)</f>
@@ -4847,15 +4847,15 @@
       </c>
       <c r="E13" s="5">
         <f t="shared" si="1"/>
-        <v>0.92500000000000004</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="F13" s="5">
         <f t="shared" si="2"/>
-        <v>0.88200000000000001</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
-        <v>8158.5000000000009</v>
+        <v>7077.3600000000006</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -4863,8 +4863,8 @@
         <v>77</v>
       </c>
       <c r="B14">
-        <f>VLOOKUP(A14,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3087825</v>
+        <f>VLOOKUP(A14,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>15478743</v>
       </c>
       <c r="C14">
         <f>VLOOKUP(A14,power!$B$2:$C$101,2,FALSE)</f>
@@ -4872,15 +4872,15 @@
       </c>
       <c r="E14" s="5">
         <f t="shared" si="1"/>
-        <v>0.48899999999999999</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="F14" s="5">
         <f t="shared" si="2"/>
-        <v>0.872</v>
+        <v>0.878</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>4264.08</v>
+        <v>7445.44</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4888,8 +4888,8 @@
         <v>33</v>
       </c>
       <c r="B15">
-        <f>VLOOKUP(A15,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3810506</v>
+        <f>VLOOKUP(A15,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9886132</v>
       </c>
       <c r="C15">
         <f>VLOOKUP(A15,power!$B$2:$C$101,2,FALSE)</f>
@@ -4897,15 +4897,15 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>0.67</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="2"/>
-        <v>0.86099999999999999</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="H15" s="3">
         <f t="shared" si="0"/>
-        <v>5768.7</v>
+        <v>4817.4000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -4913,8 +4913,8 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <f>VLOOKUP(A16,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3826667</v>
+        <f>VLOOKUP(A16,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12564284</v>
       </c>
       <c r="C16">
         <f>VLOOKUP(A16,power!$B$2:$C$101,2,FALSE)</f>
@@ -4922,15 +4922,15 @@
       </c>
       <c r="E16" s="5">
         <f t="shared" si="1"/>
-        <v>0.68</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="F16" s="5">
         <f t="shared" si="2"/>
-        <v>0.85099999999999998</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="H16" s="3">
         <f t="shared" si="0"/>
-        <v>5786.7999999999993</v>
+        <v>6323.46</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -4938,8 +4938,8 @@
         <v>75</v>
       </c>
       <c r="B17">
-        <f>VLOOKUP(A17,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3363330</v>
+        <f>VLOOKUP(A17,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10744985</v>
       </c>
       <c r="C17">
         <f>VLOOKUP(A17,power!$B$2:$C$101,2,FALSE)</f>
@@ -4947,15 +4947,15 @@
       </c>
       <c r="E17" s="5">
         <f t="shared" si="1"/>
-        <v>0.57399999999999995</v>
+        <v>0.626</v>
       </c>
       <c r="F17" s="5">
         <f t="shared" si="2"/>
-        <v>0.84</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="H17" s="3">
         <f t="shared" si="0"/>
-        <v>4821.5999999999995</v>
+        <v>5308.48</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -4963,8 +4963,8 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <f>VLOOKUP(A18,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4546105</v>
+        <f>VLOOKUP(A18,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11689720</v>
       </c>
       <c r="C18">
         <f>VLOOKUP(A18,power!$B$2:$C$101,2,FALSE)</f>
@@ -4972,15 +4972,15 @@
       </c>
       <c r="E18" s="5">
         <f t="shared" si="1"/>
-        <v>0.76500000000000001</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F18" s="5">
         <f t="shared" si="2"/>
-        <v>0.82899999999999996</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="H18" s="3">
         <f t="shared" si="0"/>
-        <v>6341.85</v>
+        <v>5832.48</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -4988,8 +4988,8 @@
         <v>1</v>
       </c>
       <c r="B19">
-        <f>VLOOKUP(A19,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>5499645</v>
+        <f>VLOOKUP(A19,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>17111381</v>
       </c>
       <c r="C19">
         <f>VLOOKUP(A19,power!$B$2:$C$101,2,FALSE)</f>
@@ -4997,15 +4997,15 @@
       </c>
       <c r="E19" s="5">
         <f t="shared" si="1"/>
-        <v>0.88200000000000001</v>
+        <v>0.878</v>
       </c>
       <c r="F19" s="5">
         <f t="shared" si="2"/>
-        <v>0.81899999999999995</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="H19" s="3">
         <f t="shared" si="0"/>
-        <v>7223.579999999999</v>
+        <v>7269.8399999999992</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -5013,8 +5013,8 @@
         <v>64</v>
       </c>
       <c r="B20">
-        <f>VLOOKUP(A20,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4792980</v>
+        <f>VLOOKUP(A20,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>17529050</v>
       </c>
       <c r="C20">
         <f>VLOOKUP(A20,power!$B$2:$C$101,2,FALSE)</f>
@@ -5022,15 +5022,15 @@
       </c>
       <c r="E20" s="5">
         <f t="shared" si="1"/>
-        <v>0.84</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="F20" s="5">
         <f t="shared" si="2"/>
-        <v>0.80800000000000005</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="H20" s="3">
         <f t="shared" si="0"/>
-        <v>6787.2</v>
+        <v>7345.64</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -5038,8 +5038,8 @@
         <v>49</v>
       </c>
       <c r="B21">
-        <f>VLOOKUP(A21,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>12214971</v>
+        <f>VLOOKUP(A21,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>32812130</v>
       </c>
       <c r="C21">
         <f>VLOOKUP(A21,power!$B$2:$C$101,2,FALSE)</f>
@@ -5051,11 +5051,11 @@
       </c>
       <c r="F21" s="5">
         <f t="shared" si="2"/>
-        <v>0.79700000000000004</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="H21" s="3">
         <f t="shared" si="0"/>
-        <v>7882.3300000000008</v>
+        <v>7991.1200000000008</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -5063,8 +5063,8 @@
         <v>52</v>
       </c>
       <c r="B22">
-        <f>VLOOKUP(A22,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3176420</v>
+        <f>VLOOKUP(A22,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10830556</v>
       </c>
       <c r="C22">
         <f>VLOOKUP(A22,power!$B$2:$C$101,2,FALSE)</f>
@@ -5072,15 +5072,15 @@
       </c>
       <c r="E22" s="5">
         <f t="shared" si="1"/>
-        <v>0.53100000000000003</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="F22" s="5">
         <f t="shared" si="2"/>
-        <v>0.78700000000000003</v>
+        <v>0.79700000000000004</v>
       </c>
       <c r="H22" s="3">
         <f t="shared" si="0"/>
-        <v>4178.97</v>
+        <v>5068.92</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -5088,8 +5088,8 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <f>VLOOKUP(A23,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2158459</v>
+        <f>VLOOKUP(A23,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6657628</v>
       </c>
       <c r="C23">
         <f>VLOOKUP(A23,power!$B$2:$C$101,2,FALSE)</f>
@@ -5097,15 +5097,15 @@
       </c>
       <c r="E23" s="5">
         <f t="shared" si="1"/>
-        <v>0.29699999999999999</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="F23" s="5">
         <f t="shared" si="2"/>
-        <v>0.77600000000000002</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="H23" s="3">
         <f t="shared" si="0"/>
-        <v>2304.7199999999998</v>
+        <v>2699.4100000000003</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -5113,8 +5113,8 @@
         <v>21</v>
       </c>
       <c r="B24">
-        <f>VLOOKUP(A24,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2356849</v>
+        <f>VLOOKUP(A24,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7534602</v>
       </c>
       <c r="C24">
         <f>VLOOKUP(A24,power!$B$2:$C$101,2,FALSE)</f>
@@ -5122,15 +5122,15 @@
       </c>
       <c r="E24" s="5">
         <f t="shared" si="1"/>
-        <v>0.38200000000000001</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F24" s="5">
         <f t="shared" si="2"/>
-        <v>0.76500000000000001</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="H24" s="3">
         <f t="shared" si="0"/>
-        <v>2922.2999999999997</v>
+        <v>2975.91</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
@@ -5138,8 +5138,8 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <f>VLOOKUP(A25,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4150745</v>
+        <f>VLOOKUP(A25,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11060238</v>
       </c>
       <c r="C25">
         <f>VLOOKUP(A25,power!$B$2:$C$101,2,FALSE)</f>
@@ -5147,15 +5147,15 @@
       </c>
       <c r="E25" s="5">
         <f t="shared" si="1"/>
-        <v>0.74399999999999999</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="F25" s="5">
         <f t="shared" si="2"/>
-        <v>0.755</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="H25" s="3">
         <f t="shared" si="0"/>
-        <v>5617.2</v>
+        <v>4954.8200000000006</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -5163,8 +5163,8 @@
         <v>19</v>
       </c>
       <c r="B26">
-        <f>VLOOKUP(A26,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4992116</v>
+        <f>VLOOKUP(A26,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11620650</v>
       </c>
       <c r="C26">
         <f>VLOOKUP(A26,power!$B$2:$C$101,2,FALSE)</f>
@@ -5172,15 +5172,15 @@
       </c>
       <c r="E26" s="5">
         <f t="shared" si="1"/>
-        <v>0.86099999999999999</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="F26" s="5">
         <f t="shared" si="2"/>
-        <v>0.74399999999999999</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="H26" s="3">
         <f t="shared" si="0"/>
-        <v>6405.8399999999992</v>
+        <v>5117.3200000000006</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -5188,8 +5188,8 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <f>VLOOKUP(A27,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>6311179</v>
+        <f>VLOOKUP(A27,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>15563050</v>
       </c>
       <c r="C27">
         <f>VLOOKUP(A27,power!$B$2:$C$101,2,FALSE)</f>
@@ -5197,15 +5197,15 @@
       </c>
       <c r="E27" s="5">
         <f t="shared" si="1"/>
-        <v>0.94599999999999995</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="F27" s="5">
         <f t="shared" si="2"/>
-        <v>0.73399999999999999</v>
+        <v>0.747</v>
       </c>
       <c r="H27" s="3">
         <f t="shared" si="0"/>
-        <v>6943.6399999999994</v>
+        <v>6409.26</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -5213,8 +5213,8 @@
         <v>43</v>
       </c>
       <c r="B28">
-        <f>VLOOKUP(A28,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>9119649</v>
+        <f>VLOOKUP(A28,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>20424390</v>
       </c>
       <c r="C28">
         <f>VLOOKUP(A28,power!$B$2:$C$101,2,FALSE)</f>
@@ -5222,15 +5222,15 @@
       </c>
       <c r="E28" s="5">
         <f t="shared" si="1"/>
-        <v>0.97799999999999998</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="F28" s="5">
         <f t="shared" si="2"/>
-        <v>0.72299999999999998</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="H28" s="3">
         <f t="shared" si="0"/>
-        <v>7070.94</v>
+        <v>6846.73</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -5238,8 +5238,8 @@
         <v>5</v>
       </c>
       <c r="B29">
-        <f>VLOOKUP(A29,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2592515</v>
+        <f>VLOOKUP(A29,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6495479</v>
       </c>
       <c r="C29">
         <f>VLOOKUP(A29,power!$B$2:$C$101,2,FALSE)</f>
@@ -5247,15 +5247,15 @@
       </c>
       <c r="E29" s="5">
         <f t="shared" si="1"/>
-        <v>0.39300000000000002</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="F29" s="5">
         <f t="shared" si="2"/>
-        <v>0.71199999999999997</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="H29" s="3">
         <f t="shared" si="0"/>
-        <v>2798.1600000000003</v>
+        <v>2420.91</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -5263,8 +5263,8 @@
         <v>83</v>
       </c>
       <c r="B30">
-        <f>VLOOKUP(A30,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2192925</v>
+        <f>VLOOKUP(A30,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10494315</v>
       </c>
       <c r="C30">
         <f>VLOOKUP(A30,power!$B$2:$C$101,2,FALSE)</f>
@@ -5272,15 +5272,15 @@
       </c>
       <c r="E30" s="5">
         <f t="shared" si="1"/>
-        <v>0.308</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="F30" s="5">
         <f t="shared" si="2"/>
-        <v>0.70199999999999996</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="H30" s="3">
         <f t="shared" si="0"/>
-        <v>2162.16</v>
+        <v>4266.1499999999996</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -5288,8 +5288,8 @@
         <v>68</v>
       </c>
       <c r="B31">
-        <f>VLOOKUP(A31,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4647868</v>
+        <f>VLOOKUP(A31,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>17190104</v>
       </c>
       <c r="C31">
         <f>VLOOKUP(A31,power!$B$2:$C$101,2,FALSE)</f>
@@ -5297,15 +5297,15 @@
       </c>
       <c r="E31" s="5">
         <f t="shared" si="1"/>
-        <v>0.78700000000000003</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="F31" s="5">
         <f t="shared" si="2"/>
-        <v>0.69099999999999995</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="0"/>
-        <v>5438.17</v>
+        <v>6278.1599999999989</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -5313,8 +5313,8 @@
         <v>101</v>
       </c>
       <c r="B32">
-        <f>VLOOKUP(A32,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2342828</v>
+        <f>VLOOKUP(A32,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12499765</v>
       </c>
       <c r="C32">
         <f>VLOOKUP(A32,power!$B$2:$C$101,2,FALSE)</f>
@@ -5322,15 +5322,15 @@
       </c>
       <c r="E32" s="5">
         <f t="shared" si="1"/>
-        <v>0.372</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="F32" s="5">
         <f t="shared" si="2"/>
-        <v>0.68</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="H32" s="3">
         <f t="shared" si="0"/>
-        <v>2529.6000000000004</v>
+        <v>5059.92</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -5338,8 +5338,8 @@
         <v>30</v>
       </c>
       <c r="B33">
-        <f>VLOOKUP(A33,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1768410</v>
+        <f>VLOOKUP(A33,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6760958</v>
       </c>
       <c r="C33">
         <f>VLOOKUP(A33,power!$B$2:$C$101,2,FALSE)</f>
@@ -5347,15 +5347,15 @@
       </c>
       <c r="E33" s="5">
         <f t="shared" si="1"/>
-        <v>0.191</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="F33" s="5">
         <f t="shared" si="2"/>
-        <v>0.67</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="0"/>
-        <v>1279.7</v>
+        <v>2421.58</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -5363,8 +5363,8 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <f>VLOOKUP(A34,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3509465</v>
+        <f>VLOOKUP(A34,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12272519</v>
       </c>
       <c r="C34">
         <f>VLOOKUP(A34,power!$B$2:$C$101,2,FALSE)</f>
@@ -5372,15 +5372,15 @@
       </c>
       <c r="E34" s="5">
         <f t="shared" si="1"/>
-        <v>0.61699999999999999</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="F34" s="5">
         <f t="shared" si="2"/>
-        <v>0.65900000000000003</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="H34" s="3">
         <f t="shared" si="0"/>
-        <v>4066.0299999999997</v>
+        <v>4779.3200000000006</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -5388,8 +5388,8 @@
         <v>72</v>
       </c>
       <c r="B35">
-        <f>VLOOKUP(A35,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4011219</v>
+        <f>VLOOKUP(A35,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5809095</v>
       </c>
       <c r="C35">
         <f>VLOOKUP(A35,power!$B$2:$C$101,2,FALSE)</f>
@@ -5397,15 +5397,15 @@
       </c>
       <c r="E35" s="5">
         <f t="shared" si="1"/>
-        <v>0.70199999999999996</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="2"/>
-        <v>0.64800000000000002</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="H35" s="3">
         <f t="shared" si="0"/>
-        <v>4548.96</v>
+        <v>1744.92</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -5413,8 +5413,8 @@
         <v>67</v>
       </c>
       <c r="B36">
-        <f>VLOOKUP(A36,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4714228</v>
+        <f>VLOOKUP(A36,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>22248635</v>
       </c>
       <c r="C36">
         <f>VLOOKUP(A36,power!$B$2:$C$101,2,FALSE)</f>
@@ -5422,15 +5422,15 @@
       </c>
       <c r="E36" s="5">
         <f t="shared" si="1"/>
-        <v>0.79700000000000004</v>
+        <v>0.95899999999999996</v>
       </c>
       <c r="F36" s="5">
         <f t="shared" si="2"/>
-        <v>0.63800000000000001</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="H36" s="3">
         <f t="shared" si="0"/>
-        <v>5084.8599999999997</v>
+        <v>6291.04</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -5438,8 +5438,8 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <f>VLOOKUP(A37,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3307184</v>
+        <f>VLOOKUP(A37,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>14839783</v>
       </c>
       <c r="C37">
         <f>VLOOKUP(A37,power!$B$2:$C$101,2,FALSE)</f>
@@ -5447,15 +5447,15 @@
       </c>
       <c r="E37" s="5">
         <f t="shared" si="1"/>
-        <v>0.56299999999999994</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="F37" s="5">
         <f t="shared" si="2"/>
-        <v>0.627</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="H37" s="3">
         <f t="shared" si="0"/>
-        <v>3530.0099999999998</v>
+        <v>5348.88</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -5463,8 +5463,8 @@
         <v>2</v>
       </c>
       <c r="B38">
-        <f>VLOOKUP(A38,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1437938</v>
+        <f>VLOOKUP(A38,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3968405</v>
       </c>
       <c r="C38">
         <f>VLOOKUP(A38,power!$B$2:$C$101,2,FALSE)</f>
@@ -5472,15 +5472,15 @@
       </c>
       <c r="E38" s="5">
         <f t="shared" si="1"/>
-        <v>0.14799999999999999</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="F38" s="5">
         <f t="shared" si="2"/>
-        <v>0.61699999999999999</v>
+        <v>0.63600000000000001</v>
       </c>
       <c r="H38" s="3">
         <f t="shared" si="0"/>
-        <v>913.16</v>
+        <v>1284.72</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -5488,8 +5488,8 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <f>VLOOKUP(A39,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1911772</v>
+        <f>VLOOKUP(A39,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9567967</v>
       </c>
       <c r="C39">
         <f>VLOOKUP(A39,power!$B$2:$C$101,2,FALSE)</f>
@@ -5497,15 +5497,15 @@
       </c>
       <c r="E39" s="5">
         <f t="shared" si="1"/>
-        <v>0.21199999999999999</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="F39" s="5">
         <f t="shared" si="2"/>
-        <v>0.60599999999999998</v>
+        <v>0.626</v>
       </c>
       <c r="H39" s="3">
         <f t="shared" si="0"/>
-        <v>1284.72</v>
+        <v>3223.9</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -5513,8 +5513,8 @@
         <v>86</v>
       </c>
       <c r="B40">
-        <f>VLOOKUP(A40,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2024897</v>
+        <f>VLOOKUP(A40,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6347132</v>
       </c>
       <c r="C40">
         <f>VLOOKUP(A40,power!$B$2:$C$101,2,FALSE)</f>
@@ -5522,15 +5522,15 @@
       </c>
       <c r="E40" s="5">
         <f t="shared" si="1"/>
-        <v>0.24399999999999999</v>
+        <v>0.313</v>
       </c>
       <c r="F40" s="5">
         <f t="shared" si="2"/>
-        <v>0.59499999999999997</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="H40" s="3">
         <f t="shared" si="0"/>
-        <v>1451.8</v>
+        <v>1928.0800000000002</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -5538,7 +5538,7 @@
         <v>102</v>
       </c>
       <c r="B41">
-        <f>VLOOKUP(A41,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <f>VLOOKUP(A41,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
         <v>3804815</v>
       </c>
       <c r="C41">
@@ -5547,15 +5547,15 @@
       </c>
       <c r="E41" s="5">
         <f t="shared" si="1"/>
-        <v>0.65900000000000003</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="F41" s="5">
         <f t="shared" si="2"/>
-        <v>0.58499999999999996</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H41" s="3">
         <f t="shared" si="0"/>
-        <v>3855.15</v>
+        <v>1096.8599999999999</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -5563,8 +5563,8 @@
         <v>80</v>
       </c>
       <c r="B42">
-        <f>VLOOKUP(A42,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2722105</v>
+        <f>VLOOKUP(A42,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11490947</v>
       </c>
       <c r="C42">
         <f>VLOOKUP(A42,power!$B$2:$C$101,2,FALSE)</f>
@@ -5572,15 +5572,15 @@
       </c>
       <c r="E42" s="5">
         <f t="shared" si="1"/>
-        <v>0.42499999999999999</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="F42" s="5">
         <f t="shared" si="2"/>
-        <v>0.57399999999999995</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="H42" s="3">
         <f t="shared" si="0"/>
-        <v>2439.4999999999995</v>
+        <v>3962.7000000000003</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="F43" s="5">
         <f t="shared" si="2"/>
-        <v>0.56299999999999994</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="H43" s="3">
         <f t="shared" si="0"/>
@@ -5612,8 +5612,8 @@
         <v>11</v>
       </c>
       <c r="B44">
-        <f>VLOOKUP(A44,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2034260</v>
+        <f>VLOOKUP(A44,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4579265</v>
       </c>
       <c r="C44">
         <f>VLOOKUP(A44,power!$B$2:$C$101,2,FALSE)</f>
@@ -5621,15 +5621,15 @@
       </c>
       <c r="E44" s="5">
         <f t="shared" si="1"/>
-        <v>0.26500000000000001</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="F44" s="5">
         <f t="shared" si="2"/>
-        <v>0.55300000000000005</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H44" s="3">
         <f t="shared" si="0"/>
-        <v>1465.45</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
@@ -5637,8 +5637,8 @@
         <v>17</v>
       </c>
       <c r="B45">
-        <f>VLOOKUP(A45,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2851320</v>
+        <f>VLOOKUP(A45,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9428270</v>
       </c>
       <c r="C45">
         <f>VLOOKUP(A45,power!$B$2:$C$101,2,FALSE)</f>
@@ -5646,15 +5646,15 @@
       </c>
       <c r="E45" s="5">
         <f t="shared" si="1"/>
-        <v>0.44600000000000001</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="F45" s="5">
         <f t="shared" si="2"/>
-        <v>0.54200000000000004</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="H45" s="3">
         <f t="shared" si="0"/>
-        <v>2417.3200000000002</v>
+        <v>2791.1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
@@ -5662,8 +5662,8 @@
         <v>99</v>
       </c>
       <c r="B46">
-        <f>VLOOKUP(A46,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>531480</v>
+        <f>VLOOKUP(A46,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3317180</v>
       </c>
       <c r="C46">
         <f>VLOOKUP(A46,power!$B$2:$C$101,2,FALSE)</f>
@@ -5671,15 +5671,15 @@
       </c>
       <c r="E46" s="5">
         <f t="shared" si="1"/>
-        <v>4.2000000000000003E-2</v>
+        <v>0.151</v>
       </c>
       <c r="F46" s="5">
         <f t="shared" si="2"/>
-        <v>0.53100000000000003</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="H46" s="3">
         <f t="shared" si="0"/>
-        <v>223.02</v>
+        <v>838.05000000000007</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
@@ -5687,8 +5687,8 @@
         <v>95</v>
       </c>
       <c r="B47">
-        <f>VLOOKUP(A47,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>894740</v>
+        <f>VLOOKUP(A47,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4016198</v>
       </c>
       <c r="C47">
         <f>VLOOKUP(A47,power!$B$2:$C$101,2,FALSE)</f>
@@ -5696,15 +5696,15 @@
       </c>
       <c r="E47" s="5">
         <f t="shared" si="1"/>
-        <v>8.5000000000000006E-2</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="F47" s="5">
         <f t="shared" si="2"/>
-        <v>0.52100000000000002</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H47" s="3">
         <f t="shared" si="0"/>
-        <v>442.85</v>
+        <v>1155.4000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -5712,8 +5712,8 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <f>VLOOKUP(A48,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>5827820</v>
+        <f>VLOOKUP(A48,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>19685975</v>
       </c>
       <c r="C48">
         <f>VLOOKUP(A48,power!$B$2:$C$101,2,FALSE)</f>
@@ -5721,15 +5721,15 @@
       </c>
       <c r="E48" s="5">
         <f t="shared" si="1"/>
-        <v>0.91400000000000003</v>
+        <v>0.91900000000000004</v>
       </c>
       <c r="F48" s="5">
         <f t="shared" si="2"/>
-        <v>0.51</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="H48" s="3">
         <f t="shared" si="0"/>
-        <v>4661.3999999999996</v>
+        <v>4916.6500000000005</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
@@ -5737,8 +5737,8 @@
         <v>31</v>
       </c>
       <c r="B49">
-        <f>VLOOKUP(A49,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3135488</v>
+        <f>VLOOKUP(A49,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>13093528</v>
       </c>
       <c r="C49">
         <f>VLOOKUP(A49,power!$B$2:$C$101,2,FALSE)</f>
@@ -5746,15 +5746,15 @@
       </c>
       <c r="E49" s="5">
         <f t="shared" si="1"/>
-        <v>0.51</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="F49" s="5">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H49" s="3">
         <f t="shared" si="0"/>
-        <v>2550</v>
+        <v>3974.2500000000005</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -5762,8 +5762,8 @@
         <v>28</v>
       </c>
       <c r="B50">
-        <f>VLOOKUP(A50,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4109114</v>
+        <f>VLOOKUP(A50,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10218996</v>
       </c>
       <c r="C50">
         <f>VLOOKUP(A50,power!$B$2:$C$101,2,FALSE)</f>
@@ -5771,15 +5771,15 @@
       </c>
       <c r="E50" s="5">
         <f t="shared" si="1"/>
-        <v>0.72299999999999998</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="F50" s="5">
         <f t="shared" si="2"/>
-        <v>0.48899999999999999</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="H50" s="3">
         <f t="shared" si="0"/>
-        <v>3535.47</v>
+        <v>2909.75</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
@@ -5787,8 +5787,8 @@
         <v>4</v>
       </c>
       <c r="B51">
-        <f>VLOOKUP(A51,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2871198</v>
+        <f>VLOOKUP(A51,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7884924</v>
       </c>
       <c r="C51">
         <f>VLOOKUP(A51,power!$B$2:$C$101,2,FALSE)</f>
@@ -5796,15 +5796,15 @@
       </c>
       <c r="E51" s="5">
         <f t="shared" si="1"/>
-        <v>0.46800000000000003</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="F51" s="5">
         <f t="shared" si="2"/>
-        <v>0.47799999999999998</v>
+        <v>0.505</v>
       </c>
       <c r="H51" s="3">
         <f t="shared" si="0"/>
-        <v>2237.04</v>
+        <v>2141.2000000000003</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
@@ -5812,8 +5812,8 @@
         <v>76</v>
       </c>
       <c r="B52">
-        <f>VLOOKUP(A52,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3160555</v>
+        <f>VLOOKUP(A52,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>15294087</v>
       </c>
       <c r="C52">
         <f>VLOOKUP(A52,power!$B$2:$C$101,2,FALSE)</f>
@@ -5821,15 +5821,15 @@
       </c>
       <c r="E52" s="5">
         <f t="shared" si="1"/>
-        <v>0.52100000000000002</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="F52" s="5">
         <f t="shared" si="2"/>
-        <v>0.46800000000000003</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="H52" s="3">
         <f t="shared" si="0"/>
-        <v>2438.2800000000002</v>
+        <v>4139.72</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
@@ -5837,8 +5837,8 @@
         <v>22</v>
       </c>
       <c r="B53">
-        <f>VLOOKUP(A53,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2766515</v>
+        <f>VLOOKUP(A53,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9472278</v>
       </c>
       <c r="C53">
         <f>VLOOKUP(A53,power!$B$2:$C$101,2,FALSE)</f>
@@ -5846,15 +5846,15 @@
       </c>
       <c r="E53" s="5">
         <f t="shared" si="1"/>
-        <v>0.436</v>
+        <v>0.505</v>
       </c>
       <c r="F53" s="5">
         <f t="shared" si="2"/>
-        <v>0.45700000000000002</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="H53" s="3">
         <f t="shared" si="0"/>
-        <v>1992.5200000000002</v>
+        <v>2444.1999999999998</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
@@ -5862,8 +5862,8 @@
         <v>51</v>
       </c>
       <c r="B54">
-        <f>VLOOKUP(A54,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>5693755</v>
+        <f>VLOOKUP(A54,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>13439148</v>
       </c>
       <c r="C54">
         <f>VLOOKUP(A54,power!$B$2:$C$101,2,FALSE)</f>
@@ -5871,15 +5871,15 @@
       </c>
       <c r="E54" s="5">
         <f t="shared" si="1"/>
-        <v>0.89300000000000002</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="F54" s="5">
         <f t="shared" si="2"/>
-        <v>0.44600000000000001</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="H54" s="3">
         <f t="shared" si="0"/>
-        <v>3982.78</v>
+        <v>3682.98</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
@@ -5887,8 +5887,8 @@
         <v>24</v>
       </c>
       <c r="B55">
-        <f>VLOOKUP(A55,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>5314806</v>
+        <f>VLOOKUP(A55,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>11078731</v>
       </c>
       <c r="C55">
         <f>VLOOKUP(A55,power!$B$2:$C$101,2,FALSE)</f>
@@ -5896,15 +5896,15 @@
       </c>
       <c r="E55" s="5">
         <f t="shared" si="1"/>
-        <v>0.872</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="F55" s="5">
         <f t="shared" si="2"/>
-        <v>0.436</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="H55" s="3">
         <f t="shared" si="0"/>
-        <v>3801.9199999999996</v>
+        <v>3043.8400000000006</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
@@ -5912,8 +5912,8 @@
         <v>9</v>
       </c>
       <c r="B56">
-        <f>VLOOKUP(A56,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>959715</v>
+        <f>VLOOKUP(A56,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3548963</v>
       </c>
       <c r="C56">
         <f>VLOOKUP(A56,power!$B$2:$C$101,2,FALSE)</f>
@@ -5921,15 +5921,15 @@
       </c>
       <c r="E56" s="5">
         <f t="shared" si="1"/>
-        <v>0.11700000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="F56" s="5">
         <f t="shared" si="2"/>
-        <v>0.42499999999999999</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="0"/>
-        <v>497.25</v>
+        <v>730.94</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -5937,8 +5937,8 @@
         <v>18</v>
       </c>
       <c r="B57">
-        <f>VLOOKUP(A57,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3433393</v>
+        <f>VLOOKUP(A57,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8216150</v>
       </c>
       <c r="C57">
         <f>VLOOKUP(A57,power!$B$2:$C$101,2,FALSE)</f>
@@ -5946,15 +5946,15 @@
       </c>
       <c r="E57" s="5">
         <f t="shared" si="1"/>
-        <v>0.59499999999999997</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="F57" s="5">
         <f t="shared" si="2"/>
-        <v>0.41399999999999998</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="H57" s="3">
         <f t="shared" si="0"/>
-        <v>2463.2999999999997</v>
+        <v>1971.3600000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
@@ -5962,8 +5962,8 @@
         <v>37</v>
       </c>
       <c r="B58">
-        <f>VLOOKUP(A58,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3370400</v>
+        <f>VLOOKUP(A58,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>14291841</v>
       </c>
       <c r="C58">
         <f>VLOOKUP(A58,power!$B$2:$C$101,2,FALSE)</f>
@@ -5971,15 +5971,15 @@
       </c>
       <c r="E58" s="5">
         <f t="shared" si="1"/>
-        <v>0.58499999999999996</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="F58" s="5">
         <f t="shared" si="2"/>
-        <v>0.40400000000000003</v>
+        <v>0.434</v>
       </c>
       <c r="H58" s="3">
         <f t="shared" si="0"/>
-        <v>2363.4</v>
+        <v>3550.12</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
@@ -5987,8 +5987,8 @@
         <v>44</v>
       </c>
       <c r="B59">
-        <f>VLOOKUP(A59,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4789200</v>
+        <f>VLOOKUP(A59,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>18355231</v>
       </c>
       <c r="C59">
         <f>VLOOKUP(A59,power!$B$2:$C$101,2,FALSE)</f>
@@ -5996,15 +5996,15 @@
       </c>
       <c r="E59" s="5">
         <f t="shared" si="1"/>
-        <v>0.81899999999999995</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="F59" s="5">
         <f t="shared" si="2"/>
-        <v>0.39300000000000002</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="H59" s="3">
         <f t="shared" si="0"/>
-        <v>3218.67</v>
+        <v>3854.16</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
@@ -6012,8 +6012,8 @@
         <v>87</v>
       </c>
       <c r="B60">
-        <f>VLOOKUP(A60,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1976858</v>
+        <f>VLOOKUP(A60,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6352421</v>
       </c>
       <c r="C60">
         <f>VLOOKUP(A60,power!$B$2:$C$101,2,FALSE)</f>
@@ -6021,15 +6021,15 @@
       </c>
       <c r="E60" s="5">
         <f t="shared" si="1"/>
-        <v>0.23400000000000001</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="F60" s="5">
         <f t="shared" si="2"/>
-        <v>0.38200000000000001</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="H60" s="3">
         <f t="shared" si="0"/>
-        <v>893.88000000000011</v>
+        <v>1337.22</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
@@ -6037,8 +6037,8 @@
         <v>62</v>
       </c>
       <c r="B61">
-        <f>VLOOKUP(A61,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>6194536</v>
+        <f>VLOOKUP(A61,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>21169959</v>
       </c>
       <c r="C61">
         <f>VLOOKUP(A61,power!$B$2:$C$101,2,FALSE)</f>
@@ -6046,15 +6046,15 @@
       </c>
       <c r="E61" s="5">
         <f t="shared" si="1"/>
-        <v>0.93600000000000005</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="F61" s="5">
         <f t="shared" si="2"/>
-        <v>0.372</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="H61" s="3">
         <f t="shared" si="0"/>
-        <v>3481.92</v>
+        <v>3793.5600000000004</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
@@ -6062,8 +6062,8 @@
         <v>10</v>
       </c>
       <c r="B62">
-        <f>VLOOKUP(A62,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2315865</v>
+        <f>VLOOKUP(A62,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5928006</v>
       </c>
       <c r="C62">
         <f>VLOOKUP(A62,power!$B$2:$C$101,2,FALSE)</f>
@@ -6071,15 +6071,15 @@
       </c>
       <c r="E62" s="5">
         <f t="shared" si="1"/>
-        <v>0.35099999999999998</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="F62" s="5">
         <f t="shared" si="2"/>
-        <v>0.36099999999999999</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="H62" s="3">
         <f t="shared" si="0"/>
-        <v>1267.1099999999999</v>
+        <v>1068.9600000000003</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
@@ -6087,7 +6087,7 @@
         <v>82</v>
       </c>
       <c r="B63">
-        <f>VLOOKUP(A63,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <f>VLOOKUP(A63,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
         <v>2217385</v>
       </c>
       <c r="C63">
@@ -6096,15 +6096,15 @@
       </c>
       <c r="E63" s="5">
         <f t="shared" si="1"/>
-        <v>0.31900000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F63" s="5">
         <f t="shared" si="2"/>
-        <v>0.35099999999999998</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="H63" s="3">
         <f t="shared" si="0"/>
-        <v>1119.69</v>
+        <v>386.83000000000004</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
@@ -6112,8 +6112,8 @@
         <v>32</v>
       </c>
       <c r="B64">
-        <f>VLOOKUP(A64,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2071567</v>
+        <f>VLOOKUP(A64,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>5204952</v>
       </c>
       <c r="C64">
         <f>VLOOKUP(A64,power!$B$2:$C$101,2,FALSE)</f>
@@ -6121,15 +6121,15 @@
       </c>
       <c r="E64" s="5">
         <f t="shared" si="1"/>
-        <v>0.27600000000000002</v>
+        <v>0.252</v>
       </c>
       <c r="F64" s="5">
         <f t="shared" si="2"/>
-        <v>0.34</v>
+        <v>0.373</v>
       </c>
       <c r="H64" s="3">
         <f t="shared" si="0"/>
-        <v>938.4000000000002</v>
+        <v>939.95999999999992</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
@@ -6137,8 +6137,8 @@
         <v>14</v>
       </c>
       <c r="B65">
-        <f>VLOOKUP(A65,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2321953</v>
+        <f>VLOOKUP(A65,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7655584</v>
       </c>
       <c r="C65">
         <f>VLOOKUP(A65,power!$B$2:$C$101,2,FALSE)</f>
@@ -6146,15 +6146,15 @@
       </c>
       <c r="E65" s="5">
         <f t="shared" si="1"/>
-        <v>0.36099999999999999</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="F65" s="5">
         <f t="shared" si="2"/>
-        <v>0.32900000000000001</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="H65" s="3">
         <f t="shared" si="0"/>
-        <v>1187.69</v>
+        <v>1426.5900000000001</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
@@ -6162,8 +6162,8 @@
         <v>0</v>
       </c>
       <c r="B66">
-        <f>VLOOKUP(A66,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4365881</v>
+        <f>VLOOKUP(A66,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9052808</v>
       </c>
       <c r="C66">
         <f>VLOOKUP(A66,power!$B$2:$C$101,2,FALSE)</f>
@@ -6171,15 +6171,15 @@
       </c>
       <c r="E66" s="5">
         <f t="shared" si="1"/>
-        <v>0.755</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="F66" s="5">
         <f t="shared" si="2"/>
-        <v>0.31900000000000001</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="H66" s="3">
         <f t="shared" si="0"/>
-        <v>2408.4499999999998</v>
+        <v>1708.5199999999998</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
@@ -6187,24 +6187,24 @@
         <v>15</v>
       </c>
       <c r="B67">
-        <f>VLOOKUP(A67,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2640978</v>
+        <f>VLOOKUP(A67,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8108164</v>
       </c>
       <c r="C67">
         <f>VLOOKUP(A67,power!$B$2:$C$101,2,FALSE)</f>
         <v>15257020</v>
       </c>
       <c r="E67" s="5">
-        <f t="shared" ref="E67:E96" si="3">PERCENTRANK(B$2:B$96,B67)</f>
-        <v>0.40400000000000003</v>
+        <f t="shared" ref="E67:E101" si="3">PERCENTRANK(B$2:B$101,B67)</f>
+        <v>0.434</v>
       </c>
       <c r="F67" s="5">
-        <f t="shared" ref="F67:F96" si="4">PERCENTRANK(C$2:C$96,C67)</f>
-        <v>0.308</v>
+        <f t="shared" ref="F67:F101" si="4">PERCENTRANK(C$2:C$101,C67)</f>
+        <v>0.34300000000000003</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" ref="H67:H96" si="5">+E67*F67*10000</f>
-        <v>1244.32</v>
+        <v>1488.6200000000001</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
@@ -6212,8 +6212,8 @@
         <v>88</v>
       </c>
       <c r="B68">
-        <f>VLOOKUP(A68,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1784180</v>
+        <f>VLOOKUP(A68,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6177225</v>
       </c>
       <c r="C68">
         <f>VLOOKUP(A68,power!$B$2:$C$101,2,FALSE)</f>
@@ -6221,15 +6221,15 @@
       </c>
       <c r="E68" s="5">
         <f t="shared" si="3"/>
-        <v>0.20200000000000001</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="F68" s="5">
         <f t="shared" si="4"/>
-        <v>0.29699999999999999</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="5"/>
-        <v>599.93999999999994</v>
+        <v>972.36</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
@@ -6237,8 +6237,8 @@
         <v>45</v>
       </c>
       <c r="B69">
-        <f>VLOOKUP(A69,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3643650</v>
+        <f>VLOOKUP(A69,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>16902407</v>
       </c>
       <c r="C69">
         <f>VLOOKUP(A69,power!$B$2:$C$101,2,FALSE)</f>
@@ -6246,15 +6246,15 @@
       </c>
       <c r="E69" s="5">
         <f t="shared" si="3"/>
-        <v>0.63800000000000001</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="F69" s="5">
         <f t="shared" si="4"/>
-        <v>0.28699999999999998</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="5"/>
-        <v>1831.06</v>
+        <v>2803.64</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -6262,8 +6262,8 @@
         <v>92</v>
       </c>
       <c r="B70">
-        <f>VLOOKUP(A70,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1523733</v>
+        <f>VLOOKUP(A70,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3769888</v>
       </c>
       <c r="C70">
         <f>VLOOKUP(A70,power!$B$2:$C$101,2,FALSE)</f>
@@ -6271,15 +6271,15 @@
       </c>
       <c r="E70" s="5">
         <f t="shared" si="3"/>
-        <v>0.159</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="F70" s="5">
         <f t="shared" si="4"/>
-        <v>0.27600000000000002</v>
+        <v>0.313</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="5"/>
-        <v>438.84000000000009</v>
+        <v>535.23</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
@@ -6287,8 +6287,8 @@
         <v>6</v>
       </c>
       <c r="B71">
-        <f>VLOOKUP(A71,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>935625</v>
+        <f>VLOOKUP(A71,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3081809</v>
       </c>
       <c r="C71">
         <f>VLOOKUP(A71,power!$B$2:$C$101,2,FALSE)</f>
@@ -6296,15 +6296,15 @@
       </c>
       <c r="E71" s="5">
         <f t="shared" si="3"/>
-        <v>0.106</v>
+        <v>0.121</v>
       </c>
       <c r="F71" s="5">
         <f t="shared" si="4"/>
-        <v>0.26500000000000001</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="5"/>
-        <v>280.89999999999998</v>
+        <v>366.63</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
@@ -6312,8 +6312,8 @@
         <v>8</v>
       </c>
       <c r="B72">
-        <f>VLOOKUP(A72,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>885310</v>
+        <f>VLOOKUP(A72,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1848861</v>
       </c>
       <c r="C72">
         <f>VLOOKUP(A72,power!$B$2:$C$101,2,FALSE)</f>
@@ -6321,15 +6321,15 @@
       </c>
       <c r="E72" s="5">
         <f t="shared" si="3"/>
-        <v>7.3999999999999996E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F72" s="5">
         <f t="shared" si="4"/>
-        <v>0.255</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="H72" s="3">
         <f t="shared" si="5"/>
-        <v>188.7</v>
+        <v>204.4</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
@@ -6337,8 +6337,8 @@
         <v>29</v>
       </c>
       <c r="B73">
-        <f>VLOOKUP(A73,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4150228</v>
+        <f>VLOOKUP(A73,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10327056</v>
       </c>
       <c r="C73">
         <f>VLOOKUP(A73,power!$B$2:$C$101,2,FALSE)</f>
@@ -6346,15 +6346,15 @@
       </c>
       <c r="E73" s="5">
         <f t="shared" si="3"/>
-        <v>0.73399999999999999</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F73" s="5">
         <f t="shared" si="4"/>
-        <v>0.24399999999999999</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="H73" s="3">
         <f t="shared" si="5"/>
-        <v>1790.96</v>
+        <v>1621.4999999999995</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
@@ -6362,8 +6362,8 @@
         <v>41</v>
       </c>
       <c r="B74">
-        <f>VLOOKUP(A74,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1936160</v>
+        <f>VLOOKUP(A74,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8547509</v>
       </c>
       <c r="C74">
         <f>VLOOKUP(A74,power!$B$2:$C$101,2,FALSE)</f>
@@ -6371,15 +6371,15 @@
       </c>
       <c r="E74" s="5">
         <f t="shared" si="3"/>
-        <v>0.223</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="F74" s="5">
         <f t="shared" si="4"/>
-        <v>0.23400000000000001</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="H74" s="3">
         <f t="shared" si="5"/>
-        <v>521.82000000000005</v>
+        <v>1262.0800000000002</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
@@ -6387,8 +6387,8 @@
         <v>35</v>
       </c>
       <c r="B75">
-        <f>VLOOKUP(A75,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3185355</v>
+        <f>VLOOKUP(A75,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9789935</v>
       </c>
       <c r="C75">
         <f>VLOOKUP(A75,power!$B$2:$C$101,2,FALSE)</f>
@@ -6396,15 +6396,15 @@
       </c>
       <c r="E75" s="5">
         <f t="shared" si="3"/>
-        <v>0.54200000000000004</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="F75" s="5">
         <f t="shared" si="4"/>
-        <v>0.223</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="H75" s="3">
         <f t="shared" si="5"/>
-        <v>1208.6600000000001</v>
+        <v>1401.7000000000003</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
@@ -6412,8 +6412,8 @@
         <v>7</v>
       </c>
       <c r="B76">
-        <f>VLOOKUP(A76,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1152085</v>
+        <f>VLOOKUP(A76,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3938443</v>
       </c>
       <c r="C76">
         <f>VLOOKUP(A76,power!$B$2:$C$101,2,FALSE)</f>
@@ -6421,15 +6421,15 @@
       </c>
       <c r="E76" s="5">
         <f t="shared" si="3"/>
-        <v>0.13800000000000001</v>
+        <v>0.191</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="4"/>
-        <v>0.21199999999999999</v>
+        <v>0.252</v>
       </c>
       <c r="H76" s="3">
         <f t="shared" si="5"/>
-        <v>292.56</v>
+        <v>481.32</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
@@ -6437,8 +6437,8 @@
         <v>94</v>
       </c>
       <c r="B77">
-        <f>VLOOKUP(A77,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>922725</v>
+        <f>VLOOKUP(A77,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3265579</v>
       </c>
       <c r="C77">
         <f>VLOOKUP(A77,power!$B$2:$C$101,2,FALSE)</f>
@@ -6446,15 +6446,15 @@
       </c>
       <c r="E77" s="5">
         <f t="shared" si="3"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="F77" s="5">
         <f t="shared" si="4"/>
-        <v>0.20200000000000001</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="H77" s="3">
         <f t="shared" si="5"/>
-        <v>191.90000000000003</v>
+        <v>341.21999999999991</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F78" s="5">
         <f t="shared" si="4"/>
-        <v>0.191</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="H78" s="3">
         <f t="shared" si="5"/>
@@ -6486,8 +6486,8 @@
         <v>84</v>
       </c>
       <c r="B79">
-        <f>VLOOKUP(A79,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2075935</v>
+        <f>VLOOKUP(A79,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8767712</v>
       </c>
       <c r="C79">
         <f>VLOOKUP(A79,power!$B$2:$C$101,2,FALSE)</f>
@@ -6495,15 +6495,15 @@
       </c>
       <c r="E79" s="5">
         <f t="shared" si="3"/>
-        <v>0.28699999999999998</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="F79" s="5">
         <f t="shared" si="4"/>
-        <v>0.18</v>
+        <v>0.222</v>
       </c>
       <c r="H79" s="3">
         <f t="shared" si="5"/>
-        <v>516.59999999999991</v>
+        <v>1052.28</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
@@ -6511,8 +6511,8 @@
         <v>55</v>
       </c>
       <c r="B80">
-        <f>VLOOKUP(A80,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3198516</v>
+        <f>VLOOKUP(A80,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9846771</v>
       </c>
       <c r="C80">
         <f>VLOOKUP(A80,power!$B$2:$C$101,2,FALSE)</f>
@@ -6520,15 +6520,15 @@
       </c>
       <c r="E80" s="5">
         <f t="shared" si="3"/>
-        <v>0.55300000000000005</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="F80" s="5">
         <f t="shared" si="4"/>
-        <v>0.17</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="H80" s="3">
         <f t="shared" si="5"/>
-        <v>940.10000000000014</v>
+        <v>1155.4000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
@@ -6536,8 +6536,8 @@
         <v>65</v>
       </c>
       <c r="B81">
-        <f>VLOOKUP(A81,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4791169</v>
+        <f>VLOOKUP(A81,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>13428284</v>
       </c>
       <c r="C81">
         <f>VLOOKUP(A81,power!$B$2:$C$101,2,FALSE)</f>
@@ -6545,15 +6545,15 @@
       </c>
       <c r="E81" s="5">
         <f t="shared" si="3"/>
-        <v>0.82899999999999996</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="F81" s="5">
         <f t="shared" si="4"/>
-        <v>0.159</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="H81" s="3">
         <f t="shared" si="5"/>
-        <v>1318.11</v>
+        <v>1549.3400000000001</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
@@ -6561,8 +6561,8 @@
         <v>97</v>
       </c>
       <c r="B82">
-        <f>VLOOKUP(A82,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>692004</v>
+        <f>VLOOKUP(A82,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>2549147</v>
       </c>
       <c r="C82">
         <f>VLOOKUP(A82,power!$B$2:$C$101,2,FALSE)</f>
@@ -6570,15 +6570,15 @@
       </c>
       <c r="E82" s="5">
         <f t="shared" si="3"/>
-        <v>5.2999999999999999E-2</v>
+        <v>0.111</v>
       </c>
       <c r="F82" s="5">
         <f t="shared" si="4"/>
-        <v>0.14799999999999999</v>
+        <v>0.191</v>
       </c>
       <c r="H82" s="3">
         <f t="shared" si="5"/>
-        <v>78.439999999999984</v>
+        <v>212.01000000000002</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
@@ -6586,7 +6586,7 @@
         <v>85</v>
       </c>
       <c r="B83">
-        <f>VLOOKUP(A83,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <f>VLOOKUP(A83,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
         <v>2025230</v>
       </c>
       <c r="C83">
@@ -6595,15 +6595,15 @@
       </c>
       <c r="E83" s="5">
         <f t="shared" si="3"/>
-        <v>0.255</v>
+        <v>0.09</v>
       </c>
       <c r="F83" s="5">
         <f t="shared" si="4"/>
-        <v>0.13800000000000001</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="H83" s="3">
         <f t="shared" si="5"/>
-        <v>351.90000000000003</v>
+        <v>162.89999999999998</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
@@ -6611,8 +6611,8 @@
         <v>90</v>
       </c>
       <c r="B84">
-        <f>VLOOKUP(A84,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1610065</v>
+        <f>VLOOKUP(A84,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>4368383</v>
       </c>
       <c r="C84">
         <f>VLOOKUP(A84,power!$B$2:$C$101,2,FALSE)</f>
@@ -6620,15 +6620,15 @@
       </c>
       <c r="E84" s="5">
         <f t="shared" si="3"/>
-        <v>0.17</v>
+        <v>0.222</v>
       </c>
       <c r="F84" s="5">
         <f t="shared" si="4"/>
-        <v>0.127</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="H84" s="3">
         <f t="shared" si="5"/>
-        <v>215.9</v>
+        <v>379.62</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -6636,7 +6636,7 @@
         <v>89</v>
       </c>
       <c r="B85">
-        <f>VLOOKUP(A85,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
+        <f>VLOOKUP(A85,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
         <v>1649135</v>
       </c>
       <c r="C85">
@@ -6645,15 +6645,15 @@
       </c>
       <c r="E85" s="5">
         <f t="shared" si="3"/>
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="F85" s="5">
         <f t="shared" si="4"/>
-        <v>0.11700000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="H85" s="3">
         <f t="shared" si="5"/>
-        <v>210.6</v>
+        <v>96.600000000000009</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
@@ -6661,8 +6661,8 @@
         <v>13</v>
       </c>
       <c r="B86">
-        <f>VLOOKUP(A86,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3089205</v>
+        <f>VLOOKUP(A86,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10492307</v>
       </c>
       <c r="C86">
         <f>VLOOKUP(A86,power!$B$2:$C$101,2,FALSE)</f>
@@ -6670,15 +6670,15 @@
       </c>
       <c r="E86" s="5">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="F86" s="5">
         <f t="shared" si="4"/>
-        <v>0.106</v>
+        <v>0.151</v>
       </c>
       <c r="H86" s="3">
         <f t="shared" si="5"/>
-        <v>530</v>
+        <v>883.35</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
@@ -6686,8 +6686,8 @@
         <v>16</v>
       </c>
       <c r="B87">
-        <f>VLOOKUP(A87,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3676403</v>
+        <f>VLOOKUP(A87,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>12455209</v>
       </c>
       <c r="C87">
         <f>VLOOKUP(A87,power!$B$2:$C$101,2,FALSE)</f>
@@ -6695,15 +6695,15 @@
       </c>
       <c r="E87" s="5">
         <f t="shared" si="3"/>
-        <v>0.64800000000000002</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="F87" s="5">
         <f t="shared" si="4"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="H87" s="3">
         <f t="shared" si="5"/>
-        <v>615.6</v>
+        <v>1010.9699999999999</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
@@ -6711,8 +6711,8 @@
         <v>81</v>
       </c>
       <c r="B88">
-        <f>VLOOKUP(A88,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2315507</v>
+        <f>VLOOKUP(A88,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7434459</v>
       </c>
       <c r="C88">
         <f>VLOOKUP(A88,power!$B$2:$C$101,2,FALSE)</f>
@@ -6720,15 +6720,15 @@
       </c>
       <c r="E88" s="5">
         <f t="shared" si="3"/>
-        <v>0.34</v>
+        <v>0.373</v>
       </c>
       <c r="F88" s="5">
         <f t="shared" si="4"/>
-        <v>8.5000000000000006E-2</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="H88" s="3">
         <f t="shared" si="5"/>
-        <v>289.00000000000006</v>
+        <v>488.63000000000005</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
@@ -6736,8 +6736,8 @@
         <v>73</v>
       </c>
       <c r="B89">
-        <f>VLOOKUP(A89,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3884630</v>
+        <f>VLOOKUP(A89,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>8301520</v>
       </c>
       <c r="C89">
         <f>VLOOKUP(A89,power!$B$2:$C$101,2,FALSE)</f>
@@ -6745,15 +6745,15 @@
       </c>
       <c r="E89" s="5">
         <f t="shared" si="3"/>
-        <v>0.69099999999999995</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="F89" s="5">
         <f t="shared" si="4"/>
-        <v>7.3999999999999996E-2</v>
+        <v>0.121</v>
       </c>
       <c r="H89" s="3">
         <f t="shared" si="5"/>
-        <v>511.33999999999992</v>
+        <v>549.33999999999992</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -6761,8 +6761,8 @@
         <v>78</v>
       </c>
       <c r="B90">
-        <f>VLOOKUP(A90,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>3068419</v>
+        <f>VLOOKUP(A90,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7813730</v>
       </c>
       <c r="C90">
         <f>VLOOKUP(A90,power!$B$2:$C$101,2,FALSE)</f>
@@ -6770,15 +6770,15 @@
       </c>
       <c r="E90" s="5">
         <f t="shared" si="3"/>
-        <v>0.47799999999999998</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="F90" s="5">
         <f t="shared" si="4"/>
-        <v>6.3E-2</v>
+        <v>0.111</v>
       </c>
       <c r="H90" s="3">
         <f t="shared" si="5"/>
-        <v>301.14</v>
+        <v>448.44</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
@@ -6786,8 +6786,8 @@
         <v>3</v>
       </c>
       <c r="B91">
-        <f>VLOOKUP(A91,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4862491</v>
+        <f>VLOOKUP(A91,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>9693854</v>
       </c>
       <c r="C91">
         <f>VLOOKUP(A91,power!$B$2:$C$101,2,FALSE)</f>
@@ -6795,15 +6795,15 @@
       </c>
       <c r="E91" s="5">
         <f t="shared" si="3"/>
-        <v>0.85099999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="F91" s="5">
         <f t="shared" si="4"/>
-        <v>5.2999999999999999E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="H91" s="3">
         <f t="shared" si="5"/>
-        <v>451.03</v>
+        <v>530.25</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
@@ -6811,8 +6811,8 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <f>VLOOKUP(A92,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2305405</v>
+        <f>VLOOKUP(A92,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6060071</v>
       </c>
       <c r="C92">
         <f>VLOOKUP(A92,power!$B$2:$C$101,2,FALSE)</f>
@@ -6820,15 +6820,15 @@
       </c>
       <c r="E92" s="5">
         <f t="shared" si="3"/>
-        <v>0.32900000000000001</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="F92" s="5">
         <f t="shared" si="4"/>
-        <v>4.2000000000000003E-2</v>
+        <v>0.09</v>
       </c>
       <c r="H92" s="3">
         <f t="shared" si="5"/>
-        <v>138.18000000000004</v>
+        <v>253.79999999999995</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
@@ -6836,8 +6836,8 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <f>VLOOKUP(A93,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>701850</v>
+        <f>VLOOKUP(A93,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1513550</v>
       </c>
       <c r="C93">
         <f>VLOOKUP(A93,power!$B$2:$C$101,2,FALSE)</f>
@@ -6845,15 +6845,15 @@
       </c>
       <c r="E93" s="5">
         <f t="shared" si="3"/>
-        <v>6.3E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F93" s="5">
         <f t="shared" si="4"/>
-        <v>3.1E-2</v>
+        <v>0.08</v>
       </c>
       <c r="H93" s="3">
         <f t="shared" si="5"/>
-        <v>19.53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
@@ -6861,8 +6861,8 @@
         <v>71</v>
       </c>
       <c r="B94">
-        <f>VLOOKUP(A94,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4088818</v>
+        <f>VLOOKUP(A94,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>10504976</v>
       </c>
       <c r="C94">
         <f>VLOOKUP(A94,power!$B$2:$C$101,2,FALSE)</f>
@@ -6870,15 +6870,15 @@
       </c>
       <c r="E94" s="5">
         <f t="shared" si="3"/>
-        <v>0.71199999999999997</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="F94" s="5">
         <f t="shared" si="4"/>
-        <v>2.1000000000000001E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H94" s="3">
         <f t="shared" si="5"/>
-        <v>149.52000000000001</v>
+        <v>424.20000000000005</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -6886,8 +6886,8 @@
         <v>27</v>
       </c>
       <c r="B95">
-        <f>VLOOKUP(A95,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1109645</v>
+        <f>VLOOKUP(A95,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7049198</v>
       </c>
       <c r="C95">
         <f>VLOOKUP(A95,power!$B$2:$C$101,2,FALSE)</f>
@@ -6895,15 +6895,15 @@
       </c>
       <c r="E95" s="5">
         <f t="shared" si="3"/>
-        <v>0.127</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="F95" s="5">
         <f t="shared" si="4"/>
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="H95" s="3">
         <f t="shared" si="5"/>
-        <v>12.700000000000001</v>
+        <v>217.79999999999998</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -6923,76 +6923,136 @@
       </c>
       <c r="F96" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H96" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>79</v>
       </c>
       <c r="B97">
-        <f>VLOOKUP(A97,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>2849850</v>
+        <f>VLOOKUP(A97,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>7827370</v>
       </c>
       <c r="C97">
         <f>VLOOKUP(A97,power!$B$2:$C$101,2,FALSE)</f>
         <v>9983003</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E97" s="5">
+        <f t="shared" si="3"/>
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="F97" s="5">
+        <f t="shared" si="4"/>
+        <v>0.04</v>
+      </c>
+      <c r="H97" s="3">
+        <f t="shared" ref="H97:H101" si="6">+E97*F97*10000</f>
+        <v>165.6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>93</v>
       </c>
       <c r="B98">
-        <f>VLOOKUP(A98,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1014383</v>
+        <f>VLOOKUP(A98,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>3155370</v>
       </c>
       <c r="C98">
         <f>VLOOKUP(A98,power!$B$2:$C$101,2,FALSE)</f>
         <v>5997750</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E98" s="5">
+        <f t="shared" si="3"/>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="F98" s="5">
+        <f t="shared" si="4"/>
+        <v>0.03</v>
+      </c>
+      <c r="H98" s="3">
+        <f t="shared" si="6"/>
+        <v>39.300000000000004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>70</v>
       </c>
       <c r="B99">
-        <f>VLOOKUP(A99,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>4121213</v>
+        <f>VLOOKUP(A99,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>6227502</v>
       </c>
       <c r="C99">
         <f>VLOOKUP(A99,power!$B$2:$C$101,2,FALSE)</f>
         <v>5821797</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E99" s="5">
+        <f t="shared" si="3"/>
+        <v>0.30299999999999999</v>
+      </c>
+      <c r="F99" s="5">
+        <f t="shared" si="4"/>
+        <v>0.02</v>
+      </c>
+      <c r="H99" s="3">
+        <f t="shared" si="6"/>
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
       <c r="B100">
-        <f>VLOOKUP(A100,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>548600</v>
+        <f>VLOOKUP(A100,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>629900</v>
       </c>
       <c r="C100">
         <f>VLOOKUP(A100,power!$B$2:$C$101,2,FALSE)</f>
         <v>2029812</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E100" s="5">
+        <f t="shared" si="3"/>
+        <v>0.04</v>
+      </c>
+      <c r="F100" s="5">
+        <f t="shared" si="4"/>
+        <v>0.01</v>
+      </c>
+      <c r="H100" s="3">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>91</v>
       </c>
       <c r="B101">
-        <f>VLOOKUP(A101,'vs (thru Wed 740pm)'!$B$2:$C$97,2,FALSE)</f>
-        <v>1544400</v>
+        <f>VLOOKUP(A101,'vs (thru Wed 815pm)'!$B$2:$C$97,2,FALSE)</f>
+        <v>1988150</v>
       </c>
       <c r="C101">
         <f>VLOOKUP(A101,power!$B$2:$C$101,2,FALSE)</f>
         <v>1595038</v>
+      </c>
+      <c r="E101" s="5">
+        <f t="shared" si="3"/>
+        <v>0.08</v>
+      </c>
+      <c r="F101" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
